--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -21765,7 +21765,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L171" s="34" t="n"/>
+      <c r="L171" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M171" s="25" t="inlineStr">
         <is>
           <t>Pass</t>

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -1357,8 +1357,16 @@
           <t>w:body</t>
         </is>
       </c>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="8" t="n"/>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>SD-2253</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>fail?</t>
+        </is>
+      </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
           <t>-</t>

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -23776,37 +23776,125 @@
       <c r="P199" s="4" t="n"/>
     </row>
     <row r="200" ht="13.5" customHeight="1" s="53">
-      <c r="A200" s="4" t="n"/>
-      <c r="B200" s="4" t="n"/>
-      <c r="C200" s="4" t="n"/>
-      <c r="D200" s="4" t="n"/>
-      <c r="E200" s="4" t="n"/>
-      <c r="F200" s="4" t="n"/>
-      <c r="G200" s="4" t="n"/>
-      <c r="H200" s="4" t="n"/>
-      <c r="I200" s="4" t="n"/>
-      <c r="J200" s="4" t="n"/>
-      <c r="K200" s="4" t="n"/>
-      <c r="L200" s="15" t="n"/>
-      <c r="M200" s="4" t="n"/>
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>styles.apply</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>styles</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>Requires an existing styles target in the starter file.</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>The output DOCX should show the visible document change produced by styles.apply.</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>Pending: no runnable script mapped for styles.apply</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr"/>
+      <c r="L200" s="15" t="inlineStr"/>
+      <c r="M200" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N200" s="4" t="n"/>
       <c r="O200" s="4" t="n"/>
       <c r="P200" s="4" t="n"/>
     </row>
     <row r="201" ht="13.5" customHeight="1" s="53">
-      <c r="A201" s="4" t="n"/>
-      <c r="B201" s="4" t="n"/>
-      <c r="C201" s="4" t="n"/>
-      <c r="D201" s="4" t="n"/>
-      <c r="E201" s="4" t="n"/>
-      <c r="F201" s="4" t="n"/>
-      <c r="G201" s="4" t="n"/>
-      <c r="H201" s="4" t="n"/>
-      <c r="I201" s="4" t="n"/>
-      <c r="J201" s="4" t="n"/>
-      <c r="K201" s="4" t="n"/>
-      <c r="L201" s="15" t="n"/>
-      <c r="M201" s="4" t="n"/>
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>trackChanges.decide</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>trackChanges</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>Requires an existing trackChanges target in the starter file.</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>The output DOCX should show the visible document change produced by trackChanges.decide.</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>Pending: no runnable script mapped for trackChanges.decide</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr"/>
+      <c r="L201" s="15" t="inlineStr"/>
+      <c r="M201" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="n"/>
       <c r="P201" s="4" t="n"/>

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -3260,7 +3260,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
@@ -17278,47 +17278,42 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-strike</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E112" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-strike-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should have one horizontal line through the middle (same visual as strikethrough).</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.strike.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.strike requires a text target.'); requireSuccess(docAny.format.strike({ target }), operation);</t>
+          <t>Pending: no runnable script mapped for format.strike</t>
         </is>
       </c>
       <c r="H112" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.strike" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-strike-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-strike-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I112" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:strike,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J112" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="25" t="inlineStr">
@@ -17333,7 +17328,7 @@
       </c>
       <c r="M112" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="32" t="n"/>
@@ -17357,47 +17352,42 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-highlight</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E113" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-highlight-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should have a bright yellow marker-style highlight behind the text.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.highlight.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.highlight requires a text target.'); requireSuccess(docAny.format.highlight({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.highlight</t>
         </is>
       </c>
       <c r="H113" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.highlight" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-highlight-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-highlight-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I113" s="25" t="inlineStr">
         <is>
-          <t>w:highlight,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J113" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="25" t="inlineStr">
@@ -17412,7 +17402,7 @@
       </c>
       <c r="M113" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="32" t="n"/>
@@ -17440,47 +17430,42 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-shading</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E114" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-shading-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should have a solid fill background behind the text (run shading, not full paragraph fill).</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.shading.</t>
         </is>
       </c>
       <c r="G114" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.shading requires a text target.'); requireSuccess(docAny.format.shading({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.shading</t>
         </is>
       </c>
       <c r="H114" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.shading" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-shading-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-shading-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I114" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:shd,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="25" t="inlineStr">
@@ -17495,7 +17480,7 @@
       </c>
       <c r="M114" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="32" t="n"/>
@@ -17523,47 +17508,42 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-border</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-border-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". There should be a visible box/border around the text run.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.border.</t>
         </is>
       </c>
       <c r="G115" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.border requires a text target.'); requireSuccess(docAny.format.border({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.border</t>
         </is>
       </c>
       <c r="H115" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.border" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-border-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-border-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I115" s="25" t="inlineStr">
         <is>
-          <t>w:bdr,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J115" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="25" t="inlineStr">
@@ -17578,7 +17558,7 @@
       </c>
       <c r="M115" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="32" t="n"/>
@@ -17602,47 +17582,42 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-outline</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E116" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-outline-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F116" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". The letters should look outlined/hollow compared to normal filled text.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.outline.</t>
         </is>
       </c>
       <c r="G116" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.outline requires a text target.'); requireSuccess(docAny.format.outline({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.outline</t>
         </is>
       </c>
       <c r="H116" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.outline" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-outline-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-outline-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I116" s="25" t="inlineStr">
         <is>
-          <t>w:outline,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J116" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="25" t="inlineStr">
@@ -17657,7 +17632,7 @@
       </c>
       <c r="M116" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="32" t="n"/>
@@ -17685,47 +17660,42 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-shadow</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E117" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-shadow-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F117" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". There should be a visible shadow offset behind the letters.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.shadow.</t>
         </is>
       </c>
       <c r="G117" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.shadow requires a text target.'); requireSuccess(docAny.format.shadow({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.shadow</t>
         </is>
       </c>
       <c r="H117" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.shadow" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-shadow-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-shadow-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I117" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:shadow,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J117" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="25" t="inlineStr">
@@ -17740,7 +17710,7 @@
       </c>
       <c r="M117" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="32" t="n"/>
@@ -17768,47 +17738,42 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-emboss</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E118" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-emboss-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". The letters should look raised (3D embossed).</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.emboss.</t>
         </is>
       </c>
       <c r="G118" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.emboss requires a text target.'); requireSuccess(docAny.format.emboss({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.emboss</t>
         </is>
       </c>
       <c r="H118" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.emboss" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-emboss-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-emboss-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I118" s="25" t="inlineStr">
         <is>
-          <t>w:emboss,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J118" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="25" t="inlineStr">
@@ -17823,7 +17788,7 @@
       </c>
       <c r="M118" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="32" t="n"/>
@@ -17851,47 +17816,42 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-imprint</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-imprint-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". The letters should look pressed/engraved (sunken), opposite of emboss.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.imprint.</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.imprint requires a text target.'); requireSuccess(docAny.format.imprint({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.imprint</t>
         </is>
       </c>
       <c r="H119" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.imprint" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-imprint-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-imprint-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I119" s="25" t="inlineStr">
         <is>
-          <t>w:imprint,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J119" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="25" t="inlineStr">
@@ -17906,7 +17866,7 @@
       </c>
       <c r="M119" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="32" t="n"/>
@@ -17934,47 +17894,42 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-vert-align</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E120" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-vertAlign-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F120" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should be shifted up like superscript relative to baseline text.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.vertAlign.</t>
         </is>
       </c>
       <c r="G120" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.vertAlign requires a text target.'); requireSuccess(docAny.format.vertAlign({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.vertAlign</t>
         </is>
       </c>
       <c r="H120" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.vertAlign" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-vertAlign-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-vertAlign-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I120" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:t,w:vertAlign</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J120" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="25" t="inlineStr">
@@ -17989,7 +17944,7 @@
       </c>
       <c r="M120" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="32" t="n"/>
@@ -18017,47 +17972,42 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-position</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E121" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-position-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F121" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should be visibly moved vertically (raised/lowered) without changing neighboring words.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.position.</t>
         </is>
       </c>
       <c r="G121" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.position requires a text target.'); requireSuccess(docAny.format.position({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.position</t>
         </is>
       </c>
       <c r="H121" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.position" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-position-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-position-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I121" s="25" t="inlineStr">
         <is>
-          <t>w:position,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J121" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="25" t="inlineStr">
@@ -18072,7 +18022,7 @@
       </c>
       <c r="M121" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="32" t="n"/>
@@ -18096,47 +18046,42 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-rtl</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E122" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-rtl-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". RTL is applied at run level; expect local run behavior changes, not guaranteed full paragraph RTL reflow.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.rtl.</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.rtl requires a text target.'); requireSuccess(docAny.format.rtl({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.rtl</t>
         </is>
       </c>
       <c r="H122" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.rtl" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-rtl-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-rtl-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I122" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:rtl,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J122" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="28" t="inlineStr">
@@ -18151,7 +18096,7 @@
       </c>
       <c r="M122" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="32" t="n"/>
@@ -18179,47 +18124,42 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-cs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E123" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-cs-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F123" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". This sets complex-script property; visible difference may be subtle depending on font/script.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.cs.</t>
         </is>
       </c>
       <c r="G123" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.cs requires a text target.'); requireSuccess(docAny.format.cs({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.cs</t>
         </is>
       </c>
       <c r="H123" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.cs" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-cs-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-cs-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I123" s="25" t="inlineStr">
         <is>
-          <t>w:cs,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J123" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="25" t="inlineStr">
@@ -18230,7 +18170,7 @@
       <c r="L123" s="34" t="n"/>
       <c r="M123" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="32" t="n"/>
@@ -18254,47 +18194,42 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-b-cs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E124" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-bCs-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F124" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Complex-script bold is set; visible difference may be subtle unless CS rendering is active.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.bCs.</t>
         </is>
       </c>
       <c r="G124" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.bCs requires a text target.'); requireSuccess(docAny.format.bCs({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.bCs</t>
         </is>
       </c>
       <c r="H124" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.bCs" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-bCs-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-bCs-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I124" s="25" t="inlineStr">
         <is>
-          <t>w:bCs,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J124" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="25" t="inlineStr">
@@ -18305,7 +18240,7 @@
       <c r="L124" s="34" t="n"/>
       <c r="M124" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="32" t="n"/>
@@ -18329,47 +18264,42 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-i-cs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E125" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-iCs-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F125" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Complex-script italic is set; visible difference may be subtle unless CS rendering is active.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.iCs.</t>
         </is>
       </c>
       <c r="G125" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.iCs requires a text target.'); requireSuccess(docAny.format.iCs({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.iCs</t>
         </is>
       </c>
       <c r="H125" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.iCs" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-iCs-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-iCs-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I125" s="25" t="inlineStr">
         <is>
-          <t>w:iCs,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J125" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="25" t="inlineStr">
@@ -18380,7 +18310,7 @@
       <c r="L125" s="34" t="n"/>
       <c r="M125" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="32" t="n"/>
@@ -18404,47 +18334,42 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-vanish</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E126" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-vanish-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F126" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should be hidden text (may disappear depending on Word hidden-text display settings).</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.vanish.</t>
         </is>
       </c>
       <c r="G126" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.vanish requires a text target.'); requireSuccess(docAny.format.vanish({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.vanish</t>
         </is>
       </c>
       <c r="H126" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.vanish" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-vanish-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-vanish-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I126" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:t,w:vanish</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J126" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="25" t="inlineStr">
@@ -18459,7 +18384,7 @@
       </c>
       <c r="M126" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="32" t="n"/>
@@ -18483,47 +18408,42 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-web-hidden</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-webHidden-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F127" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It may be hidden in web-layout contexts; visual change depends on view mode.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.webHidden.</t>
         </is>
       </c>
       <c r="G127" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.webHidden requires a text target.'); requireSuccess(docAny.format.webHidden({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.webHidden</t>
         </is>
       </c>
       <c r="H127" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.webHidden" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-webHidden-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-webHidden-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I127" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:t,w:webHidden</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J127" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="25" t="inlineStr">
@@ -18538,7 +18458,7 @@
       </c>
       <c r="M127" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="32" t="n"/>
@@ -18562,47 +18482,42 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-spec-vanish</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E128" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-specVanish-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Special hidden behavior is set; visible change can be subtle and view-dependent.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.specVanish.</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.specVanish requires a text target.'); requireSuccess(docAny.format.specVanish({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.specVanish</t>
         </is>
       </c>
       <c r="H128" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.specVanish" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-specVanish-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-specVanish-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I128" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:specVanish,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J128" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="25" t="inlineStr">
@@ -18613,7 +18528,7 @@
       <c r="L128" s="34" t="n"/>
       <c r="M128" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" s="32" t="n"/>
@@ -18641,47 +18556,42 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-snap-to-grid</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-snapToGrid-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Snap-to-grid is set; visible difference is subtle unless document grid is enabled/obvious.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.snapToGrid.</t>
         </is>
       </c>
       <c r="G129" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.snapToGrid requires a text target.'); requireSuccess(docAny.format.snapToGrid({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.snapToGrid</t>
         </is>
       </c>
       <c r="H129" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.snapToGrid" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-snapToGrid-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-snapToGrid-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I129" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:snapToGrid,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J129" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="25" t="inlineStr">
@@ -18692,7 +18602,7 @@
       <c r="L129" s="34" t="n"/>
       <c r="M129" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="32" t="n"/>
@@ -18720,47 +18630,42 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-o-math</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E130" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-oMath-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F130" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Math-run flag is set; visible change may be subtle in plain text context.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.oMath.</t>
         </is>
       </c>
       <c r="G130" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.oMath requires a text target.'); requireSuccess(docAny.format.oMath({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.oMath</t>
         </is>
       </c>
       <c r="H130" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.oMath" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-oMath-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-oMath-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I130" s="25" t="inlineStr">
         <is>
-          <t>w:oMath,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J130" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="25" t="inlineStr">
@@ -18775,7 +18680,7 @@
       </c>
       <c r="M130" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N130" s="32" t="n"/>
@@ -18803,47 +18708,42 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-font-size-cs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-fontSizeCs-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Complex-script size is set to a large value; visible difference depends on CS rendering path.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.fontSizeCs.</t>
         </is>
       </c>
       <c r="G131" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.fontSizeCs requires a text target.'); requireSuccess(docAny.format.fontSizeCs({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.fontSizeCs</t>
         </is>
       </c>
       <c r="H131" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.fontSizeCs" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-fontSizeCs-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-fontSizeCs-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I131" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:szCs,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J131" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="25" t="inlineStr">
@@ -18854,7 +18754,7 @@
       <c r="L131" s="34" t="n"/>
       <c r="M131" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="32" t="n"/>
@@ -18878,47 +18778,42 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-char-scale</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E132" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-charScale-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Characters should look stretched wider than normal.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.charScale.</t>
         </is>
       </c>
       <c r="G132" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.charScale requires a text target.'); requireSuccess(docAny.format.charScale({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.charScale</t>
         </is>
       </c>
       <c r="H132" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.charScale" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-charScale-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-charScale-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I132" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:t,w:w</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J132" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="25" t="inlineStr">
@@ -18933,7 +18828,7 @@
       </c>
       <c r="M132" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N132" s="32" t="n"/>
@@ -18957,47 +18852,42 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-kerning</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-kerning-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Character-pair spacing behavior should change; often subtle unless size/font make it obvious.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.kerning.</t>
         </is>
       </c>
       <c r="G133" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.kerning requires a text target.'); requireSuccess(docAny.format.kerning({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.kerning</t>
         </is>
       </c>
       <c r="H133" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.kerning" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-kerning-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-kerning-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I133" s="25" t="inlineStr">
         <is>
-          <t>w:kern,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J133" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="25" t="inlineStr">
@@ -19008,7 +18898,7 @@
       <c r="L133" s="34" t="n"/>
       <c r="M133" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="32" t="n"/>
@@ -19036,47 +18926,42 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-fit-text</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E134" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-fitText-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Text should look compressed to fit width constraints (tighter than normal).</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.fitText.</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.fitText requires a text target.'); requireSuccess(docAny.format.fitText({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.fitText</t>
         </is>
       </c>
       <c r="H134" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.fitText" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-fitText-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-fitText-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I134" s="25" t="inlineStr">
         <is>
-          <t>w:fitText,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J134" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="25" t="inlineStr">
@@ -19087,7 +18972,7 @@
       <c r="L134" s="34" t="n"/>
       <c r="M134" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N134" s="32" t="n"/>
@@ -19111,47 +18996,42 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-lang</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E135" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-lang-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Language metadata is changed; visual difference may be minimal, but spell/locale behavior can differ.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.lang.</t>
         </is>
       </c>
       <c r="G135" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.lang requires a text target.'); requireSuccess(docAny.format.lang({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.lang</t>
         </is>
       </c>
       <c r="H135" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.lang" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-lang-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-lang-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I135" s="25" t="inlineStr">
         <is>
-          <t>w:lang,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J135" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="25" t="inlineStr">
@@ -19162,7 +19042,7 @@
       <c r="L135" s="34" t="n"/>
       <c r="M135" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="32" t="n"/>
@@ -19186,47 +19066,42 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-r-style</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E136" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-rStyle-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Run style should change appearance according to the referenced style.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.rStyle.</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.rStyle requires a text target.'); requireSuccess(docAny.format.rStyle({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.rStyle</t>
         </is>
       </c>
       <c r="H136" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.rStyle" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-rStyle-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-rStyle-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I136" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:rStyle,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J136" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="25" t="inlineStr">
@@ -19237,7 +19112,7 @@
       <c r="L136" s="34" t="n"/>
       <c r="M136" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N136" s="32" t="n"/>
@@ -19261,47 +19136,42 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-r-fonts</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-rFonts-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Font mapping should switch to the specified font, visibly different from nearby text.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.rFonts.</t>
         </is>
       </c>
       <c r="G137" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.rFonts requires a text target.'); requireSuccess(docAny.format.rFonts({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.rFonts</t>
         </is>
       </c>
       <c r="H137" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.rFonts" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-rFonts-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-rFonts-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I137" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J137" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="25" t="inlineStr">
@@ -19312,7 +19182,7 @@
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="32" t="n"/>
@@ -19336,47 +19206,42 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-east-asian-layout</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-eastAsianLayout-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". East Asian layout properties are set; visible difference depends on compatible script/font.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.eastAsianLayout.</t>
         </is>
       </c>
       <c r="G138" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.eastAsianLayout requires a text target.'); requireSuccess(docAny.format.eastAsianLayout({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.eastAsianLayout</t>
         </is>
       </c>
       <c r="H138" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.eastAsianLayout" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-eastAsianLayout-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-eastAsianLayout-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I138" s="25" t="inlineStr">
         <is>
-          <t>w:eastAsianLayout,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J138" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="25" t="inlineStr">
@@ -19387,7 +19252,7 @@
       <c r="L138" s="34" t="n"/>
       <c r="M138" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="32" t="n"/>
@@ -19411,47 +19276,42 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-em</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E139" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-em-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Emphasis mark styling should appear where supported by font/language.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.em.</t>
         </is>
       </c>
       <c r="G139" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.em requires a text target.'); requireSuccess(docAny.format.em({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.em</t>
         </is>
       </c>
       <c r="H139" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.em" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-em-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-em-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I139" s="25" t="inlineStr">
         <is>
-          <t>w:em,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J139" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="25" t="inlineStr">
@@ -19462,7 +19322,7 @@
       <c r="L139" s="34" t="n"/>
       <c r="M139" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="32" t="n"/>
@@ -19486,47 +19346,42 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-ligatures</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E140" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-ligatures-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Ligature shaping should change where the font supports ligatures.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.ligatures.</t>
         </is>
       </c>
       <c r="G140" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.ligatures requires a text target.'); requireSuccess(docAny.format.ligatures({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.ligatures</t>
         </is>
       </c>
       <c r="H140" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.ligatures" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-ligatures-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-ligatures-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I140" s="25" t="inlineStr">
         <is>
-          <t>w:ligatures,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J140" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="25" t="inlineStr">
@@ -19537,7 +19392,7 @@
       <c r="L140" s="34" t="n"/>
       <c r="M140" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="32" t="n"/>
@@ -19561,47 +19416,42 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-num-form</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-numForm-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F141" s="25" t="inlineStr">
         <is>
-          <t>If "bananas" contains digits, numeral form should change (old-style/lining). If no digits, visual change may be none.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.numForm.</t>
         </is>
       </c>
       <c r="G141" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.numForm requires a text target.'); requireSuccess(docAny.format.numForm({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.numForm</t>
         </is>
       </c>
       <c r="H141" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.numForm" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-numForm-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-numForm-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I141" s="25" t="inlineStr">
         <is>
-          <t>w:numForm,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J141" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="25" t="inlineStr">
@@ -19612,7 +19462,7 @@
       <c r="L141" s="34" t="n"/>
       <c r="M141" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="32" t="n"/>
@@ -19636,47 +19486,42 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-num-spacing</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E142" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-numSpacing-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>If "bananas" contains digits, numeral spacing should change (proportional/tabular). If no digits, visual change may be none.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.numSpacing.</t>
         </is>
       </c>
       <c r="G142" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.numSpacing requires a text target.'); requireSuccess(docAny.format.numSpacing({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.numSpacing</t>
         </is>
       </c>
       <c r="H142" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.numSpacing" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-numSpacing-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-numSpacing-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I142" s="25" t="inlineStr">
         <is>
-          <t>w:numSpacing,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J142" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="25" t="inlineStr">
@@ -19687,7 +19532,7 @@
       <c r="L142" s="34" t="n"/>
       <c r="M142" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N142" s="32" t="n"/>
@@ -19711,47 +19556,42 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-stylistic-sets</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E143" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-stylisticSets-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F143" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Alternate glyph forms should appear if the font supports the selected stylistic set.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.stylisticSets.</t>
         </is>
       </c>
       <c r="G143" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.stylisticSets requires a text target.'); requireSuccess(docAny.format.stylisticSets({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.stylisticSets</t>
         </is>
       </c>
       <c r="H143" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.stylisticSets" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-stylisticSets-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-stylisticSets-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I143" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:ss,w:stylisticSets,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J143" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="25" t="inlineStr">
@@ -19762,7 +19602,7 @@
       <c r="L143" s="34" t="n"/>
       <c r="M143" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="32" t="n"/>
@@ -19786,47 +19626,42 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-contextual-alternates</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E144" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-contextualAlternates-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Contextual alternate glyphs should appear if font supports them.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.contextualAlternates.</t>
         </is>
       </c>
       <c r="G144" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.contextualAlternates requires a text target.'); requireSuccess(docAny.format.contextualAlternates({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.contextualAlternates</t>
         </is>
       </c>
       <c r="H144" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.contextualAlternates" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-contextualAlternates-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-contextualAlternates-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I144" s="25" t="inlineStr">
         <is>
-          <t>w:cntxtAlts,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J144" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="25" t="inlineStr">
@@ -19837,7 +19672,7 @@
       <c r="L144" s="34" t="n"/>
       <c r="M144" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N144" s="32" t="n"/>
@@ -19865,47 +19700,42 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-dstrike</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-dstrike-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F145" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". It should have two horizontal strike lines (double strikethrough).</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.dstrike.</t>
         </is>
       </c>
       <c r="G145" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.dstrike requires a text target.'); requireSuccess(docAny.format.dstrike({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.dstrike</t>
         </is>
       </c>
       <c r="H145" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.dstrike" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-dstrike-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-dstrike-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I145" s="25" t="inlineStr">
         <is>
-          <t>w:dstrike,w:r,w:rPr,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J145" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="25" t="inlineStr">
@@ -19920,7 +19750,7 @@
       </c>
       <c r="M145" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="32" t="n"/>
@@ -19944,47 +19774,42 @@
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-small-caps</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E146" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-smallCaps-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F146" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Lowercase letters should appear as smaller capital letters.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.smallCaps.</t>
         </is>
       </c>
       <c r="G146" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.smallCaps requires a text target.'); requireSuccess(docAny.format.smallCaps({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.smallCaps</t>
         </is>
       </c>
       <c r="H146" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.smallCaps" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-smallCaps-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-smallCaps-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I146" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:rPr,w:smallCaps,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J146" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="25" t="inlineStr">
@@ -19999,7 +19824,7 @@
       </c>
       <c r="M146" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N146" s="32" t="n"/>
@@ -20023,47 +19848,42 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-caps</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E147" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-caps-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F147" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Letters should render in all caps style.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.caps.</t>
         </is>
       </c>
       <c r="G147" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.caps requires a text target.'); requireSuccess(docAny.format.caps({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.caps</t>
         </is>
       </c>
       <c r="H147" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.caps" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-caps-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-caps-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I147" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J147" s="25" t="inlineStr">
         <is>
-          <t>w:r,w:t</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="25" t="inlineStr">
@@ -20078,7 +19898,7 @@
       </c>
       <c r="M147" s="25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="32" t="n"/>
@@ -20102,37 +19922,32 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>docapi:format-letter-spacing</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E148" s="25" t="inlineStr">
         <is>
-          <t>Exaggerated rerun (March 1, 2026). Target word: "bananas". Output: format-letterSpacing-exaggerated-output.docx</t>
+          <t>Can run from a blank or prepared starter depending on the command.</t>
         </is>
       </c>
       <c r="F148" s="25" t="inlineStr">
         <is>
-          <t>Find "bananas". Letters should be visibly spread apart compared to normal spacing.</t>
+          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.letterSpacing.</t>
         </is>
       </c>
       <c r="G148" s="25" t="inlineStr">
         <is>
-          <t>const target = firstTextRange(doc); if (!target) throw new Error('format.letterSpacing requires a text target.'); requireSuccess(docAny.format.letterSpacing({ target, value: &lt;exaggerated&gt; }), operation);</t>
+          <t>Pending: no runnable script mapped for format.letterSpacing</t>
         </is>
       </c>
       <c r="H148" s="25" t="inlineStr">
         <is>
-          <t>DOCAPI_SOURCE="https://github.com/missysuperdoc/temp-doc-host/blob/main/Starting%20files/docapi-create-paragraph-output.docx" \
- DOCAPI_OPERATION="format.letterSpacing" \
- DOCAPI_EXAGGERATED_VISUAL=1 \
- DOCAPI_OUTPUT="/Users/missyresutko/Documents/Codex/Github/temp-doc-host/Output/format-letterSpacing-exaggerated-output.docx" \
- pnpm --dir /Users/missyresutko/Documents/Codex/Github/superdoc exec vitest run --root ./packages/super-editor ./packages/super-editor/src/tests/docapi-operations-harness.test.ts
- Output: https://github.com/missysuperdoc/temp-doc-host/blob/main/Output/format-letterSpacing-exaggerated-output.docx</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I148" s="25" t="inlineStr">
@@ -20153,7 +19968,7 @@
       <c r="L148" s="34" t="n"/>
       <c r="M148" s="25" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N148" s="32" t="n"/>

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Runs create.paragraph to apply a document change, then saves output DOCX for visual verification. Create a standalone paragraph at the target position. To add a list item, use lists.insert instead. Expected result: Returns a CreateParagraphResult with the new paragraph block ID and address.</t>
+          <t>Run create.paragraph. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Runs create.heading to apply a document change, then saves output DOCX for visual verification. Create a new heading at the target position. Expected result: Returns a CreateHeadingResult with the new heading block ID and address.</t>
+          <t>Run create.heading. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Runs create.table to apply a document change, then saves output DOCX for visual verification. Create a new table at the target position. Expected result: Returns a CreateTableResult with the new table block ID and address.</t>
+          <t>Run create.table. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Runs insert to apply a document change, then saves output DOCX for visual verification. Insert content into the document. Two input shapes: text-based (value + type) inserts inline content at a SelectionTarget or ref position within an existing block; structural SDFragment (content) inserts one or more blo... Expected result: Returns an SDMutationReceipt with applied status; resolution reports the inserted TextAddress for text insertion or a BlockNodeAddress for structural insertion. Receipt reports NO_OP if the insertion point is invalid or content is empty.</t>
+          <t>Run insert. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Runs lists.insert to apply a document change, then saves output DOCX for visual verification. Insert a new list item before or after an existing list item. The new item inherits the target list context. Expected result: Returns a ListsInsertResult with the new list item address and block ID.</t>
+          <t>Run lists.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Runs replace to apply a document change, then saves output DOCX for visual verification. Replace content at a contiguous document selection. Text path accepts a SelectionTarget or ref plus replacement text. Structural path accepts a BlockNodeAddress (replaces whole block), SelectionTarget (expands to full c... Expected result: Returns an SDMutationReceipt with applied status; receipt reports NO_OP if the target range already contains identical content.</t>
+          <t>Run replace. The targeted content should be replaced with the new content, in the same location.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Runs delete to apply a document change, then saves output DOCX for visual verification. Delete content at a contiguous document selection. Accepts a SelectionTarget or mutation-ready ref. Supports cross-block deletion and optional block-edge expansion via behavior mode. Expected result: Returns a TextMutationReceipt with applied status; receipt reports NO_OP if the target range is collapsed or empty.</t>
+          <t>Run delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Runs blocks.delete to apply a document change, then saves output DOCX for visual verification. Delete an entire block node (paragraph, heading, list item, table, image, or sdt) deterministically. Expected result: Returns a BlocksDeleteResult receipt confirming the block was removed, including a deletedBlock summary with ordinal, nodeType, and textPreview.</t>
+          <t>Run blocks.delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Runs format.apply to apply a document change, then saves output DOCX for visual verification. Apply inline run-property patch changes to the target range with explicit set/clear semantics. Expected result: Returns a TextMutationReceipt confirming inline styles were applied to the target range.</t>
+          <t>Run format.apply. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Runs format.fontSize to apply a document change, then saves output DOCX for visual verification. Set or clear the `fontSize` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.fontSize. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Runs format.fontFamily to apply a document change, then saves output DOCX for visual verification. Set or clear the `fontFamily` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.fontFamily. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Runs format.color to apply a document change, then saves output DOCX for visual verification. Set or clear the `color` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.color. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Runs comments.create to apply a document change, then saves output DOCX for visual verification. Create a new comment thread (or reply when parentCommentId is given). Expected result: Returns a Receipt confirming the comment was created; reports NO_OP if the anchor target is invalid.</t>
+          <t>Run comments.create. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Runs comments.patch to apply a document change, then saves output DOCX for visual verification. Patch fields on an existing comment (text, target, status, or isInternal). Expected result: Returns a Receipt confirming the comment was updated; reports NO_OP if no fields changed.</t>
+          <t>Run comments.patch. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Runs comments.delete to apply a document change, then saves output DOCX for visual verification. Remove a comment or reply by ID. Expected result: Returns a Receipt confirming the comment was removed; reports NO_OP if the comment was already deleted.</t>
+          <t>Run comments.delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Runs lists.setType to apply a document change, then saves output DOCX for visual verification. Convert a list to ordered or bullet and merge adjacent compatible sequences to preserve continuous numbering. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the list is already the requested kind and no sequences were merged.</t>
+          <t>Run lists.setType. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Runs lists.indent to apply a document change, then saves output DOCX for visual verification. Increase the indentation level of a list item. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the item is already at maximum indent level.</t>
+          <t>Run lists.indent. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Runs lists.outdent to apply a document change, then saves output DOCX for visual verification. Decrease the indentation level of a list item. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the item is already at the root level.</t>
+          <t>Run lists.outdent. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.insertRow to apply a document change, then saves output DOCX for visual verification. Insert a new row into the target table. Expected result: Returns a TableMutationResult receipt confirming a row was inserted.</t>
+          <t>Run tables.insertRow. A new row should appear adjacent to the targeted row (above or below based on input).</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.deleteRow to apply a document change, then saves output DOCX for visual verification. Delete a row from the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the target row does not exist.</t>
+          <t>Run tables.deleteRow. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.insertColumn to apply a document change, then saves output DOCX for visual verification. Insert a new column into the target table. Expected result: Returns a TableMutationResult receipt confirming a column was inserted.</t>
+          <t>Run tables.insertColumn. A new column should appear adjacent to the targeted column (left or right based on input).</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.deleteColumn to apply a document change, then saves output DOCX for visual verification. Delete a column from the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the target column does not exist.</t>
+          <t>Run tables.deleteColumn. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Runs format.bold to apply a document change, then saves output DOCX for visual verification. Set or clear the `bold` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.bold. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Runs format.italic to apply a document change, then saves output DOCX for visual verification. Set or clear the `italic` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.italic. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Runs format.underline to apply a document change, then saves output DOCX for visual verification. Set or clear the `underline` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.underline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.delete to apply a document change, then saves output DOCX for visual verification. Delete the target table from the document. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the table was already removed.</t>
+          <t>Run tables.delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.clearContents to apply a document change, then saves output DOCX for visual verification. Clear the contents of the target table or cell range. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the target cells are already empty.</t>
+          <t>Run tables.clearContents. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.split to apply a document change, then saves output DOCX for visual verification. Split a table into two tables at the target row. Expected result: Returns a TableMutationResult receipt confirming the table was split at the target row.</t>
+          <t>Run tables.split. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.convertToText to apply a document change, then saves output DOCX for visual verification. Convert a table back to plain text. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the table has no content to convert.</t>
+          <t>Run tables.convertToText. The targeted table should be replaced by plain text content at the same location.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setLayout to apply a document change, then saves output DOCX for visual verification. Set the layout mode of the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the table already uses the requested layout mode.</t>
+          <t>Run tables.setLayout. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setRowHeight to apply a document change, then saves output DOCX for visual verification. Set the height of a table row. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the row height already matches.</t>
+          <t>Run tables.setRowHeight. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.distributeRows to apply a document change, then saves output DOCX for visual verification. Distribute row heights evenly across the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if row heights are already equal.</t>
+          <t>Run tables.distributeRows. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setRowOptions to apply a document change, then saves output DOCX for visual verification. Set options on a table row such as header repeat or page break. Expected result: Returns a TableMutationResult receipt; reports NO_OP if row options already match.</t>
+          <t>Run tables.setRowOptions. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setColumnWidth to apply a document change, then saves output DOCX for visual verification. Set the width of a table column. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the column width already matches.</t>
+          <t>Run tables.setColumnWidth. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.distributeColumns to apply a document change, then saves output DOCX for visual verification. Distribute column widths evenly across the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if column widths are already equal.</t>
+          <t>Run tables.distributeColumns. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.insertCell to apply a document change, then saves output DOCX for visual verification. Insert a new cell into a table row. Expected result: Returns a TableMutationResult receipt confirming a cell was inserted.</t>
+          <t>Run tables.insertCell. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.deleteCell to apply a document change, then saves output DOCX for visual verification. Delete a cell from a table row. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the target cell does not exist.</t>
+          <t>Run tables.deleteCell. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.mergeCells to apply a document change, then saves output DOCX for visual verification. Merge a range of table cells into one. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the cells are already merged.</t>
+          <t>Run tables.mergeCells. The selected neighboring cells should become one merged cell containing combined content.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.unmergeCells to apply a document change, then saves output DOCX for visual verification. Unmerge a previously merged table cell. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the cell is not merged.</t>
+          <t>Run tables.unmergeCells. The targeted merged cell should split into multiple cells.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.splitCell to apply a document change, then saves output DOCX for visual verification. Split a table cell into multiple cells. Expected result: Returns a TableMutationResult receipt confirming the cell was split.</t>
+          <t>Run tables.splitCell. The targeted merged cell should split into multiple cells.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setCellProperties to apply a document change, then saves output DOCX for visual verification. Set properties on a table cell such as vertical alignment or text direction. Expected result: Returns a TableMutationResult receipt; reports NO_OP if cell properties already match.</t>
+          <t>Run tables.setCellProperties. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.sort to apply a document change, then saves output DOCX for visual verification. Sort table rows by a column value. Expected result: Returns a TableMutationResult receipt confirming rows were reordered.</t>
+          <t>Run tables.sort. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setAltText to apply a document change, then saves output DOCX for visual verification. Set the alternative text description for a table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if alt text already matches.</t>
+          <t>Run tables.setAltText. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setStyle to apply a document change, then saves output DOCX for visual verification. Apply a named table style to the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the table already uses the requested style.</t>
+          <t>Run tables.setStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.clearStyle to apply a document change, then saves output DOCX for visual verification. Remove the applied table style, reverting to defaults. Expected result: Returns a TableMutationResult receipt; reports NO_OP if no table style is applied.</t>
+          <t>Run tables.clearStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setStyleOption to apply a document change, then saves output DOCX for visual verification. Toggle a conditional style option such as banded rows or first column. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the style option already matches.</t>
+          <t>Run tables.setStyleOption. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setBorder to apply a document change, then saves output DOCX for visual verification. Set border properties on a table or cell range. Expected result: Returns a TableMutationResult receipt; reports NO_OP if border properties already match.</t>
+          <t>Run tables.setBorder. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.clearBorder to apply a document change, then saves output DOCX for visual verification. Remove border formatting from a table or cell range. Expected result: Returns a TableMutationResult receipt; reports NO_OP if no borders are set.</t>
+          <t>Run tables.clearBorder. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.applyBorderPreset to apply a document change, then saves output DOCX for visual verification. Apply a border preset (e.g. all borders, outside only) to a table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the preset is already applied.</t>
+          <t>Run tables.applyBorderPreset. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setShading to apply a document change, then saves output DOCX for visual verification. Set the background shading color on a table or cell range. Expected result: Returns a TableMutationResult receipt; reports NO_OP if shading already matches.</t>
+          <t>Run tables.setShading. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.clearShading to apply a document change, then saves output DOCX for visual verification. Remove shading from a table or cell range. Expected result: Returns a TableMutationResult receipt; reports NO_OP if no shading is set.</t>
+          <t>Run tables.clearShading. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setTablePadding to apply a document change, then saves output DOCX for visual verification. Set default cell padding for the entire table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if table padding already matches.</t>
+          <t>Run tables.setTablePadding. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setCellPadding to apply a document change, then saves output DOCX for visual verification. Set padding on a specific table cell or cell range. Expected result: Returns a TableMutationResult receipt; reports NO_OP if cell padding already matches.</t>
+          <t>Run tables.setCellPadding. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.setCellSpacing to apply a document change, then saves output DOCX for visual verification. Set the cell spacing for the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if cell spacing already matches.</t>
+          <t>Run tables.setCellSpacing. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Runs tables.clearCellSpacing to apply a document change, then saves output DOCX for visual verification. Remove custom cell spacing from the target table. Expected result: Returns a TableMutationResult receipt; reports NO_OP if no custom cell spacing is set.</t>
+          <t>Run tables.clearCellSpacing. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Runs mutations.apply to apply a document change, then saves output DOCX for visual verification. Execute a mutation plan atomically against the document. Expected result: Returns a PlanReceipt with per-step results for the atomically applied mutation plan.</t>
+          <t>Run mutations.apply. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Runs tables.convertFromText to apply a document change, then saves output DOCX for visual verification. Convert a text range into a table. Expected result: Returns a TableMutationResult receipt confirming text was converted into a table.</t>
+          <t>Run tables.convertFromText. The selected plain text should become a table. The same information should now be arranged in table cells.</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t>Runs tables.move to apply a document change, then saves output DOCX for visual verification. Move a table to a new position in the document. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the table is already at the target position.</t>
+          <t>Run tables.move. The targeted content should be moved from its original location to the requested location (for example, below/after the reference content). It should no longer appear at the old location.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>Runs create.sectionBreak to apply a document change, then saves output DOCX for visual verification. Create a section break at the target location with optional initial section properties. Expected result: Returns a CreateSectionBreakResult with the new section break position and section address.</t>
+          <t>Run create.sectionBreak. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>Runs create.tableOfContents to apply a document change, then saves output DOCX for visual verification. Insert a new table of contents at the target position. Expected result: Returns a CreateTableOfContentsResult with the new TOC block address.</t>
+          <t>Run create.tableOfContents. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.clearHeaderFooterRef to apply a document change, then saves output DOCX for visual verification. Clear a section header/footer reference for a specific variant. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if no reference exists for the specified variant.</t>
+          <t>Run sections.clearHeaderFooterRef. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.clearPageBorders to apply a document change, then saves output DOCX for visual verification. Clear page border configuration for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if no page borders are configured on the section.</t>
+          <t>Run sections.clearPageBorders. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setBreakType to apply a document change, then saves output DOCX for visual verification. Set the section break type. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if the section already has the requested break type.</t>
+          <t>Run sections.setBreakType. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setColumns to apply a document change, then saves output DOCX for visual verification. Set column configuration for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if column configuration already matches.</t>
+          <t>Run sections.setColumns. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setHeaderFooterMargins to apply a document change, then saves output DOCX for visual verification. Set header/footer margin distances for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if header/footer margins already match the requested values.</t>
+          <t>Run sections.setHeaderFooterMargins. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setHeaderFooterRef to apply a document change, then saves output DOCX for visual verification. Set or replace a section header/footer reference for a variant. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if the header/footer reference already matches.</t>
+          <t>Run sections.setHeaderFooterRef. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setLineNumbering to apply a document change, then saves output DOCX for visual verification. Enable or configure line numbering for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if line numbering settings already match.</t>
+          <t>Run sections.setLineNumbering. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setLinkToPrevious to apply a document change, then saves output DOCX for visual verification. Set or clear link-to-previous behavior for a header/footer variant. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if link-to-previous already matches the requested value.</t>
+          <t>Run sections.setLinkToPrevious. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setOddEvenHeadersFooters to apply a document change, then saves output DOCX for visual verification. Enable or disable odd/even header-footer mode in document settings. Expected result: Returns a DocumentMutationResult (not SectionMutationResult) because odd/even headers-footers is a document-level setting, not per-section. Reports NO_OP if the setting already matches.</t>
+          <t>Run sections.setOddEvenHeadersFooters. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setPageBorders to apply a document change, then saves output DOCX for visual verification. Set page border configuration for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if page border configuration already matches.</t>
+          <t>Run sections.setPageBorders. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setPageMargins to apply a document change, then saves output DOCX for visual verification. Set page-edge margins for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if margins already match the requested values.</t>
+          <t>Run sections.setPageMargins. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G101" s="22" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setPageNumbering to apply a document change, then saves output DOCX for visual verification. Set page numbering format/start for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if page numbering format already matches.</t>
+          <t>Run sections.setPageNumbering. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setPageSetup to apply a document change, then saves output DOCX for visual verification. Set page size/orientation properties for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if page size and orientation already match the requested values.</t>
+          <t>Run sections.setPageSetup. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G103" s="22" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setSectionDirection to apply a document change, then saves output DOCX for visual verification. Set section text flow direction (LTR/RTL). Expected result: Returns a SectionMutationResult receipt; reports NO_OP if text direction already matches.</t>
+          <t>Run sections.setSectionDirection. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setTitlePage to apply a document change, then saves output DOCX for visual verification. Enable or disable title-page behavior for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if the title-page setting already matches.</t>
+          <t>Run sections.setTitlePage. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G105" s="22" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t>Runs sections.setVerticalAlign to apply a document change, then saves output DOCX for visual verification. Set vertical page alignment for a section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if vertical alignment already matches.</t>
+          <t>Run sections.setVerticalAlign. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>Runs toc.configure to apply a document change, then saves output DOCX for visual verification. Update the configuration switches of a table of contents. Expected result: Returns a TocMutationResult with the updated TOC address on success, or a failure code on no-op.</t>
+          <t>Run toc.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G107" s="22" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t>Runs toc.remove to apply a document change, then saves output DOCX for visual verification. Remove a table of contents from the document. Expected result: Returns a TocMutationResult with the removed TOC address on success, or a failure code on no-op.</t>
+          <t>Run toc.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>Runs toc.update to apply a document change, then saves output DOCX for visual verification. Rebuild or refresh the materialized content of a table of contents. Expected result: Returns a TocMutationResult with the TOC address on success, or a failure code if content is unchanged or page numbers cannot be resolved.</t>
+          <t>Run toc.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G111" s="22" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Runs format.strike to apply a document change, then saves output DOCX for visual verification. Set or clear the `strike` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.strike. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Runs format.highlight to apply a document change, then saves output DOCX for visual verification. Set or clear the `highlight` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.highlight. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>Runs format.shading to apply a document change, then saves output DOCX for visual verification. Set or clear the `shading` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.shading. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G114" s="25" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>Runs format.border to apply a document change, then saves output DOCX for visual verification. Set or clear the `border` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.border. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G115" s="25" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F116" s="25" t="inlineStr">
         <is>
-          <t>Runs format.outline to apply a document change, then saves output DOCX for visual verification. Set or clear the `outline` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.outline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G116" s="25" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="F117" s="25" t="inlineStr">
         <is>
-          <t>Runs format.shadow to apply a document change, then saves output DOCX for visual verification. Set or clear the `shadow` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.shadow. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G117" s="25" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>Runs format.emboss to apply a document change, then saves output DOCX for visual verification. Set or clear the `emboss` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.emboss. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G118" s="25" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>Runs format.imprint to apply a document change, then saves output DOCX for visual verification. Set or clear the `imprint` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.imprint. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F120" s="25" t="inlineStr">
         <is>
-          <t>Runs format.vertAlign to apply a document change, then saves output DOCX for visual verification. Set or clear the `vertAlign` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.vertAlign. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G120" s="25" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="F121" s="25" t="inlineStr">
         <is>
-          <t>Runs format.position to apply a document change, then saves output DOCX for visual verification. Set or clear the `position` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.position. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G121" s="25" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>Runs format.rtl to apply a document change, then saves output DOCX for visual verification. Set or clear the `rtl` inline run property on the target text range. This does not change paragraph direction; use `format.paragraph.setDirection` for paragraph-level RTL. Expected result: Returns a TextMutationReceipt confirming only the inline run property patch was applied to the target range; paragraph direction is unchanged.</t>
+          <t>Run format.rtl. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F123" s="25" t="inlineStr">
         <is>
-          <t>Runs format.cs to apply a document change, then saves output DOCX for visual verification. Set or clear the `cs` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.cs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G123" s="25" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F124" s="25" t="inlineStr">
         <is>
-          <t>Runs format.bCs to apply a document change, then saves output DOCX for visual verification. Set or clear the `bCs` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.bCs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G124" s="25" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="F125" s="25" t="inlineStr">
         <is>
-          <t>Runs format.iCs to apply a document change, then saves output DOCX for visual verification. Set or clear the `iCs` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.iCs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G125" s="25" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="F126" s="25" t="inlineStr">
         <is>
-          <t>Runs format.vanish to apply a document change, then saves output DOCX for visual verification. Set or clear the `vanish` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.vanish. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G126" s="25" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="F127" s="25" t="inlineStr">
         <is>
-          <t>Runs format.webHidden to apply a document change, then saves output DOCX for visual verification. Set or clear the `webHidden` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.webHidden. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G127" s="25" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>Runs format.specVanish to apply a document change, then saves output DOCX for visual verification. Set or clear the `specVanish` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.specVanish. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>Runs format.snapToGrid to apply a document change, then saves output DOCX for visual verification. Set or clear the `snapToGrid` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.snapToGrid. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G129" s="25" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="F130" s="25" t="inlineStr">
         <is>
-          <t>Runs format.oMath to apply a document change, then saves output DOCX for visual verification. Set or clear the `oMath` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.oMath. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G130" s="25" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
-          <t>Runs format.fontSizeCs to apply a document change, then saves output DOCX for visual verification. Set or clear the `fontSizeCs` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.fontSizeCs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G131" s="25" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>Runs format.charScale to apply a document change, then saves output DOCX for visual verification. Set or clear the `charScale` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.charScale. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G132" s="25" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>Runs format.kerning to apply a document change, then saves output DOCX for visual verification. Set or clear the `kerning` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.kerning. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G133" s="25" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>Runs format.fitText to apply a document change, then saves output DOCX for visual verification. Set or clear the `fitText` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.fitText. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>Runs format.lang to apply a document change, then saves output DOCX for visual verification. Set or clear the `lang` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.lang. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G135" s="25" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>Runs format.rStyle to apply a document change, then saves output DOCX for visual verification. Set or clear the `rStyle` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.rStyle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>Runs format.rFonts to apply a document change, then saves output DOCX for visual verification. Set or clear the `rFonts` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.rFonts. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G137" s="25" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>Runs format.eastAsianLayout to apply a document change, then saves output DOCX for visual verification. Set or clear the `eastAsianLayout` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.eastAsianLayout. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G138" s="25" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>Runs format.em to apply a document change, then saves output DOCX for visual verification. Set or clear the `em` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.em. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G139" s="25" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>Runs format.ligatures to apply a document change, then saves output DOCX for visual verification. Set or clear the `ligatures` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.ligatures. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G140" s="25" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="F141" s="25" t="inlineStr">
         <is>
-          <t>Runs format.numForm to apply a document change, then saves output DOCX for visual verification. Set or clear the `numForm` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.numForm. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G141" s="25" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>Runs format.numSpacing to apply a document change, then saves output DOCX for visual verification. Set or clear the `numSpacing` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.numSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G142" s="25" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F143" s="25" t="inlineStr">
         <is>
-          <t>Runs format.stylisticSets to apply a document change, then saves output DOCX for visual verification. Set or clear the `stylisticSets` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.stylisticSets. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G143" s="25" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>Runs format.contextualAlternates to apply a document change, then saves output DOCX for visual verification. Set or clear the `contextualAlternates` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.contextualAlternates. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G144" s="25" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="F145" s="25" t="inlineStr">
         <is>
-          <t>Runs format.dstrike to apply a document change, then saves output DOCX for visual verification. Set or clear the `dstrike` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.dstrike. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G145" s="25" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="F146" s="25" t="inlineStr">
         <is>
-          <t>Runs format.smallCaps to apply a document change, then saves output DOCX for visual verification. Set or clear the `smallCaps` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.smallCaps. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G146" s="25" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="F147" s="25" t="inlineStr">
         <is>
-          <t>Runs format.caps to apply a document change, then saves output DOCX for visual verification. Set or clear the `caps` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.caps. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G147" s="25" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="F148" s="25" t="inlineStr">
         <is>
-          <t>Runs format.letterSpacing to apply a document change, then saves output DOCX for visual verification. Set or clear the `letterSpacing` inline run property on the target text range. Expected result: Returns a TextMutationReceipt confirming the inline run property patch was applied to the target range.</t>
+          <t>Run format.letterSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G148" s="25" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="F152" s="25" t="inlineStr">
         <is>
-          <t>Runs styles.paragraph.setStyle to apply a document change, then saves output DOCX for visual verification. Apply a paragraph style (w:pStyle) to a paragraph-like block, clearing direct run formatting while preserving character-style references. Expected result: Returns a ParagraphMutationResult; reports NO_OP if the style already matches. When the style changes, direct run formatting is cleared while character-style references are preserved.</t>
+          <t>Run styles.paragraph.setStyle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G152" s="25" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="F153" s="25" t="inlineStr">
         <is>
-          <t>Runs styles.paragraph.clearStyle to apply a document change, then saves output DOCX for visual verification. Remove the paragraph style reference from a paragraph-like block. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no style is set.</t>
+          <t>Run styles.paragraph.clearStyle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G153" s="25" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F154" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.resetDirectFormatting to apply a document change, then saves output DOCX for visual verification. Strip all direct paragraph formatting while preserving style reference, numbering, and section metadata. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no direct formatting is present.</t>
+          <t>Run format.paragraph.resetDirectFormatting. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G154" s="25" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="F155" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setAlignment to apply a document change, then saves output DOCX for visual verification. Set paragraph alignment (justification) on a paragraph-like block. Expected result: Returns a ParagraphMutationResult; reports NO_OP if the alignment already matches.</t>
+          <t>Run format.paragraph.setAlignment. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G155" s="25" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="F156" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearAlignment to apply a document change, then saves output DOCX for visual verification. Remove direct paragraph alignment, reverting to style-defined or default alignment. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no direct alignment is set.</t>
+          <t>Run format.paragraph.clearAlignment. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G156" s="25" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setIndentation to apply a document change, then saves output DOCX for visual verification. Set paragraph indentation properties (left, right, firstLine, hanging) in twips. Expected result: Returns a ParagraphMutationResult; reports NO_OP if indentation already matches.</t>
+          <t>Run format.paragraph.setIndentation. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G157" s="25" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="F158" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearIndentation to apply a document change, then saves output DOCX for visual verification. Remove all direct paragraph indentation. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no direct indentation is set.</t>
+          <t>Run format.paragraph.clearIndentation. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G158" s="25" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F159" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setSpacing to apply a document change, then saves output DOCX for visual verification. Set paragraph spacing properties (before, after, line, lineRule) in twips. Expected result: Returns a ParagraphMutationResult; reports NO_OP if spacing already matches.</t>
+          <t>Run format.paragraph.setSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G159" s="25" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="F160" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearSpacing to apply a document change, then saves output DOCX for visual verification. Remove all direct paragraph spacing. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no direct spacing is set.</t>
+          <t>Run format.paragraph.clearSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G160" s="25" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F161" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setKeepOptions to apply a document change, then saves output DOCX for visual verification. Set keep-with-next, keep-lines-together, and widow/orphan control flags. Expected result: Returns a ParagraphMutationResult; reports NO_OP if all flags already match.</t>
+          <t>Run format.paragraph.setKeepOptions. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G161" s="25" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setOutlineLevel to apply a document change, then saves output DOCX for visual verification. Set the paragraph outline level (0–9) or null to clear. Expected result: Returns a ParagraphMutationResult; reports NO_OP if outline level already matches.</t>
+          <t>Run format.paragraph.setOutlineLevel. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G162" s="25" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="F163" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setFlowOptions to apply a document change, then saves output DOCX for visual verification. Set contextual spacing, page-break-before, and suppress-auto-hyphens flags. Expected result: Returns a ParagraphMutationResult; reports NO_OP if all flags already match.</t>
+          <t>Run format.paragraph.setFlowOptions. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G163" s="25" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="F164" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setTabStop to apply a document change, then saves output DOCX for visual verification. Add or replace a tab stop at a given position. Expected result: Returns a ParagraphMutationResult; reports NO_OP if an identical tab stop already exists.</t>
+          <t>Run format.paragraph.setTabStop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G164" s="25" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F165" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearTabStop to apply a document change, then saves output DOCX for visual verification. Remove a tab stop at a given position. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no tab stop exists at that position.</t>
+          <t>Run format.paragraph.clearTabStop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G165" s="25" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F166" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearAllTabStops to apply a document change, then saves output DOCX for visual verification. Remove all tab stops from a paragraph. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no tab stops exist.</t>
+          <t>Run format.paragraph.clearAllTabStops. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G166" s="25" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F167" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setBorder to apply a document change, then saves output DOCX for visual verification. Set border properties for a specific side of a paragraph. Expected result: Returns a ParagraphMutationResult; reports NO_OP if the border already matches.</t>
+          <t>Run format.paragraph.setBorder. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G167" s="25" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearBorder to apply a document change, then saves output DOCX for visual verification. Remove border for a specific side or all sides of a paragraph. Expected result: Returns a ParagraphMutationResult; reports NO_OP if the border is already absent.</t>
+          <t>Run format.paragraph.clearBorder. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G168" s="25" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setShading to apply a document change, then saves output DOCX for visual verification. Set paragraph shading (background fill, pattern color, pattern type). Expected result: Returns a ParagraphMutationResult; reports NO_OP if the shading already matches.</t>
+          <t>Run format.paragraph.setShading. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G169" s="25" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F170" s="25" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearShading to apply a document change, then saves output DOCX for visual verification. Remove all paragraph shading. Expected result: Returns a ParagraphMutationResult; reports NO_OP if no shading is set.</t>
+          <t>Run format.paragraph.clearShading. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G170" s="25" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.create to apply a document change, then saves output DOCX for visual verification. Create a new list from one or more paragraphs. Supports optional preset or style for new sequences. When sequence.mode is "continuePrevious", preset and style are not allowed — the new items inherit formatting from the... Expected result: Returns a ListsCreateResult with the new listId and the first item address.</t>
+          <t>Run lists.create. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G171" s="25" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.attach to apply a document change, then saves output DOCX for visual verification. Convert non-list paragraphs to list items under an existing list sequence. Expected result: Returns a ListsMutateItemResult confirming attachment.</t>
+          <t>Run lists.attach. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G172" s="25" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.detach to apply a document change, then saves output DOCX for visual verification. Remove numbering properties from list items, converting them to plain paragraphs. Expected result: Returns a ListsDetachResult confirming the item was converted to a plain paragraph.</t>
+          <t>Run lists.detach. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G173" s="25" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.join to apply a document change, then saves output DOCX for visual verification. Merge two adjacent list sequences into one. Expected result: Returns a ListsJoinResult with the resulting listId of the merged sequence.</t>
+          <t>Run lists.join. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G174" s="25" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.separate to apply a document change, then saves output DOCX for visual verification. Split a list sequence at the target item, creating a new sequence from that point forward. Expected result: Returns a ListsSeparateResult with the new listId and numId.</t>
+          <t>Run lists.separate. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G176" s="25" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.setLevel to apply a document change, then saves output DOCX for visual verification. Set the absolute nesting level (0..8) of a list item. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if already at the target level.</t>
+          <t>Run lists.setLevel. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G177" s="25" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.setValue to apply a document change, then saves output DOCX for visual verification. Set an explicit numbering value at the target item. Mid-sequence targets are atomically separated first. Expected result: Returns a ListsMutateItemResult receipt.</t>
+          <t>Run lists.setValue. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G178" s="25" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.continuePrevious to apply a document change, then saves output DOCX for visual verification. Continue numbering from the nearest compatible previous list sequence. Expected result: Returns a ListsMutateItemResult receipt.</t>
+          <t>Run lists.continuePrevious. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G179" s="25" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelRestart to apply a document change, then saves output DOCX for visual verification. Set the restart behavior for a specific list level. Expected result: Returns a ListsMutateItemResult receipt.</t>
+          <t>Run lists.setLevelRestart. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G181" s="25" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>Runs lists.convertToText to apply a document change, then saves output DOCX for visual verification. Convert list items to plain paragraphs, optionally prepending the rendered marker text. Expected result: Returns a ListsConvertToTextResult confirming the conversion.</t>
+          <t>Run lists.convertToText. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G182" s="25" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>Runs tables.setDefaultStyle to apply a document change, then saves output DOCX for visual verification. Set the document-level default table style (w:defaultTableStyle in settings.xml). Expected result: Returns a DocumentMutationResult; reports NO_OP if the default already matches.</t>
+          <t>Run tables.setDefaultStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G184" s="25" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>Runs tables.clearDefaultStyle to apply a document change, then saves output DOCX for visual verification. Remove the document-level default table style setting. Expected result: Returns a DocumentMutationResult; reports NO_OP if no default is set.</t>
+          <t>Run tables.clearDefaultStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G185" s="25" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>Runs toc.markEntry to apply a document change, then saves output DOCX for visual verification. Insert a TC (table of contents entry) field at the target paragraph. Expected result: Returns a TocEntryMutationResult with the created entry address on success.</t>
+          <t>Run toc.markEntry. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G186" s="25" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>Runs toc.unmarkEntry to apply a document change, then saves output DOCX for visual verification. Remove a TC (table of contents entry) field from the document. Expected result: Returns a TocEntryMutationResult with the removed entry address on success.</t>
+          <t>Run toc.unmarkEntry. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G187" s="25" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>Runs toc.listEntries and returns structured data only. DOCX should remain visually unchanged. Returns a TocListEntriesResult with an array of TC entry discovery items and pagination metadata.</t>
+          <t>Run toc.listEntries. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G188" s="25" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F189" s="25" t="inlineStr">
         <is>
-          <t>Runs toc.getEntry and returns structured data only. DOCX should remain visually unchanged. Returns a TocEntryInfo object with the instruction, text, level, and switch configuration.</t>
+          <t>Run toc.getEntry. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G189" s="25" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>Runs toc.editEntry to apply a document change, then saves output DOCX for visual verification. Update the properties of a TC (table of contents entry) field. Expected result: Returns a TocEntryMutationResult with the updated entry address on success, or NO_OP if no change.</t>
+          <t>Run toc.editEntry. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G190" s="25" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="F192" s="25" t="inlineStr">
         <is>
-          <t>Runs history.undo to apply a document change, then saves output DOCX for visual verification. Undo the most recent history-safe mutation in the active editor. Expected result: Returns a HistoryActionResult with noop flag, reason (EMPTY_UNDO_STACK | NO_EFFECT when noop), and revision before/after.</t>
+          <t>Run history.undo. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G192" s="25" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>Runs history.redo to apply a document change, then saves output DOCX for visual verification. Redo the most recently undone action in the active editor. Expected result: Returns a HistoryActionResult with noop flag, reason (EMPTY_REDO_STACK | NO_EFFECT when noop), and revision before/after.</t>
+          <t>Run history.redo. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G193" s="25" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Runs styles.apply to apply a document change, then saves output DOCX for visual verification. Apply document-level default style changes to the stylesheet (word/styles.xml). Targets docDefaults run and paragraph channels with set-style patch semantics. Expected result: Returns a StylesApplyReceipt with per-channel success/failure details for each property change.</t>
+          <t>Run styles.apply. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Runs trackChanges.decide to apply a document change, then saves output DOCX for visual verification. Accept or reject a tracked change (by ID or scope: all). Expected result: Returns a Receipt confirming the decision was applied; reports NO_OP if the change was already resolved.</t>
+          <t>Run trackChanges.decide. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Runs get and returns structured data only. DOCX should remain visually unchanged. Returns an SDDocument with body content projected into SDM/1 canonical shapes.</t>
+          <t>Run get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Runs markdownToFragment and returns structured data only. DOCX should remain visually unchanged. Returns an SDMarkdownToFragmentResult with the converted fragment, lossy flag, and diagnostics.</t>
+          <t>Run markdownToFragment. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Runs clearContent to apply a document change, then saves output DOCX for visual verification. Clear all document body content, leaving a single empty paragraph. Expected result: Returns a Receipt with success status; reports NO_OP if the document is already empty.</t>
+          <t>Run clearContent. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Runs blocks.list and returns structured data only. DOCX should remain visually unchanged. Returns a BlocksListResult with total block count, an ordered array of block entries (ordinal, nodeId, nodeType, textPreview, isEmpty), and the current document revision.</t>
+          <t>Run blocks.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Runs blocks.deleteRange to apply a document change, then saves output DOCX for visual verification. Delete a contiguous range of top-level blocks between two endpoints (inclusive). Both endpoints must be direct children of the document node. Supports dry-run preview. Expected result: Returns a BlocksDeleteRangeResult with deletedCount, deletedBlocks array (each with ordinal, nodeId, nodeType, textPreview), before/after revision, and dryRun flag.</t>
+          <t>Run blocks.deleteRange. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.setDirection to apply a document change, then saves output DOCX for visual verification. Set paragraph base direction (LTR or RTL via w:bidi). Optionally align text to match. Expected result: Returns a ParagraphMutationResult; reports NO_OP if the direction already matches.</t>
+          <t>Run format.paragraph.setDirection. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>Runs format.paragraph.clearDirection to apply a document change, then saves output DOCX for visual verification. Remove explicit paragraph direction, reverting to inherited or default (LTR). Expected result: Returns a ParagraphMutationResult; reports NO_OP if no direction is set.</t>
+          <t>Run format.paragraph.clearDirection. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.applyTemplate to apply a document change, then saves output DOCX for visual verification. Advanced alias for lists.applyStyle. Apply a captured ListTemplate to the target list (abstract-scoped, no clone-on-write). Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if all levels already match.</t>
+          <t>Run lists.applyTemplate. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.applyPreset to apply a document change, then saves output DOCX for visual verification. Apply a built-in list formatting preset to the target list. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if all levels already match the preset.</t>
+          <t>Run lists.applyPreset. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.captureTemplate and returns structured data only. DOCX should remain visually unchanged. Returns a ListsCaptureTemplateResult containing the captured template.</t>
+          <t>Run lists.captureTemplate. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelNumbering to apply a document change, then saves output DOCX for visual verification. Advanced alias for lists.setLevelNumberStyle/setLevelText/setLevelStart. Set format, pattern, and start in one call (abstract-scoped, no clone-on-write). Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the level already matches.</t>
+          <t>Run lists.setLevelNumbering. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelBullet to apply a document change, then saves output DOCX for visual verification. Set the bullet marker text for a specific list level. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the marker already matches.</t>
+          <t>Run lists.setLevelBullet. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelPictureBullet to apply a document change, then saves output DOCX for visual verification. Set a picture bullet for a specific list level by its OOXML lvlPicBulletId. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the picture bullet already matches.</t>
+          <t>Run lists.setLevelPictureBullet. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelAlignment to apply a document change, then saves output DOCX for visual verification. Set the marker alignment (left, center, right) for a specific list level. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the alignment already matches.</t>
+          <t>Run lists.setLevelAlignment. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelIndents to apply a document change, then saves output DOCX for visual verification. Set the paragraph indentation values (left, hanging, firstLine) for a specific list level. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if all indent values already match.</t>
+          <t>Run lists.setLevelIndents. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelTrailingCharacter to apply a document change, then saves output DOCX for visual verification. Set the trailing character (tab, space, nothing) after the marker for a specific list level. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the trailing character already matches.</t>
+          <t>Run lists.setLevelTrailingCharacter. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelMarkerFont to apply a document change, then saves output DOCX for visual verification. Set the font family used for the marker character at a specific list level. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the font already matches.</t>
+          <t>Run lists.setLevelMarkerFont. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.clearLevelOverrides to apply a document change, then saves output DOCX for visual verification. Remove instance-level overrides for a specific list level, restoring abstract definition values. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if no override exists.</t>
+          <t>Run lists.clearLevelOverrides. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.getStyle and returns structured data only. DOCX should remain visually unchanged. Returns a ListsGetStyleResult containing the captured style.</t>
+          <t>Run lists.getStyle. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.applyStyle to apply a document change, then saves output DOCX for visual verification. Apply a reusable list style to the target list. Sequence-local: if the abstract definition is shared with other lists, it is cloned first to avoid affecting them. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if all levels already match.</t>
+          <t>Run lists.applyStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.restartAt to apply a document change, then saves output DOCX for visual verification. Restart numbering at the target list item with a specific value. If the item is mid-sequence, it is separated first. Expected result: Returns a ListsMutateItemResult receipt.</t>
+          <t>Run lists.restartAt. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelNumberStyle to apply a document change, then saves output DOCX for visual verification. Set the numbering style (e.g. decimal, lowerLetter, upperRoman) for a specific list level. Rejects "bullet" — use setLevelBullet instead. Sequence-local: clones shared definitions. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the value already matches.</t>
+          <t>Run lists.setLevelNumberStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelText to apply a document change, then saves output DOCX for visual verification. Set the level text pattern (e.g. "%1.", "(%1)") for a specific list level. Uses OOXML level-placeholder syntax. Sequence-local: clones shared definitions. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the value already matches.</t>
+          <t>Run lists.setLevelText. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelStart to apply a document change, then saves output DOCX for visual verification. Set the start value for a specific list level. Rejects bullet levels and non-positive values. Sequence-local: clones shared definitions. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if the value already matches.</t>
+          <t>Run lists.setLevelStart. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Runs lists.setLevelLayout to apply a document change, then saves output DOCX for visual verification. Set the layout properties (alignment, indentation, trailing character, tab stop) for a specific list level. Accepts partial updates — omitted fields are left unchanged. Sequence-local: clones shared definitions. Expected result: Returns a ListsMutateItemResult receipt; reports NO_OP if all values already match.</t>
+          <t>Run lists.setLevelLayout. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Runs ranges.resolve and returns structured data only. DOCX should remain visually unchanged. Returns a ResolveRangeOutput with evaluatedRevision, handle.ref, target (SelectionTarget), and preview metadata.</t>
+          <t>Run ranges.resolve. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Runs tables.applyStyle to apply a document change, then saves output DOCX for visual verification. Apply a table style and/or style options in one call. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the style and all provided options already match.</t>
+          <t>Run tables.applyStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Runs tables.setBorders to apply a document change, then saves output DOCX for visual verification. Set borders on a table using a target set or per-edge patch. Expected result: Returns a TableMutationResult receipt. Does not perform NO_OP detection.</t>
+          <t>Run tables.setBorders. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Runs tables.setTableOptions to apply a document change, then saves output DOCX for visual verification. Set table-level default cell margins and/or cell spacing. Expected result: Returns a TableMutationResult receipt; reports NO_OP if the provided values already match current direct formatting.</t>
+          <t>Run tables.setTableOptions. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Runs create.image to apply a document change, then saves output DOCX for visual verification. Insert a new image at the target position. Expected result: Returns a CreateImageResult with the new image address.</t>
+          <t>Run create.image. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Runs images.list and returns structured data only. DOCX should remain visually unchanged. Returns an ImagesListResult with total count and image summaries.</t>
+          <t>Run images.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Runs images.get and returns structured data only. DOCX should remain visually unchanged. Returns an ImageSummary with full image properties.</t>
+          <t>Run images.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Runs images.delete to apply a document change, then saves output DOCX for visual verification. Delete an image from the document. Expected result: Returns an ImagesMutationResult indicating success or failure.</t>
+          <t>Run images.delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>Runs images.move to apply a document change, then saves output DOCX for visual verification. Move an image to a new location in the document. Expected result: Returns an ImagesMutationResult indicating success or failure.</t>
+          <t>Run images.move. The targeted content should be moved from its original location to the requested location (for example, below/after the reference content). It should no longer appear at the old location.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Runs images.convertToInline to apply a document change, then saves output DOCX for visual verification. Convert a floating image to inline placement. Expected result: Returns an ImagesMutationResult; reports NO_OP if already inline.</t>
+          <t>Run images.convertToInline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Runs images.convertToFloating to apply a document change, then saves output DOCX for visual verification. Convert an inline image to floating placement. Expected result: Returns an ImagesMutationResult; reports NO_OP if already floating.</t>
+          <t>Run images.convertToFloating. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setSize to apply a document change, then saves output DOCX for visual verification. Set explicit width/height for an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if the size already matches.</t>
+          <t>Run images.setSize. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setWrapType to apply a document change, then saves output DOCX for visual verification. Set the text wrapping type for a floating image. Expected result: Returns an ImagesMutationResult; reports NO_OP if already set.</t>
+          <t>Run images.setWrapType. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setWrapSide to apply a document change, then saves output DOCX for visual verification. Set which side(s) text wraps around a floating image. Expected result: Returns an ImagesMutationResult; reports NO_OP if already set.</t>
+          <t>Run images.setWrapSide. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setWrapDistances to apply a document change, then saves output DOCX for visual verification. Set the text-wrap distance margins for a floating image. Expected result: Returns an ImagesMutationResult; reports NO_OP if already set.</t>
+          <t>Run images.setWrapDistances. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setPosition to apply a document change, then saves output DOCX for visual verification. Set the anchor position for a floating image. Expected result: Returns an ImagesMutationResult.</t>
+          <t>Run images.setPosition. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setAnchorOptions to apply a document change, then saves output DOCX for visual verification. Set anchor behavior options for a floating image. Expected result: Returns an ImagesMutationResult.</t>
+          <t>Run images.setAnchorOptions. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setZOrder to apply a document change, then saves output DOCX for visual verification. Set the z-order (relativeHeight) for a floating image. Expected result: Returns an ImagesMutationResult.</t>
+          <t>Run images.setZOrder. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Runs images.scale to apply a document change, then saves output DOCX for visual verification. Scale an image by a uniform factor applied to both dimensions. Expected result: Returns an ImagesMutationResult with the updated image address.</t>
+          <t>Run images.scale. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setLockAspectRatio to apply a document change, then saves output DOCX for visual verification. Lock or unlock the aspect ratio for an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if already set.</t>
+          <t>Run images.setLockAspectRatio. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>Runs images.rotate to apply a document change, then saves output DOCX for visual verification. Set the absolute rotation angle for an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if already set.</t>
+          <t>Run images.rotate. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>Runs images.flip to apply a document change, then saves output DOCX for visual verification. Set horizontal and/or vertical flip state for an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if already set.</t>
+          <t>Run images.flip. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>Runs images.crop to apply a document change, then saves output DOCX for visual verification. Apply rectangular edge-percentage crop to an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run images.crop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>Runs images.resetCrop to apply a document change, then saves output DOCX for visual verification. Remove all cropping from an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if no crop is set.</t>
+          <t>Run images.resetCrop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Runs images.replaceSource to apply a document change, then saves output DOCX for visual verification. Replace the image source while preserving identity and placement. Expected result: Returns an ImagesMutationResult with the updated image address.</t>
+          <t>Run images.replaceSource. The targeted content should be replaced with the new content, in the same location.</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setAltText to apply a document change, then saves output DOCX for visual verification. Set the accessibility description (alt text) for an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run images.setAltText. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setDecorative to apply a document change, then saves output DOCX for visual verification. Mark or unmark an image as decorative. Expected result: Returns an ImagesMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run images.setDecorative. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setName to apply a document change, then saves output DOCX for visual verification. Set the object name for an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run images.setName. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Runs images.setHyperlink to apply a document change, then saves output DOCX for visual verification. Set or remove the hyperlink attached to an image. Expected result: Returns an ImagesMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run images.setHyperlink. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>Runs images.insertCaption to apply a document change, then saves output DOCX for visual verification. Insert a caption paragraph below the image. Expected result: Returns an ImagesMutationResult with the image address.</t>
+          <t>Run images.insertCaption. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Runs images.updateCaption to apply a document change, then saves output DOCX for visual verification. Update the text of an existing caption paragraph. Expected result: Returns an ImagesMutationResult; reports NO_OP if text unchanged.</t>
+          <t>Run images.updateCaption. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>Runs images.removeCaption to apply a document change, then saves output DOCX for visual verification. Remove the caption paragraph from below the image. Expected result: Returns an ImagesMutationResult; reports NO_OP if no caption exists.</t>
+          <t>Run images.removeCaption. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Runs hyperlinks.list and returns structured data only. DOCX should remain visually unchanged. Returns a HyperlinksListResult with an array of hyperlink discovery items and pagination metadata.</t>
+          <t>Run hyperlinks.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>Runs hyperlinks.get and returns structured data only. DOCX should remain visually unchanged. Returns a HyperlinkInfo object with the address, destination properties, and display text.</t>
+          <t>Run hyperlinks.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Runs hyperlinks.wrap to apply a document change, then saves output DOCX for visual verification. Wrap an existing text range with a hyperlink. Expected result: Returns a HyperlinkMutationResult with the created hyperlink address on success, or a failure code on no-op.</t>
+          <t>Run hyperlinks.wrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>Runs hyperlinks.insert to apply a document change, then saves output DOCX for visual verification. Insert new linked text at a target position. Expected result: Returns a HyperlinkMutationResult with the created hyperlink address on success, or a failure code.</t>
+          <t>Run hyperlinks.insert. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Runs hyperlinks.patch to apply a document change, then saves output DOCX for visual verification. Update hyperlink metadata (destination, tooltip, target, rel) without changing display text. Expected result: Returns a HyperlinkMutationResult with the updated hyperlink address on success, or NO_OP if unchanged.</t>
+          <t>Run hyperlinks.patch. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Runs hyperlinks.remove to apply a document change, then saves output DOCX for visual verification. Remove a hyperlink. Mode 'unwrap' preserves display text; 'deleteText' removes the linked content entirely. Expected result: Returns a HyperlinkMutationResult with the removed hyperlink address on success, or a failure code on no-op.</t>
+          <t>Run hyperlinks.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.list and returns structured data only. DOCX should remain visually unchanged. Returns a paginated DiscoveryOutput of HeaderFooterSlotEntry items.</t>
+          <t>Run headerFooters.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.get and returns structured data only. DOCX should remain visually unchanged. Returns a HeaderFooterSlotEntry for the targeted section slot.</t>
+          <t>Run headerFooters.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.resolve and returns structured data only. DOCX should remain visually unchanged. Returns a HeaderFooterResolveResult indicating explicit, inherited, or none status with the resolved refId.</t>
+          <t>Run headerFooters.resolve. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.refs.set to apply a document change, then saves output DOCX for visual verification. Set an explicit header/footer reference on a section slot. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if the reference already matches, INVALID_TARGET if the relationship does not exist.</t>
+          <t>Run headerFooters.refs.set. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.refs.clear to apply a document change, then saves output DOCX for visual verification. Clear an explicit header/footer reference from a section slot. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if no explicit reference existed.</t>
+          <t>Run headerFooters.refs.clear. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.refs.setLinkedToPrevious to apply a document change, then saves output DOCX for visual verification. Link or unlink a header/footer slot to/from the previous section. Expected result: Returns a SectionMutationResult receipt; reports NO_OP if the link state already matches, INVALID_TARGET for the first section.</t>
+          <t>Run headerFooters.refs.setLinkedToPrevious. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.parts.list and returns structured data only. DOCX should remain visually unchanged. Returns a paginated DiscoveryOutput of HeaderFooterPartEntry items.</t>
+          <t>Run headerFooters.parts.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.parts.create to apply a document change, then saves output DOCX for visual verification. Create a new independent header/footer part, optionally cloned from an existing part. Expected result: Returns a HeaderFooterPartsMutationResult with the new refId/partPath on success, INVALID_TARGET failure when sourceRefId is invalid or mismatched.</t>
+          <t>Run headerFooters.parts.create. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G272" s="4" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>Runs headerFooters.parts.delete to apply a document change, then saves output DOCX for visual verification. Delete a header/footer part and its associated relationship when no section slots reference it. Expected result: Returns a HeaderFooterPartsMutationResult on success; INVALID_TARGET failure if sections still reference the part.</t>
+          <t>Run headerFooters.parts.delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>Runs create.contentControl to apply a document change, then saves output DOCX for visual verification. Create a new content control (SDT) in the document. Expected result: Returns a ContentControlMutationResult with the created content control target.</t>
+          <t>Run create.contentControl. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
         </is>
       </c>
       <c r="G274" s="4" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.list and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsListResult with items and total count.</t>
+          <t>Run contentControls.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.get and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlInfo with full properties.</t>
+          <t>Run contentControls.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.listInRange and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsListResult scoped to the range.</t>
+          <t>Run contentControls.listInRange. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G277" s="4" t="inlineStr">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.selectByTag and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsListResult with matching items.</t>
+          <t>Run contentControls.selectByTag. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G278" s="4" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.selectByTitle and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsListResult with matching items.</t>
+          <t>Run contentControls.selectByTitle. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G279" s="4" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.listChildren and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsListResult with child items.</t>
+          <t>Run contentControls.listChildren. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.getParent and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlInfo for the parent, or null if no parent SDT exists.</t>
+          <t>Run contentControls.getParent. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.wrap to apply a document change, then saves output DOCX for visual verification. Wrap existing content with a new content control. Expected result: Returns a ContentControlMutationResult with the wrapper target.</t>
+          <t>Run contentControls.wrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G282" s="4" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.unwrap to apply a document change, then saves output DOCX for visual verification. Remove the content control wrapper, preserving its content in place. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already unwrapped.</t>
+          <t>Run contentControls.unwrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.delete to apply a document change, then saves output DOCX for visual verification. Delete a content control and its content from the document. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already removed.</t>
+          <t>Run contentControls.delete. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G284" s="4" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.copy to apply a document change, then saves output DOCX for visual verification. Copy a content control to a destination position. Copied SDTs receive new IDs. Expected result: Returns a ContentControlMutationResult with the copied content control target.</t>
+          <t>Run contentControls.copy. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.move to apply a document change, then saves output DOCX for visual verification. Move a content control to a new position. Preserves original IDs. Expected result: Returns a ContentControlMutationResult with the updated target position.</t>
+          <t>Run contentControls.move. The targeted content should be moved from its original location to the requested location (for example, below/after the reference content). It should no longer appear at the old location.</t>
         </is>
       </c>
       <c r="G286" s="4" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.patch to apply a document change, then saves output DOCX for visual verification. Patch metadata properties on a content control (tag, alias, appearance, color, etc.). Expected result: Returns a ContentControlMutationResult; reports NO_OP if no fields changed.</t>
+          <t>Run contentControls.patch. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.setLockMode to apply a document change, then saves output DOCX for visual verification. Set the lock mode on a content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if lock mode unchanged.</t>
+          <t>Run contentControls.setLockMode. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.setType to apply a document change, then saves output DOCX for visual verification. Transition a content control to a different semantic type. Metadata-only; no implicit content rewrite. Expected result: Returns a ContentControlMutationResult; reports NO_OP if type unchanged.</t>
+          <t>Run contentControls.setType. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.getContent and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsGetContentResult with the content string and format.</t>
+          <t>Run contentControls.getContent. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.replaceContent to apply a document change, then saves output DOCX for visual verification. Replace the entire content of a content control. Expected result: Returns a ContentControlMutationResult with the updated target.</t>
+          <t>Run contentControls.replaceContent. The targeted content should be replaced with the new content, in the same location.</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.clearContent to apply a document change, then saves output DOCX for visual verification. Clear all content inside a content control, leaving it empty. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already empty.</t>
+          <t>Run contentControls.clearContent. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G292" s="4" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.appendContent to apply a document change, then saves output DOCX for visual verification. Append content to the end of a content control. Expected result: Returns a ContentControlMutationResult with the updated target.</t>
+          <t>Run contentControls.appendContent. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G293" s="4" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.prependContent to apply a document change, then saves output DOCX for visual verification. Prepend content to the beginning of a content control. Expected result: Returns a ContentControlMutationResult with the updated target.</t>
+          <t>Run contentControls.prependContent. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.insertBefore to apply a document change, then saves output DOCX for visual verification. Insert content immediately before a content control. Expected result: Returns a ContentControlMutationResult with the target.</t>
+          <t>Run contentControls.insertBefore. The inserted content should appear immediately before the target content.</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.insertAfter to apply a document change, then saves output DOCX for visual verification. Insert content immediately after a content control. Expected result: Returns a ContentControlMutationResult with the target.</t>
+          <t>Run contentControls.insertAfter. The inserted content should appear immediately after the target content.</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.getBinding and returns structured data only. DOCX should remain visually unchanged. Returns the ContentControlBinding or null if no binding is set.</t>
+          <t>Run contentControls.getBinding. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G297" s="4" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.setBinding to apply a document change, then saves output DOCX for visual verification. Set data binding metadata on a content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if binding unchanged.</t>
+          <t>Run contentControls.setBinding. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.clearBinding to apply a document change, then saves output DOCX for visual verification. Remove data binding metadata from a content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if no binding existed.</t>
+          <t>Run contentControls.clearBinding. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G299" s="4" t="inlineStr">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.getRawProperties and returns structured data only. DOCX should remain visually unchanged. Returns a ContentControlsGetRawPropertiesResult with the raw properties.</t>
+          <t>Run contentControls.getRawProperties. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.patchRawProperties to apply a document change, then saves output DOCX for visual verification. Apply raw XML-level patches to the sdtPr subtree of a content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if no effective changes.</t>
+          <t>Run contentControls.patchRawProperties. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.validateWordCompatibility and returns structured data only. DOCX should remain visually unchanged. Returns a compatibility result with diagnostics.</t>
+          <t>Run contentControls.validateWordCompatibility. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.normalizeWordCompatibility to apply a document change, then saves output DOCX for visual verification. Normalize a content control to resolve Word compatibility issues. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already compatible.</t>
+          <t>Run contentControls.normalizeWordCompatibility. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.normalizeTagPayload to apply a document change, then saves output DOCX for visual verification. Normalize a content control tag between plain-string and JSON-encoded formats. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already normalized.</t>
+          <t>Run contentControls.normalizeTagPayload. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.text.setMultiline to apply a document change, then saves output DOCX for visual verification. Set or clear the multiline attribute on a plain-text content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.text.setMultiline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.text.setValue to apply a document change, then saves output DOCX for visual verification. Set the text value of a plain-text content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.text.setValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.text.clearValue to apply a document change, then saves output DOCX for visual verification. Clear the text value of a plain-text content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already empty.</t>
+          <t>Run contentControls.text.clearValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.date.setValue to apply a document change, then saves output DOCX for visual verification. Set the date value of a date content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.date.setValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.date.clearValue to apply a document change, then saves output DOCX for visual verification. Clear the date value of a date content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if already empty.</t>
+          <t>Run contentControls.date.clearValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.date.setDisplayFormat to apply a document change, then saves output DOCX for visual verification. Set the display format string for a date content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.date.setDisplayFormat. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.date.setDisplayLocale to apply a document change, then saves output DOCX for visual verification. Set the display locale for a date content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.date.setDisplayLocale. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -24860,7 +24860,7 @@
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.date.setStorageFormat to apply a document change, then saves output DOCX for visual verification. Set the XML storage format for a date content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.date.setStorageFormat. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.date.setCalendar to apply a document change, then saves output DOCX for visual verification. Set the calendar type for a date content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.date.setCalendar. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.checkbox.getState and returns structured data only. DOCX should remain visually unchanged. Returns a CheckboxGetStateResult with the checked boolean.</t>
+          <t>Run contentControls.checkbox.getState. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G314" s="4" t="inlineStr">
@@ -25038,7 +25038,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.checkbox.setState to apply a document change, then saves output DOCX for visual verification. Set the checked state of a checkbox content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.checkbox.setState. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.checkbox.toggle to apply a document change, then saves output DOCX for visual verification. Toggle the checked state of a checkbox content control. Expected result: Returns a ContentControlMutationResult with the updated state.</t>
+          <t>Run contentControls.checkbox.toggle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G316" s="4" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.checkbox.setSymbolPair to apply a document change, then saves output DOCX for visual verification. Set the checked and unchecked symbol glyphs for a checkbox content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if symbols unchanged.</t>
+          <t>Run contentControls.checkbox.setSymbolPair. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.choiceList.getItems and returns structured data only. DOCX should remain visually unchanged. Returns a ChoiceListGetItemsResult with items and selectedValue.</t>
+          <t>Run contentControls.choiceList.getItems. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.choiceList.setItems to apply a document change, then saves output DOCX for visual verification. Replace the list items of a comboBox or dropDownList content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if items unchanged.</t>
+          <t>Run contentControls.choiceList.setItems. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.choiceList.setSelected to apply a document change, then saves output DOCX for visual verification. Set the selected value of a comboBox or dropDownList content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if selection unchanged.</t>
+          <t>Run contentControls.choiceList.setSelected. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G320" s="4" t="inlineStr">
@@ -25390,7 +25390,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.repeatingSection.listItems and returns structured data only. DOCX should remain visually unchanged. Returns a RepeatingSectionListItemsResult with child item info.</t>
+          <t>Run contentControls.repeatingSection.listItems. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.repeatingSection.insertItemBefore to apply a document change, then saves output DOCX for visual verification. Insert a new item before a specific index in a repeating section. Expected result: Returns a ContentControlMutationResult with the new item target.</t>
+          <t>Run contentControls.repeatingSection.insertItemBefore. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.repeatingSection.insertItemAfter to apply a document change, then saves output DOCX for visual verification. Insert a new item after a specific index in a repeating section. Expected result: Returns a ContentControlMutationResult with the new item target.</t>
+          <t>Run contentControls.repeatingSection.insertItemAfter. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.repeatingSection.cloneItem to apply a document change, then saves output DOCX for visual verification. Clone a repeating section item at the given index. Cloned SDTs receive new IDs. Expected result: Returns a ContentControlMutationResult with the cloned item target.</t>
+          <t>Run contentControls.repeatingSection.cloneItem. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.repeatingSection.deleteItem to apply a document change, then saves output DOCX for visual verification. Delete a repeating section item at the given index. Expected result: Returns a ContentControlMutationResult; reports NO_OP if item does not exist.</t>
+          <t>Run contentControls.repeatingSection.deleteItem. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G325" s="4" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.repeatingSection.setAllowInsertDelete to apply a document change, then saves output DOCX for visual verification. Set the allowInsertDelete flag on a repeating section. Expected result: Returns a ContentControlMutationResult; reports NO_OP if unchanged.</t>
+          <t>Run contentControls.repeatingSection.setAllowInsertDelete. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.group.wrap to apply a document change, then saves output DOCX for visual verification. Wrap a content control inside a new group content control. Always nests; not idempotent. Expected result: Returns a ContentControlMutationResult with the new group wrapper target.</t>
+          <t>Run contentControls.group.wrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>Runs contentControls.group.ungroup to apply a document change, then saves output DOCX for visual verification. Remove the group designation from a group content control. Expected result: Returns a ContentControlMutationResult; reports NO_OP if not a group.</t>
+          <t>Run contentControls.group.ungroup. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Runs bookmarks.list and returns structured data only. DOCX should remain visually unchanged. Returns a BookmarksListResult containing discovered bookmarks with address and domain data.</t>
+          <t>Run bookmarks.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>Runs bookmarks.get and returns structured data only. DOCX should remain visually unchanged. Returns a BookmarkInfo object with the bookmark's name, range, and optional table-column data.</t>
+          <t>Run bookmarks.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Runs bookmarks.insert to apply a document change, then saves output DOCX for visual verification. Insert a new named bookmark at a target location. Expected result: Returns a BookmarkMutationResult indicating success with the bookmark address or a failure.</t>
+          <t>Run bookmarks.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr">
@@ -26048,7 +26048,7 @@
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>Runs bookmarks.rename to apply a document change, then saves output DOCX for visual verification. Rename an existing bookmark. Expected result: Returns a BookmarkMutationResult indicating success with the updated bookmark address or a failure.</t>
+          <t>Run bookmarks.rename. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Runs bookmarks.remove to apply a document change, then saves output DOCX for visual verification. Remove a bookmark from the document. Expected result: Returns a BookmarkMutationResult indicating success or a failure.</t>
+          <t>Run bookmarks.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G333" s="4" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Runs footnotes.list and returns structured data only. DOCX should remain visually unchanged. Returns a FootnotesListResult containing discovered footnotes with address and domain data.</t>
+          <t>Run footnotes.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Runs footnotes.get and returns structured data only. DOCX should remain visually unchanged. Returns a FootnoteInfo object with the note's type, display number, and content.</t>
+          <t>Run footnotes.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Runs footnotes.insert to apply a document change, then saves output DOCX for visual verification. Insert a new footnote or endnote at a target location. Expected result: Returns a FootnoteMutationResult indicating success with the footnote address or a failure.</t>
+          <t>Run footnotes.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Runs footnotes.update to apply a document change, then saves output DOCX for visual verification. Update the content of an existing footnote or endnote. Expected result: Returns a FootnoteMutationResult indicating success with the updated footnote address or a failure.</t>
+          <t>Run footnotes.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>Runs footnotes.remove to apply a document change, then saves output DOCX for visual verification. Remove a footnote or endnote from the document. Expected result: Returns a FootnoteMutationResult indicating success or a failure.</t>
+          <t>Run footnotes.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Runs footnotes.configure to apply a document change, then saves output DOCX for visual verification. Configure numbering and placement for footnotes or endnotes. Expected result: Returns a FootnoteConfigResult indicating success or a failure.</t>
+          <t>Run footnotes.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>Runs crossRefs.list and returns structured data only. DOCX should remain visually unchanged. Returns a CrossRefsListResult containing discovered cross-references with address and domain data.</t>
+          <t>Run crossRefs.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Runs crossRefs.get and returns structured data only. DOCX should remain visually unchanged. Returns a CrossRefInfo object with the cross-reference's target, display, and resolved text.</t>
+          <t>Run crossRefs.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G341" s="4" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>Runs crossRefs.insert to apply a document change, then saves output DOCX for visual verification. Insert a new cross-reference field at a target location. Expected result: Returns a CrossRefMutationResult indicating success with the cross-reference address or a failure.</t>
+          <t>Run crossRefs.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G342" s="4" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>Runs crossRefs.rebuild to apply a document change, then saves output DOCX for visual verification. Rebuild (recalculate) a cross-reference field. Expected result: Returns a CrossRefMutationResult indicating success or a failure.</t>
+          <t>Run crossRefs.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -26776,7 +26776,7 @@
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>Runs crossRefs.remove to apply a document change, then saves output DOCX for visual verification. Remove a cross-reference field from the document. Expected result: Returns a CrossRefMutationResult indicating success or a failure.</t>
+          <t>Run crossRefs.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>Runs index.list and returns structured data only. DOCX should remain visually unchanged. Returns an IndexListResult containing discovered index blocks with address and domain data.</t>
+          <t>Run index.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>Runs index.get and returns structured data only. DOCX should remain visually unchanged. Returns an IndexInfo object with the index's instruction, configuration, and entry count.</t>
+          <t>Run index.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Runs index.insert to apply a document change, then saves output DOCX for visual verification. Insert a new index block at a target location. Expected result: Returns an IndexMutationResult indicating success with the index address or a failure.</t>
+          <t>Run index.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G347" s="4" t="inlineStr">
@@ -27024,7 +27024,7 @@
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>Runs index.configure to apply a document change, then saves output DOCX for visual verification. Update the configuration of an existing index block. Expected result: Returns an IndexMutationResult indicating success or a failure.</t>
+          <t>Run index.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>Runs index.rebuild to apply a document change, then saves output DOCX for visual verification. Rebuild (regenerate) an index block from its entries. Expected result: Returns an IndexMutationResult indicating success or a failure.</t>
+          <t>Run index.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>Runs index.remove to apply a document change, then saves output DOCX for visual verification. Remove an index block from the document. Expected result: Returns an IndexMutationResult indicating success or a failure.</t>
+          <t>Run index.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -27198,7 +27198,7 @@
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Runs index.entries.list and returns structured data only. DOCX should remain visually unchanged. Returns an IndexEntryListResult containing discovered index entries with address and domain data.</t>
+          <t>Run index.entries.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>Runs index.entries.get and returns structured data only. DOCX should remain visually unchanged. Returns an IndexEntryInfo object with the entry's text, sub-entry, formatting, and instruction.</t>
+          <t>Run index.entries.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>Runs index.entries.insert to apply a document change, then saves output DOCX for visual verification. Insert a new XE index entry field at a target location. Expected result: Returns an IndexEntryMutationResult indicating success with the entry address or a failure.</t>
+          <t>Run index.entries.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Runs index.entries.update to apply a document change, then saves output DOCX for visual verification. Update the properties of an existing XE index entry. Expected result: Returns an IndexEntryMutationResult indicating success or a failure.</t>
+          <t>Run index.entries.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -27438,7 +27438,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Runs index.entries.remove to apply a document change, then saves output DOCX for visual verification. Remove an XE index entry field from the document. Expected result: Returns an IndexEntryMutationResult indicating success or a failure.</t>
+          <t>Run index.entries.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>Runs captions.list and returns structured data only. DOCX should remain visually unchanged. Returns a CaptionsListResult containing discovered captions with address and domain data.</t>
+          <t>Run captions.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Runs captions.get and returns structured data only. DOCX should remain visually unchanged. Returns a CaptionInfo object with the caption's label, number, text, and instruction.</t>
+          <t>Run captions.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Runs captions.insert to apply a document change, then saves output DOCX for visual verification. Insert a new caption paragraph adjacent to a target block. Expected result: Returns a CaptionMutationResult indicating success with the caption address or a failure.</t>
+          <t>Run captions.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Runs captions.update to apply a document change, then saves output DOCX for visual verification. Update the text of an existing caption paragraph. Expected result: Returns a CaptionMutationResult indicating success or a failure.</t>
+          <t>Run captions.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -27744,7 +27744,7 @@
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Runs captions.remove to apply a document change, then saves output DOCX for visual verification. Remove a caption paragraph from the document. Expected result: Returns a CaptionMutationResult indicating success or a failure.</t>
+          <t>Run captions.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Runs captions.configure to apply a document change, then saves output DOCX for visual verification. Configure numbering format for a caption label. Expected result: Returns a CaptionConfigResult indicating success or a failure.</t>
+          <t>Run captions.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>Runs fields.list and returns structured data only. DOCX should remain visually unchanged. Returns a FieldsListResult containing discovered fields with address and domain data.</t>
+          <t>Run fields.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Runs fields.get and returns structured data only. DOCX should remain visually unchanged. Returns a FieldInfo object with the field's instruction, result text, and nesting data.</t>
+          <t>Run fields.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>Runs fields.insert to apply a document change, then saves output DOCX for visual verification. Insert a raw field code at a target location. Expected result: Returns a FieldMutationResult indicating success with the field address or a failure.</t>
+          <t>Run fields.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Runs fields.rebuild to apply a document change, then saves output DOCX for visual verification. Rebuild (recalculate) a field. Expected result: Returns a FieldMutationResult indicating success or a failure.</t>
+          <t>Run fields.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>Runs fields.remove to apply a document change, then saves output DOCX for visual verification. Remove a field from the document. Expected result: Returns a FieldMutationResult indicating success or a failure.</t>
+          <t>Run fields.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.list and returns structured data only. DOCX should remain visually unchanged. Returns a CitationsListResult containing discovered citation marks with address and domain data.</t>
+          <t>Run citations.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.get and returns structured data only. DOCX should remain visually unchanged. Returns a CitationInfo object with the citation's source references and display text.</t>
+          <t>Run citations.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G368" s="4" t="inlineStr">
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.insert to apply a document change, then saves output DOCX for visual verification. Insert a new citation mark at a target location. Expected result: Returns a CitationMutationResult indicating success with the citation address or a failure.</t>
+          <t>Run citations.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.update to apply a document change, then saves output DOCX for visual verification. Update an existing citation mark's source references. Expected result: Returns a CitationMutationResult indicating success or a failure.</t>
+          <t>Run citations.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.remove to apply a document change, then saves output DOCX for visual verification. Remove a citation mark from the document. Expected result: Returns a CitationMutationResult indicating success or a failure.</t>
+          <t>Run citations.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.sources.list and returns structured data only. DOCX should remain visually unchanged. Returns a CitationSourcesListResult containing discovered sources with address and domain data.</t>
+          <t>Run citations.sources.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.sources.get and returns structured data only. DOCX should remain visually unchanged. Returns a CitationSourceInfo object with the source's type, fields, and metadata.</t>
+          <t>Run citations.sources.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.sources.insert to apply a document change, then saves output DOCX for visual verification. Register a new citation source in the document store. Expected result: Returns a CitationSourceMutationResult indicating success with the source address or a failure.</t>
+          <t>Run citations.sources.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G374" s="4" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.sources.update to apply a document change, then saves output DOCX for visual verification. Update the fields of an existing citation source. Expected result: Returns a CitationSourceMutationResult indicating success or a failure.</t>
+          <t>Run citations.sources.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G375" s="4" t="inlineStr">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.sources.remove to apply a document change, then saves output DOCX for visual verification. Remove a citation source from the document store. Expected result: Returns a CitationSourceMutationResult indicating success or a failure.</t>
+          <t>Run citations.sources.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G376" s="4" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.bibliography.get and returns structured data only. DOCX should remain visually unchanged. Returns a BibliographyInfo object with the bibliography's address and configuration.</t>
+          <t>Run citations.bibliography.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G377" s="4" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.bibliography.insert to apply a document change, then saves output DOCX for visual verification. Insert a bibliography block at a target location. Expected result: Returns a BibliographyMutationResult indicating success with the bibliography address or a failure.</t>
+          <t>Run citations.bibliography.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G378" s="4" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.bibliography.rebuild to apply a document change, then saves output DOCX for visual verification. Rebuild the bibliography from current sources. Expected result: Returns a BibliographyMutationResult indicating success or a failure.</t>
+          <t>Run citations.bibliography.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr">
@@ -28948,7 +28948,7 @@
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.bibliography.configure to apply a document change, then saves output DOCX for visual verification. Configure the bibliography style. Expected result: Returns a BibliographyMutationResult indicating success or a failure.</t>
+          <t>Run citations.bibliography.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Runs citations.bibliography.remove to apply a document change, then saves output DOCX for visual verification. Remove the bibliography block from the document. Expected result: Returns a BibliographyMutationResult indicating success or a failure.</t>
+          <t>Run citations.bibliography.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G381" s="4" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.list and returns structured data only. DOCX should remain visually unchanged. Returns an AuthoritiesListResult containing discovered TOA blocks with address and domain data.</t>
+          <t>Run authorities.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G382" s="4" t="inlineStr">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.get and returns structured data only. DOCX should remain visually unchanged. Returns an AuthoritiesInfo object with the TOA's category filter and configuration.</t>
+          <t>Run authorities.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -29196,7 +29196,7 @@
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.insert to apply a document change, then saves output DOCX for visual verification. Insert a new table-of-authorities block at a target location. Expected result: Returns an AuthoritiesMutationResult indicating success with the TOA address or a failure.</t>
+          <t>Run authorities.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G384" s="4" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.configure to apply a document change, then saves output DOCX for visual verification. Update the configuration of an existing table-of-authorities block. Expected result: Returns an AuthoritiesMutationResult indicating success or a failure.</t>
+          <t>Run authorities.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -29312,7 +29312,7 @@
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.rebuild to apply a document change, then saves output DOCX for visual verification. Rebuild a table-of-authorities block from its entries. Expected result: Returns an AuthoritiesMutationResult indicating success or a failure.</t>
+          <t>Run authorities.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G386" s="4" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.remove to apply a document change, then saves output DOCX for visual verification. Remove a table-of-authorities block from the document. Expected result: Returns an AuthoritiesMutationResult indicating success or a failure.</t>
+          <t>Run authorities.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G387" s="4" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.entries.list and returns structured data only. DOCX should remain visually unchanged. Returns an AuthorityEntryListResult containing discovered entries with address and domain data.</t>
+          <t>Run authorities.entries.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.entries.get and returns structured data only. DOCX should remain visually unchanged. Returns an AuthorityEntryInfo object with the entry's citations and category.</t>
+          <t>Run authorities.entries.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.entries.insert to apply a document change, then saves output DOCX for visual verification. Insert a new TA authority entry field at a target location. Expected result: Returns an AuthorityEntryMutationResult indicating success with the entry address or a failure.</t>
+          <t>Run authorities.entries.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.entries.update to apply a document change, then saves output DOCX for visual verification. Update the properties of an existing TA authority entry. Expected result: Returns an AuthorityEntryMutationResult indicating success or a failure.</t>
+          <t>Run authorities.entries.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>Runs authorities.entries.remove to apply a document change, then saves output DOCX for visual verification. Remove a TA authority entry field from the document. Expected result: Returns an AuthorityEntryMutationResult indicating success or a failure.</t>
+          <t>Run authorities.entries.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Runs diff.capture and returns structured data only. DOCX should remain visually unchanged. Returns a DiffSnapshot with a fingerprint and opaque payload.</t>
+          <t>Run diff.capture. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G393" s="4" t="inlineStr">
@@ -29792,7 +29792,7 @@
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>Runs diff.compare and returns structured data only. DOCX should remain visually unchanged. Returns a DiffPayload with a summary and opaque payload.</t>
+          <t>Run diff.compare. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Runs diff.apply to apply a document change, then saves output DOCX for visual verification. Apply a previously computed diff payload to the current document. The document fingerprint must match the diff base fingerprint. Tracked mode governs body content only; styles, numbering, and comments are always applied... Expected result: Returns a DiffApplyResult with applied operation count and diagnostics.</t>
+          <t>Run diff.apply. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>Runs protection.get and returns structured data only. DOCX should remain visually unchanged. Returns a DocumentProtectionState with editingRestriction, writeProtection, and readOnlyRecommended fields.</t>
+          <t>Run protection.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Runs protection.setEditingRestriction to apply a document change, then saves output DOCX for visual verification. Enable Word-style editing restriction on the document. Only readOnly mode is supported in v1. Expected result: Returns a ProtectionMutationResult with the updated protection state on success.</t>
+          <t>Run protection.setEditingRestriction. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
@@ -30040,7 +30040,7 @@
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>Runs protection.clearEditingRestriction to apply a document change, then saves output DOCX for visual verification. Disable document-level editing restriction by setting enforcement to off. Preserves the protection element and its metadata for round-trip fidelity. Expected result: Returns a ProtectionMutationResult with the updated protection state on success.</t>
+          <t>Run protection.clearEditingRestriction. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Runs permissionRanges.list and returns structured data only. DOCX should remain visually unchanged. Returns a PermissionRangesListResult containing discovered permission ranges with principal and position data.</t>
+          <t>Run permissionRanges.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>Runs permissionRanges.get and returns structured data only. DOCX should remain visually unchanged. Returns a PermissionRangeInfo object with the range principal, kind, and positions.</t>
+          <t>Run permissionRanges.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Runs permissionRanges.create to apply a document change, then saves output DOCX for visual verification. Create a permission range exception region in the document. Inserts matched permStart/permEnd markers at the target. Expected result: Returns a PermissionRangeMutationResult with the created range info on success.</t>
+          <t>Run permissionRanges.create. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>Runs permissionRanges.remove to apply a document change, then saves output DOCX for visual verification. Remove a permission range by ID. Removes whichever markers exist for the given ID (start, end, or both). Expected result: Returns a PermissionRangeRemoveResult indicating success or a failure.</t>
+          <t>Run permissionRanges.remove. The targeted content should be removed and should no longer appear in the document.</t>
         </is>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Runs permissionRanges.updatePrincipal to apply a document change, then saves output DOCX for visual verification. Change which principal is allowed to edit a permission range. Updates the principal fields on the start marker. Expected result: Returns a PermissionRangeMutationResult with the updated range info on success.</t>
+          <t>Run permissionRanges.updatePrincipal. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr">

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -834,12 +834,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Run create.paragraph. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Run create.heading. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Run create.table. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Run insert. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Run lists.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Run replace. The targeted content should be replaced with the new content, in the same location.</t>
+          <t>Expected check: Replaced "ABC" with "XYZ" at the same location.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Run delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Run blocks.delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Run format.apply. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Run format.fontSize. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Run format.fontFamily. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Run format.color. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Run comments.create. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Run comments.patch. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Run comments.delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Run lists.setType. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Run lists.indent. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Run lists.outdent. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Run tables.insertRow. A new row should appear adjacent to the targeted row (above or below based on input).</t>
+          <t>Expected check: Inserted a row next to row containing "ABC"; new row appears directly above/below as requested.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Run tables.deleteRow. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Run tables.insertColumn. A new column should appear adjacent to the targeted column (left or right based on input).</t>
+          <t>Expected check: Inserted a column next to column containing "ABC"; new column appears directly left/right as requested.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Run tables.deleteColumn. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Run format.bold. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Run format.italic. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Run format.underline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Run tables.delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Run tables.clearContents. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Run tables.split. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Run tables.convertToText. The targeted table should be replaced by plain text content at the same location.</t>
+          <t>Expected check: Converted table cells "ABC" and "XYZ" into plain text at the same location.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setLayout. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setRowHeight. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Run tables.distributeRows. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setRowOptions. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setColumnWidth. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Run tables.distributeColumns. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Run tables.insertCell. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Run tables.deleteCell. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Run tables.mergeCells. The selected neighboring cells should become one merged cell containing combined content.</t>
+          <t>Expected check: Merged adjacent cells containing "ABC" and "XYZ" into one cell.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Run tables.unmergeCells. The targeted merged cell should split into multiple cells.</t>
+          <t>Expected check: Split merged cell containing "ABC" into multiple cells.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Run tables.splitCell. The targeted merged cell should split into multiple cells.</t>
+          <t>Expected check: Split merged cell containing "ABC" into multiple cells.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setCellProperties. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Run tables.sort. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setAltText. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Run tables.clearStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setStyleOption. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setBorder. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Run tables.clearBorder. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Run tables.applyBorderPreset. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setShading. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Run tables.clearShading. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setTablePadding. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setCellPadding. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Run tables.setCellSpacing. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Run tables.clearCellSpacing. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Run mutations.apply. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Run tables.convertFromText. The selected plain text should become a table. The same information should now be arranged in table cells.</t>
+          <t>Expected check: Converted text line "ABC | XYZ" into table cells ("ABC" and "XYZ" in separate cells).</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E86" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t>Run tables.move. The targeted content should be moved from its original location to the requested location (for example, below/after the reference content). It should no longer appear at the old location.</t>
+          <t>Expected check: Moved "ABC" to below "XYZ". "ABC" should no longer appear in its old location.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="E87" s="22" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>Run create.sectionBreak. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="E88" s="22" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>Run create.tableOfContents. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="E89" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>Run sections.clearHeaderFooterRef. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="E90" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t>Run sections.clearPageBorders. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="E93" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setBreakType. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="E94" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setColumns. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="E95" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setHeaderFooterMargins. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr">
@@ -11156,12 +11156,12 @@
       </c>
       <c r="E96" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setHeaderFooterRef. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -11222,12 +11222,12 @@
       </c>
       <c r="E97" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setLineNumbering. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="E98" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setLinkToPrevious. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="E99" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setOddEvenHeadersFooters. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="E100" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setPageBorders. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="E101" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setPageMargins. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G101" s="22" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="E102" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setPageNumbering. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="E103" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setPageSetup. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G103" s="22" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="E104" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setSectionDirection. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E105" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setTitlePage. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G105" s="22" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E106" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t>Run sections.setVerticalAlign. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="E107" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>Run toc.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G107" s="22" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="E110" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t>Run toc.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="E111" s="22" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>Run toc.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G111" s="22" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="E112" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Run format.strike. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H112" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I112" s="25" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="E113" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Run format.highlight. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="H113" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I113" s="25" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="E114" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>Run format.shading. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G114" s="25" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="H114" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I114" s="25" t="inlineStr">
@@ -12494,12 +12494,12 @@
       </c>
       <c r="E115" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>Run format.border. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G115" s="25" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H115" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I115" s="25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E116" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F116" s="25" t="inlineStr">
         <is>
-          <t>Run format.outline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G116" s="25" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="H116" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I116" s="25" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="E117" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F117" s="25" t="inlineStr">
         <is>
-          <t>Run format.shadow. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G117" s="25" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="H117" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I117" s="25" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="E118" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>Run format.emboss. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G118" s="25" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="H118" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I118" s="25" t="inlineStr">
@@ -12786,12 +12786,12 @@
       </c>
       <c r="E119" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>Run format.imprint. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H119" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I119" s="25" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="E120" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F120" s="25" t="inlineStr">
         <is>
-          <t>Run format.vertAlign. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G120" s="25" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H120" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I120" s="25" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="E121" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F121" s="25" t="inlineStr">
         <is>
-          <t>Run format.position. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G121" s="25" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="H121" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I121" s="25" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="E122" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>Run format.rtl. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="H122" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I122" s="25" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="E123" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F123" s="25" t="inlineStr">
         <is>
-          <t>Run format.cs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G123" s="25" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="H123" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I123" s="25" t="inlineStr">
@@ -13144,12 +13144,12 @@
       </c>
       <c r="E124" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F124" s="25" t="inlineStr">
         <is>
-          <t>Run format.bCs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G124" s="25" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="H124" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I124" s="25" t="inlineStr">
@@ -13210,12 +13210,12 @@
       </c>
       <c r="E125" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F125" s="25" t="inlineStr">
         <is>
-          <t>Run format.iCs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G125" s="25" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="H125" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I125" s="25" t="inlineStr">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="E126" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F126" s="25" t="inlineStr">
         <is>
-          <t>Run format.vanish. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G126" s="25" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="H126" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I126" s="25" t="inlineStr">
@@ -13346,12 +13346,12 @@
       </c>
       <c r="E127" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F127" s="25" t="inlineStr">
         <is>
-          <t>Run format.webHidden. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G127" s="25" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="H127" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I127" s="25" t="inlineStr">
@@ -13416,12 +13416,12 @@
       </c>
       <c r="E128" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>Run format.specVanish. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="H128" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I128" s="25" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="E129" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>Run format.snapToGrid. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G129" s="25" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="H129" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I129" s="25" t="inlineStr">
@@ -13556,12 +13556,12 @@
       </c>
       <c r="E130" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F130" s="25" t="inlineStr">
         <is>
-          <t>Run format.oMath. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G130" s="25" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="H130" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I130" s="25" t="inlineStr">
@@ -13630,12 +13630,12 @@
       </c>
       <c r="E131" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
-          <t>Run format.fontSizeCs. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G131" s="25" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="H131" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I131" s="25" t="inlineStr">
@@ -13696,12 +13696,12 @@
       </c>
       <c r="E132" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>Run format.charScale. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G132" s="25" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="H132" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I132" s="25" t="inlineStr">
@@ -13766,12 +13766,12 @@
       </c>
       <c r="E133" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>Run format.kerning. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G133" s="25" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="H133" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I133" s="25" t="inlineStr">
@@ -13836,12 +13836,12 @@
       </c>
       <c r="E134" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>Run format.fitText. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H134" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I134" s="25" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="E135" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>Run format.lang. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G135" s="25" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="H135" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I135" s="25" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="E136" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>Run format.rStyle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="H136" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I136" s="25" t="inlineStr">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="E137" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>Run format.rFonts. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G137" s="25" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="H137" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I137" s="25" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="E138" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>Run format.eastAsianLayout. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G138" s="25" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="H138" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I138" s="25" t="inlineStr">
@@ -14166,12 +14166,12 @@
       </c>
       <c r="E139" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>Run format.em. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G139" s="25" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="H139" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I139" s="25" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="E140" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>Run format.ligatures. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G140" s="25" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="H140" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I140" s="25" t="inlineStr">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="E141" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F141" s="25" t="inlineStr">
         <is>
-          <t>Run format.numForm. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G141" s="25" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="H141" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I141" s="25" t="inlineStr">
@@ -14364,12 +14364,12 @@
       </c>
       <c r="E142" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>Run format.numSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G142" s="25" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="H142" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I142" s="25" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="E143" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F143" s="25" t="inlineStr">
         <is>
-          <t>Run format.stylisticSets. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G143" s="25" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="H143" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I143" s="25" t="inlineStr">
@@ -14496,12 +14496,12 @@
       </c>
       <c r="E144" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>Run format.contextualAlternates. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G144" s="25" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="H144" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I144" s="25" t="inlineStr">
@@ -14566,12 +14566,12 @@
       </c>
       <c r="E145" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F145" s="25" t="inlineStr">
         <is>
-          <t>Run format.dstrike. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G145" s="25" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="H145" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I145" s="25" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E146" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F146" s="25" t="inlineStr">
         <is>
-          <t>Run format.smallCaps. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G146" s="25" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="H146" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I146" s="25" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="E147" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F147" s="25" t="inlineStr">
         <is>
-          <t>Run format.caps. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G147" s="25" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="H147" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I147" s="25" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="E148" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F148" s="25" t="inlineStr">
         <is>
-          <t>Run format.letterSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G148" s="25" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="H148" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I148" s="25" t="inlineStr">
@@ -15073,12 +15073,12 @@
       </c>
       <c r="E152" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F152" s="25" t="inlineStr">
         <is>
-          <t>Run styles.paragraph.setStyle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G152" s="25" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="H152" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I152" s="25" t="inlineStr">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="E153" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F153" s="25" t="inlineStr">
         <is>
-          <t>Run styles.paragraph.clearStyle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G153" s="25" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="H153" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I153" s="25" t="inlineStr">
@@ -15197,12 +15197,12 @@
       </c>
       <c r="E154" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F154" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.resetDirectFormatting. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G154" s="25" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="H154" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I154" s="25" t="inlineStr">
@@ -15259,12 +15259,12 @@
       </c>
       <c r="E155" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F155" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setAlignment. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G155" s="25" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="H155" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I155" s="25" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E156" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F156" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearAlignment. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G156" s="25" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="H156" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I156" s="25" t="inlineStr">
@@ -15383,12 +15383,12 @@
       </c>
       <c r="E157" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setIndentation. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G157" s="25" t="inlineStr">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="H157" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I157" s="25" t="inlineStr">
@@ -15449,12 +15449,12 @@
       </c>
       <c r="E158" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F158" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearIndentation. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G158" s="25" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="H158" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I158" s="25" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="E159" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F159" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G159" s="25" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="H159" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I159" s="25" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E160" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F160" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearSpacing. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G160" s="25" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="H160" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I160" s="25" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E161" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F161" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setKeepOptions. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G161" s="25" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="H161" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I161" s="25" t="inlineStr">
@@ -15701,12 +15701,12 @@
       </c>
       <c r="E162" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setOutlineLevel. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G162" s="25" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="H162" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I162" s="25" t="inlineStr">
@@ -15763,12 +15763,12 @@
       </c>
       <c r="E163" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F163" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setFlowOptions. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G163" s="25" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="H163" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I163" s="25" t="inlineStr">
@@ -15825,12 +15825,12 @@
       </c>
       <c r="E164" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F164" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setTabStop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G164" s="25" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="H164" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I164" s="25" t="inlineStr">
@@ -15887,12 +15887,12 @@
       </c>
       <c r="E165" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F165" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearTabStop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G165" s="25" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="H165" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I165" s="25" t="inlineStr">
@@ -15949,12 +15949,12 @@
       </c>
       <c r="E166" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F166" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearAllTabStops. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G166" s="25" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="H166" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I166" s="25" t="inlineStr">
@@ -16011,12 +16011,12 @@
       </c>
       <c r="E167" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F167" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setBorder. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G167" s="25" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="H167" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I167" s="25" t="inlineStr">
@@ -16073,12 +16073,12 @@
       </c>
       <c r="E168" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearBorder. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G168" s="25" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="H168" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I168" s="25" t="inlineStr">
@@ -16135,12 +16135,12 @@
       </c>
       <c r="E169" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setShading. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G169" s="25" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="H169" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I169" s="25" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="E170" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F170" s="25" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearShading. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G170" s="25" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="H170" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I170" s="25" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E171" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>Run lists.create. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G171" s="25" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="H171" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I171" s="25" t="inlineStr">
@@ -16325,12 +16325,12 @@
       </c>
       <c r="E172" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>Run lists.attach. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G172" s="25" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="H172" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I172" s="25" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="E173" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>Run lists.detach. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G173" s="25" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="H173" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I173" s="25" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="E174" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>Run lists.join. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G174" s="25" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="H174" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I174" s="25" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E176" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>Run lists.separate. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G176" s="25" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="H176" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I176" s="25" t="inlineStr">
@@ -16655,12 +16655,12 @@
       </c>
       <c r="E177" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>Run lists.setLevel. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G177" s="25" t="inlineStr">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="H177" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I177" s="25" t="inlineStr">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="E178" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>Run lists.setValue. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G178" s="25" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="H178" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I178" s="25" t="inlineStr">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="E179" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>Run lists.continuePrevious. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G179" s="25" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="H179" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I179" s="25" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E181" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>Run lists.setLevelRestart. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G181" s="25" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="H181" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I181" s="25" t="inlineStr">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="E182" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>Run lists.convertToText. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G182" s="25" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="H182" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I182" s="25" t="inlineStr">
@@ -17129,12 +17129,12 @@
       </c>
       <c r="E184" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>Run tables.setDefaultStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G184" s="25" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="H184" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I184" s="25" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="E185" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>Run tables.clearDefaultStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G185" s="25" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H185" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I185" s="25" t="inlineStr">
@@ -17253,12 +17253,12 @@
       </c>
       <c r="E186" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>Run toc.markEntry. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G186" s="25" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="H186" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I186" s="25" t="inlineStr">
@@ -17315,12 +17315,12 @@
       </c>
       <c r="E187" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>Run toc.unmarkEntry. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G187" s="25" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="H187" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I187" s="25" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="E188" s="25" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>Run toc.listEntries. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G188" s="25" t="inlineStr">
@@ -17443,12 +17443,12 @@
       </c>
       <c r="E189" s="25" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F189" s="25" t="inlineStr">
         <is>
-          <t>Run toc.getEntry. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G189" s="25" t="inlineStr">
@@ -17509,12 +17509,12 @@
       </c>
       <c r="E190" s="25" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>Run toc.editEntry. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G190" s="25" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="H190" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I190" s="25" t="inlineStr">
@@ -17648,17 +17648,17 @@
       </c>
       <c r="D192" s="25" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E192" s="25" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F192" s="25" t="inlineStr">
         <is>
-          <t>Run history.undo. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G192" s="25" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="H192" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I192" s="25" t="inlineStr">
@@ -17710,17 +17710,17 @@
       </c>
       <c r="D193" s="25" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E193" s="25" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>Run history.redo. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G193" s="25" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="H193" s="25" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I193" s="25" t="inlineStr">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Run styles.apply. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr">
@@ -18253,12 +18253,12 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Run trackChanges.decide. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I201" s="4" t="inlineStr">
@@ -18311,12 +18311,12 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Run get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -18377,12 +18377,12 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Run markdownToFragment. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -18438,17 +18438,17 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Run clearContent. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I204" s="4" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Run blocks.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -18558,17 +18558,17 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Run blocks.deleteRange. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr">
@@ -18621,12 +18621,12 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Run format.paragraph.setDirection. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I207" s="4" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>Run format.paragraph.clearDirection. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I208" s="4" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Run lists.applyTemplate. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I209" s="4" t="inlineStr">
@@ -18795,12 +18795,12 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Run lists.applyPreset. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I210" s="4" t="inlineStr">
@@ -18853,12 +18853,12 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Run lists.captureTemplate. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -18915,12 +18915,12 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelNumbering. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I212" s="4" t="inlineStr">
@@ -18973,12 +18973,12 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelBullet. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I213" s="4" t="inlineStr">
@@ -19031,12 +19031,12 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelPictureBullet. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I214" s="4" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelAlignment. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr">
@@ -19147,12 +19147,12 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelIndents. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I216" s="4" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelTrailingCharacter. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I217" s="4" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelMarkerFont. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I218" s="4" t="inlineStr">
@@ -19321,12 +19321,12 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Run lists.clearLevelOverrides. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr">
@@ -19379,12 +19379,12 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Run lists.getStyle. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19445,12 +19445,12 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Run lists.applyStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I221" s="4" t="inlineStr">
@@ -19503,12 +19503,12 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Run lists.restartAt. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr">
@@ -19561,12 +19561,12 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelNumberStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr">
@@ -19619,12 +19619,12 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelText. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I224" s="4" t="inlineStr">
@@ -19677,12 +19677,12 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelStart. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Run lists.setLevelLayout. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
@@ -19793,12 +19793,12 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Run ranges.resolve. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -19859,12 +19859,12 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Run tables.applyStyle. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I228" s="4" t="inlineStr">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Run tables.setBorders. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I229" s="4" t="inlineStr">
@@ -19975,12 +19975,12 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Run tables.setTableOptions. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr">
@@ -20033,12 +20033,12 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Run create.image. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Run images.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -20157,12 +20157,12 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Run images.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Run images.delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I234" s="4" t="inlineStr">
@@ -20281,12 +20281,12 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>Run images.move. The targeted content should be moved from its original location to the requested location (for example, below/after the reference content). It should no longer appear at the old location.</t>
+          <t>Expected check: Moved "ABC" to below "XYZ". "ABC" should no longer appear in its old location.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I235" s="4" t="inlineStr">
@@ -20339,12 +20339,12 @@
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Run images.convertToInline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I236" s="4" t="inlineStr">
@@ -20397,12 +20397,12 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Run images.convertToFloating. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr">
@@ -20455,12 +20455,12 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>Run images.setSize. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I238" s="4" t="inlineStr">
@@ -20513,12 +20513,12 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>Run images.setWrapType. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I239" s="4" t="inlineStr">
@@ -20571,12 +20571,12 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Run images.setWrapSide. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr">
@@ -20629,12 +20629,12 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>Run images.setWrapDistances. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr">
@@ -20687,12 +20687,12 @@
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>Run images.setPosition. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I242" s="4" t="inlineStr">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Run images.setAnchorOptions. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I243" s="4" t="inlineStr">
@@ -20803,12 +20803,12 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>Run images.setZOrder. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -20818,7 +20818,7 @@
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr">
@@ -20861,12 +20861,12 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Run images.scale. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr">
@@ -20919,12 +20919,12 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>Run images.setLockAspectRatio. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -20934,7 +20934,7 @@
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I246" s="4" t="inlineStr">
@@ -20977,12 +20977,12 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>Run images.rotate. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>Run images.flip. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr">
@@ -21093,12 +21093,12 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>Run images.crop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr">
@@ -21151,12 +21151,12 @@
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>Run images.resetCrop. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Run images.replaceSource. The targeted content should be replaced with the new content, in the same location.</t>
+          <t>Expected check: Replaced "ABC" with "XYZ" at the same location.</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr">
@@ -21267,12 +21267,12 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>Run images.setAltText. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr">
@@ -21325,12 +21325,12 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Run images.setDecorative. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
@@ -21383,12 +21383,12 @@
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Run images.setName. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Run images.setHyperlink. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr">
@@ -21499,12 +21499,12 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>Run images.insertCaption. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr">
@@ -21557,12 +21557,12 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Run images.updateCaption. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I257" s="4" t="inlineStr">
@@ -21615,12 +21615,12 @@
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>Run images.removeCaption. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -21630,7 +21630,7 @@
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I258" s="4" t="inlineStr">
@@ -21673,12 +21673,12 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Run hyperlinks.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -21735,12 +21735,12 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>Run hyperlinks.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -21797,12 +21797,12 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Run hyperlinks.wrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I261" s="4" t="inlineStr">
@@ -21855,12 +21855,12 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>Run hyperlinks.insert. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I262" s="4" t="inlineStr">
@@ -21913,12 +21913,12 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Run hyperlinks.patch. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -21928,7 +21928,7 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I263" s="4" t="inlineStr">
@@ -21971,12 +21971,12 @@
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Run hyperlinks.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I264" s="4" t="inlineStr">
@@ -22029,12 +22029,12 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
@@ -22161,12 +22161,12 @@
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.resolve. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
@@ -22223,12 +22223,12 @@
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.refs.set. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -22238,7 +22238,7 @@
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I268" s="4" t="inlineStr">
@@ -22281,12 +22281,12 @@
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.refs.clear. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I269" s="4" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.refs.setLinkedToPrevious. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I270" s="4" t="inlineStr">
@@ -22397,12 +22397,12 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.parts.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
@@ -22459,12 +22459,12 @@
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.parts.create. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G272" s="4" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr">
@@ -22517,12 +22517,12 @@
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>Run headerFooters.parts.delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr">
@@ -22575,12 +22575,12 @@
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>Can execute without pre-existing target content (creates/inserts directly). Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Can run without existing selected content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>Run create.contentControl. New content should appear at the requested insertion point. Existing surrounding content should remain in place except where text reflow is expected.</t>
+          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
         </is>
       </c>
       <c r="G274" s="4" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr">
@@ -22699,12 +22699,12 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -22765,12 +22765,12 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.listInRange. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G277" s="4" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.selectByTag. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G278" s="4" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.selectByTitle. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G279" s="4" t="inlineStr">
@@ -22955,12 +22955,12 @@
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.listChildren. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
@@ -23021,12 +23021,12 @@
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.getParent. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr">
@@ -23087,12 +23087,12 @@
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.wrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G282" s="4" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr">
@@ -23145,12 +23145,12 @@
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.unwrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr">
@@ -23203,12 +23203,12 @@
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.delete. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G284" s="4" t="inlineStr">
@@ -23218,7 +23218,7 @@
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I284" s="4" t="inlineStr">
@@ -23261,12 +23261,12 @@
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.copy. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr">
@@ -23319,12 +23319,12 @@
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.move. The targeted content should be moved from its original location to the requested location (for example, below/after the reference content). It should no longer appear at the old location.</t>
+          <t>Expected check: Moved "ABC" to below "XYZ". "ABC" should no longer appear in its old location.</t>
         </is>
       </c>
       <c r="G286" s="4" t="inlineStr">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr">
@@ -23377,12 +23377,12 @@
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.patch. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
@@ -23435,12 +23435,12 @@
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.setLockMode. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -23450,7 +23450,7 @@
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I288" s="4" t="inlineStr">
@@ -23493,12 +23493,12 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.setType. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
@@ -23551,12 +23551,12 @@
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.getContent. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -23617,12 +23617,12 @@
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.replaceContent. The targeted content should be replaced with the new content, in the same location.</t>
+          <t>Expected check: Replaced "ABC" with "XYZ" at the same location.</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -23632,7 +23632,7 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
@@ -23675,12 +23675,12 @@
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.clearContent. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G292" s="4" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr">
@@ -23733,12 +23733,12 @@
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.appendContent. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G293" s="4" t="inlineStr">
@@ -23748,7 +23748,7 @@
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr">
@@ -23791,12 +23791,12 @@
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.prependContent. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -23806,7 +23806,7 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr">
@@ -23849,12 +23849,12 @@
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.insertBefore. The inserted content should appear immediately before the target content.</t>
+          <t>Expected check: Inserted "ABC" immediately before "XYZ".</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
@@ -23907,12 +23907,12 @@
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.insertAfter. The inserted content should appear immediately after the target content.</t>
+          <t>Expected check: Inserted "ABC" immediately after "XYZ".</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -23922,7 +23922,7 @@
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr">
@@ -23965,12 +23965,12 @@
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.getBinding. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G297" s="4" t="inlineStr">
@@ -24031,12 +24031,12 @@
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.setBinding. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I298" s="4" t="inlineStr">
@@ -24089,12 +24089,12 @@
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.clearBinding. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G299" s="4" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">
@@ -24147,12 +24147,12 @@
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.getRawProperties. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -24213,12 +24213,12 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.patchRawProperties. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
@@ -24271,12 +24271,12 @@
       </c>
       <c r="E302" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.validateWordCompatibility. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -24333,12 +24333,12 @@
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.normalizeWordCompatibility. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
@@ -24391,12 +24391,12 @@
       </c>
       <c r="E304" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.normalizeTagPayload. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
@@ -24449,12 +24449,12 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.text.setMultiline. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
@@ -24507,12 +24507,12 @@
       </c>
       <c r="E306" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.text.setValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
@@ -24565,12 +24565,12 @@
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.text.clearValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
@@ -24623,12 +24623,12 @@
       </c>
       <c r="E308" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.date.setValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
@@ -24681,12 +24681,12 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.date.clearValue. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
@@ -24739,12 +24739,12 @@
       </c>
       <c r="E310" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.date.setDisplayFormat. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -24754,7 +24754,7 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.date.setDisplayLocale. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
@@ -24855,12 +24855,12 @@
       </c>
       <c r="E312" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.date.setStorageFormat. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
@@ -24870,7 +24870,7 @@
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
@@ -24913,12 +24913,12 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.date.setCalendar. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
@@ -24971,12 +24971,12 @@
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.checkbox.getState. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G314" s="4" t="inlineStr">
@@ -25033,12 +25033,12 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.checkbox.setState. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
@@ -25091,12 +25091,12 @@
       </c>
       <c r="E316" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.checkbox.toggle. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G316" s="4" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
@@ -25149,12 +25149,12 @@
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.checkbox.setSymbolPair. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -25164,7 +25164,7 @@
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="E318" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.choiceList.getItems. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -25269,12 +25269,12 @@
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.choiceList.setItems. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="E320" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.choiceList.setSelected. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G320" s="4" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.repeatingSection.listItems. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -25447,12 +25447,12 @@
       </c>
       <c r="E322" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.repeatingSection.insertItemBefore. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -25462,7 +25462,7 @@
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
@@ -25505,12 +25505,12 @@
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.repeatingSection.insertItemAfter. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -25520,7 +25520,7 @@
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
@@ -25563,12 +25563,12 @@
       </c>
       <c r="E324" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.repeatingSection.cloneItem. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
@@ -25621,12 +25621,12 @@
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.repeatingSection.deleteItem. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G325" s="4" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
@@ -25679,12 +25679,12 @@
       </c>
       <c r="E326" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.repeatingSection.setAllowInsertDelete. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
@@ -25737,12 +25737,12 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.group.wrap. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
@@ -25795,12 +25795,12 @@
       </c>
       <c r="E328" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>Run contentControls.group.ungroup. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -25810,7 +25810,7 @@
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
@@ -25853,12 +25853,12 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Run bookmarks.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -25919,12 +25919,12 @@
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>Run bookmarks.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -25985,12 +25985,12 @@
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Run bookmarks.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I331" s="4" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="E332" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>Run bookmarks.rename. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -26058,7 +26058,7 @@
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I332" s="4" t="inlineStr">
@@ -26101,12 +26101,12 @@
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Run bookmarks.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G333" s="4" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I333" s="4" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="E334" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Run footnotes.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -26225,12 +26225,12 @@
       </c>
       <c r="E335" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Run footnotes.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -26291,12 +26291,12 @@
       </c>
       <c r="E336" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Run footnotes.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I336" s="4" t="inlineStr">
@@ -26349,12 +26349,12 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Run footnotes.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I337" s="4" t="inlineStr">
@@ -26407,12 +26407,12 @@
       </c>
       <c r="E338" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>Run footnotes.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="H338" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I338" s="4" t="inlineStr">
@@ -26465,12 +26465,12 @@
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Run footnotes.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -26480,7 +26480,7 @@
       </c>
       <c r="H339" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I339" s="4" t="inlineStr">
@@ -26523,12 +26523,12 @@
       </c>
       <c r="E340" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>Run crossRefs.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -26589,12 +26589,12 @@
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Run crossRefs.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G341" s="4" t="inlineStr">
@@ -26655,12 +26655,12 @@
       </c>
       <c r="E342" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>Run crossRefs.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G342" s="4" t="inlineStr">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="H342" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I342" s="4" t="inlineStr">
@@ -26713,12 +26713,12 @@
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>Run crossRefs.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I343" s="4" t="inlineStr">
@@ -26771,12 +26771,12 @@
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>Run crossRefs.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="H344" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I344" s="4" t="inlineStr">
@@ -26829,12 +26829,12 @@
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>Run index.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -26895,12 +26895,12 @@
       </c>
       <c r="E346" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>Run index.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -26961,12 +26961,12 @@
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Run index.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G347" s="4" t="inlineStr">
@@ -26976,7 +26976,7 @@
       </c>
       <c r="H347" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I347" s="4" t="inlineStr">
@@ -27019,12 +27019,12 @@
       </c>
       <c r="E348" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>Run index.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="H348" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I348" s="4" t="inlineStr">
@@ -27077,12 +27077,12 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>Run index.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H349" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I349" s="4" t="inlineStr">
@@ -27135,12 +27135,12 @@
       </c>
       <c r="E350" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>Run index.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="H350" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I350" s="4" t="inlineStr">
@@ -27193,12 +27193,12 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Run index.entries.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -27255,12 +27255,12 @@
       </c>
       <c r="E352" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>Run index.entries.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
@@ -27317,12 +27317,12 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>Run index.entries.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I353" s="4" t="inlineStr">
@@ -27375,12 +27375,12 @@
       </c>
       <c r="E354" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Run index.entries.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I354" s="4" t="inlineStr">
@@ -27433,12 +27433,12 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Run index.entries.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="H355" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I355" s="4" t="inlineStr">
@@ -27491,12 +27491,12 @@
       </c>
       <c r="E356" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>Run captions.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -27557,12 +27557,12 @@
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Run captions.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -27623,12 +27623,12 @@
       </c>
       <c r="E358" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Run captions.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -27638,7 +27638,7 @@
       </c>
       <c r="H358" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I358" s="4" t="inlineStr">
@@ -27681,12 +27681,12 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Run captions.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -27696,7 +27696,7 @@
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I359" s="4" t="inlineStr">
@@ -27739,12 +27739,12 @@
       </c>
       <c r="E360" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Run captions.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I360" s="4" t="inlineStr">
@@ -27797,12 +27797,12 @@
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Run captions.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I361" s="4" t="inlineStr">
@@ -27855,12 +27855,12 @@
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>Run fields.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -27921,12 +27921,12 @@
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Run fields.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E364" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>Run fields.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -28002,7 +28002,7 @@
       </c>
       <c r="H364" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I364" s="4" t="inlineStr">
@@ -28045,12 +28045,12 @@
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Run fields.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H365" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I365" s="4" t="inlineStr">
@@ -28103,12 +28103,12 @@
       </c>
       <c r="E366" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>Run fields.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I366" s="4" t="inlineStr">
@@ -28161,12 +28161,12 @@
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Run citations.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -28227,12 +28227,12 @@
       </c>
       <c r="E368" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>Run citations.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G368" s="4" t="inlineStr">
@@ -28293,12 +28293,12 @@
       </c>
       <c r="E369" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Run citations.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I369" s="4" t="inlineStr">
@@ -28351,12 +28351,12 @@
       </c>
       <c r="E370" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>Run citations.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="H370" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I370" s="4" t="inlineStr">
@@ -28409,12 +28409,12 @@
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>Run citations.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -28424,7 +28424,7 @@
       </c>
       <c r="H371" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I371" s="4" t="inlineStr">
@@ -28467,12 +28467,12 @@
       </c>
       <c r="E372" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
-          <t>Run citations.sources.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -28529,12 +28529,12 @@
       </c>
       <c r="E373" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Run citations.sources.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -28591,12 +28591,12 @@
       </c>
       <c r="E374" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>Run citations.sources.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G374" s="4" t="inlineStr">
@@ -28606,7 +28606,7 @@
       </c>
       <c r="H374" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I374" s="4" t="inlineStr">
@@ -28649,12 +28649,12 @@
       </c>
       <c r="E375" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Run citations.sources.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G375" s="4" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="H375" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I375" s="4" t="inlineStr">
@@ -28707,12 +28707,12 @@
       </c>
       <c r="E376" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>Run citations.sources.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G376" s="4" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I376" s="4" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Run citations.bibliography.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G377" s="4" t="inlineStr">
@@ -28827,12 +28827,12 @@
       </c>
       <c r="E378" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>Run citations.bibliography.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G378" s="4" t="inlineStr">
@@ -28842,7 +28842,7 @@
       </c>
       <c r="H378" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I378" s="4" t="inlineStr">
@@ -28885,12 +28885,12 @@
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Run citations.bibliography.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="H379" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I379" s="4" t="inlineStr">
@@ -28943,12 +28943,12 @@
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>Run citations.bibliography.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -28958,7 +28958,7 @@
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I380" s="4" t="inlineStr">
@@ -29001,12 +29001,12 @@
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Run citations.bibliography.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G381" s="4" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="H381" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I381" s="4" t="inlineStr">
@@ -29059,12 +29059,12 @@
       </c>
       <c r="E382" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G382" s="4" t="inlineStr">
@@ -29125,12 +29125,12 @@
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -29191,12 +29191,12 @@
       </c>
       <c r="E384" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G384" s="4" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="H384" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I384" s="4" t="inlineStr">
@@ -29249,12 +29249,12 @@
       </c>
       <c r="E385" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.configure. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -29264,7 +29264,7 @@
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I385" s="4" t="inlineStr">
@@ -29307,12 +29307,12 @@
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.rebuild. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G386" s="4" t="inlineStr">
@@ -29322,7 +29322,7 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I386" s="4" t="inlineStr">
@@ -29365,12 +29365,12 @@
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G387" s="4" t="inlineStr">
@@ -29380,7 +29380,7 @@
       </c>
       <c r="H387" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I387" s="4" t="inlineStr">
@@ -29423,12 +29423,12 @@
       </c>
       <c r="E388" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.entries.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -29485,12 +29485,12 @@
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.entries.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -29547,12 +29547,12 @@
       </c>
       <c r="E390" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.entries.insert. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I390" s="4" t="inlineStr">
@@ -29605,12 +29605,12 @@
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.entries.update. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr">
@@ -29620,7 +29620,7 @@
       </c>
       <c r="H391" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I391" s="4" t="inlineStr">
@@ -29663,12 +29663,12 @@
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>Run authorities.entries.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="H392" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I392" s="4" t="inlineStr">
@@ -29721,12 +29721,12 @@
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Run diff.capture. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G393" s="4" t="inlineStr">
@@ -29787,12 +29787,12 @@
       </c>
       <c r="E394" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>Run diff.compare. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -29848,17 +29848,17 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports tracked changes mode. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Run diff.apply. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
@@ -29868,7 +29868,7 @@
       </c>
       <c r="H395" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I395" s="4" t="inlineStr">
@@ -29911,12 +29911,12 @@
       </c>
       <c r="E396" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>Run protection.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
@@ -29972,17 +29972,17 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Run protection.setEditingRestriction. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
@@ -29992,7 +29992,7 @@
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I397" s="4" t="inlineStr">
@@ -30030,17 +30030,17 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
-          <t>Target requirement depends on the input shape and whether a target/ref is supplied. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>Run protection.clearEditingRestriction. The exact targeted content should change according to the input. Verify the change is visible in the output DOCX at the intended location.</t>
+          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -30050,7 +30050,7 @@
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I398" s="4" t="inlineStr">
@@ -30093,12 +30093,12 @@
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Run permissionRanges.list. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -30159,12 +30159,12 @@
       </c>
       <c r="E400" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it validates/document-queries state and does not write changes to the DOCX.</t>
+          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
         </is>
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>Run permissionRanges.get. The command should return data only, and the output DOCX should look exactly the same as before (no visible edits).</t>
+          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -30225,12 +30225,12 @@
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Run permissionRanges.create. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -30240,7 +30240,7 @@
       </c>
       <c r="H401" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I401" s="4" t="inlineStr">
@@ -30283,12 +30283,12 @@
       </c>
       <c r="E402" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>Run permissionRanges.remove. The targeted content should be removed and should no longer appear in the document.</t>
+          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
         </is>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -30298,7 +30298,7 @@
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I402" s="4" t="inlineStr">
@@ -30341,12 +30341,12 @@
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>Needs an existing valid target (node/ref/selection) in the starter DOCX before execution. Supports dry-run planning before apply. Mutates document content or formatting when applied.</t>
+          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Run permissionRanges.updatePrincipal. The targeted content should stay in the same location, but its specified property should change (format/layout/metadata) according to the input.</t>
+          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
-          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit target + fixture doc.</t>
+          <t>No dedicated harness script yet; execute via SDK/CLI operation call with explicit fixture.</t>
         </is>
       </c>
       <c r="I403" s="4" t="inlineStr">

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -834,12 +834,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
+          <t>Can run without selecting existing content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
+          <t>Can run without selecting existing content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
+          <t>Can run without selecting existing content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run. Supports tracked changes.</t>
+          <t>Can run without selecting existing content. Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Replaced "ABC" with "XYZ" at the same location.</t>
+          <t>Expected check: Replace "apples" with "bananas" at the same location in the document.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.apply should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Its font size should visibly change compared with nearby text.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Its typeface should change (for example to Courier New) while content remains "bananas".</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". The text color should visibly change (for example to red) while the words stay the same.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply comments.create and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply comments.patch and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Inserted a row next to row containing "ABC"; new row appears directly above/below as requested.</t>
+          <t>Expected check: In the table row containing "bananas", insert a new adjacent row above/below as requested.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Inserted a column next to column containing "ABC"; new column appears directly left/right as requested.</t>
+          <t>Expected check: In the table column containing "bananas", insert a new adjacent column left/right as requested.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should render in bold while nearby "apples" stays regular.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should render in italics while nearby "apples" stays upright.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should have a visible underline.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Converted table cells "ABC" and "XYZ" into plain text at the same location.</t>
+          <t>Expected check: Convert table cells "bananas" and "apples" into plain text in the same location.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Merged adjacent cells containing "ABC" and "XYZ" into one cell.</t>
+          <t>Expected check: Merge cells containing "bananas" and "apples" into one cell.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Split merged cell containing "ABC" into multiple cells.</t>
+          <t>Expected check: Split the merged cell containing "bananas" into multiple cells.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Split merged cell containing "ABC" into multiple cells.</t>
+          <t>Expected check: Split the merged cell containing "bananas" into multiple cells.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports tracked changes.</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply mutations.apply and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Expected check: Converted text line "ABC | XYZ" into table cells ("ABC" and "XYZ" in separate cells).</t>
+          <t>Expected check: Convert plain text line "bananas | apples" into table cells.</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E86" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Moved "ABC" to below "XYZ". "ABC" should no longer appear in its old location.</t>
+          <t>Expected check: Move sentence "bananas are ripe." to directly below heading "Shopping List". It should disappear from its old location.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="E87" s="22" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run.</t>
+          <t>Can run without selecting existing content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="E88" s="22" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run.</t>
+          <t>Can run without selecting existing content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="E89" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="E90" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="E93" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="E94" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="E95" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr">
@@ -11156,12 +11156,12 @@
       </c>
       <c r="E96" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -11222,12 +11222,12 @@
       </c>
       <c r="E97" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="E98" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="E99" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="E100" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="E101" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G101" s="22" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="E102" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="E103" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G103" s="22" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="E104" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E105" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G105" s="22" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E106" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="E107" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
         </is>
       </c>
       <c r="G107" s="22" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="E110" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="E111" s="22" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
         </is>
       </c>
       <c r="G111" s="22" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="E112" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should have a single strike-through line.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="E113" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should have a bright yellow marker-style highlight behind the text.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="E114" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.shading should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G114" s="25" t="inlineStr">
@@ -12494,12 +12494,12 @@
       </c>
       <c r="E115" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.border should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G115" s="25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E116" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F116" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should show an outlined glyph effect.</t>
         </is>
       </c>
       <c r="G116" s="25" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="E117" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F117" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should show a visible text shadow effect.</t>
         </is>
       </c>
       <c r="G117" s="25" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="E118" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should show an embossed text effect.</t>
         </is>
       </c>
       <c r="G118" s="25" t="inlineStr">
@@ -12786,12 +12786,12 @@
       </c>
       <c r="E119" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should show an imprinted/debossed text effect.</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="E120" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F120" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.vertAlign should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G120" s="25" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="E121" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F121" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.position should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G121" s="25" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="E122" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.rtl should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="E123" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F123" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.cs should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G123" s="25" t="inlineStr">
@@ -13144,12 +13144,12 @@
       </c>
       <c r="E124" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F124" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.bCs should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G124" s="25" t="inlineStr">
@@ -13210,12 +13210,12 @@
       </c>
       <c r="E125" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F125" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.iCs should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G125" s="25" t="inlineStr">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="E126" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F126" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.vanish should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G126" s="25" t="inlineStr">
@@ -13346,12 +13346,12 @@
       </c>
       <c r="E127" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F127" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.webHidden should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G127" s="25" t="inlineStr">
@@ -13416,12 +13416,12 @@
       </c>
       <c r="E128" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.specVanish should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="E129" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.snapToGrid should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G129" s="25" t="inlineStr">
@@ -13556,12 +13556,12 @@
       </c>
       <c r="E130" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F130" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.oMath should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G130" s="25" t="inlineStr">
@@ -13630,12 +13630,12 @@
       </c>
       <c r="E131" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.fontSizeCs should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G131" s="25" t="inlineStr">
@@ -13696,12 +13696,12 @@
       </c>
       <c r="E132" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.charScale should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G132" s="25" t="inlineStr">
@@ -13766,12 +13766,12 @@
       </c>
       <c r="E133" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.kerning should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G133" s="25" t="inlineStr">
@@ -13836,12 +13836,12 @@
       </c>
       <c r="E134" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.fitText should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="E135" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.lang should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G135" s="25" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="E136" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.rStyle should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="E137" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.rFonts should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G137" s="25" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="E138" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.eastAsianLayout should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G138" s="25" t="inlineStr">
@@ -14166,12 +14166,12 @@
       </c>
       <c r="E139" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.em should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G139" s="25" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="E140" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.ligatures should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G140" s="25" t="inlineStr">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="E141" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F141" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.numForm should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G141" s="25" t="inlineStr">
@@ -14364,12 +14364,12 @@
       </c>
       <c r="E142" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.numSpacing should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G142" s="25" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="E143" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F143" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.stylisticSets should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G143" s="25" t="inlineStr">
@@ -14496,12 +14496,12 @@
       </c>
       <c r="E144" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.contextualAlternates should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G144" s="25" t="inlineStr">
@@ -14566,12 +14566,12 @@
       </c>
       <c r="E145" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F145" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should have a double strike-through line.</t>
         </is>
       </c>
       <c r="G145" s="25" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E146" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F146" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should display in small caps.</t>
         </is>
       </c>
       <c r="G146" s="25" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="E147" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F147" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". It should display in all caps.</t>
         </is>
       </c>
       <c r="G147" s="25" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="E148" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run. Supports tracked changes.</t>
         </is>
       </c>
       <c r="F148" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Letters should be spaced farther apart or tighter based on input.</t>
         </is>
       </c>
       <c r="G148" s="25" t="inlineStr">
@@ -15073,12 +15073,12 @@
       </c>
       <c r="E152" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F152" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Apply style to text/paragraph containing "bananas" and verify only intended styling changes.</t>
         </is>
       </c>
       <c r="G152" s="25" t="inlineStr">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="E153" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F153" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Apply style to text/paragraph containing "bananas" and verify only intended styling changes.</t>
         </is>
       </c>
       <c r="G153" s="25" t="inlineStr">
@@ -15197,12 +15197,12 @@
       </c>
       <c r="E154" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F154" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.resetDirectFormatting should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G154" s="25" t="inlineStr">
@@ -15259,12 +15259,12 @@
       </c>
       <c r="E155" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F155" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setAlignment should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G155" s="25" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E156" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F156" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearAlignment should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G156" s="25" t="inlineStr">
@@ -15383,12 +15383,12 @@
       </c>
       <c r="E157" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setIndentation should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G157" s="25" t="inlineStr">
@@ -15449,12 +15449,12 @@
       </c>
       <c r="E158" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F158" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearIndentation should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G158" s="25" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="E159" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F159" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setSpacing should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G159" s="25" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E160" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F160" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearSpacing should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G160" s="25" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E161" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F161" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setKeepOptions should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G161" s="25" t="inlineStr">
@@ -15701,12 +15701,12 @@
       </c>
       <c r="E162" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setOutlineLevel should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G162" s="25" t="inlineStr">
@@ -15763,12 +15763,12 @@
       </c>
       <c r="E163" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F163" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setFlowOptions should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G163" s="25" t="inlineStr">
@@ -15825,12 +15825,12 @@
       </c>
       <c r="E164" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F164" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setTabStop should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G164" s="25" t="inlineStr">
@@ -15887,12 +15887,12 @@
       </c>
       <c r="E165" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F165" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearTabStop should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G165" s="25" t="inlineStr">
@@ -15949,12 +15949,12 @@
       </c>
       <c r="E166" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F166" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearAllTabStops should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G166" s="25" t="inlineStr">
@@ -16011,12 +16011,12 @@
       </c>
       <c r="E167" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F167" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setBorder should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G167" s="25" t="inlineStr">
@@ -16073,12 +16073,12 @@
       </c>
       <c r="E168" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearBorder should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G168" s="25" t="inlineStr">
@@ -16135,12 +16135,12 @@
       </c>
       <c r="E169" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setShading should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G169" s="25" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="E170" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F170" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearShading should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G170" s="25" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E171" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G171" s="25" t="inlineStr">
@@ -16325,12 +16325,12 @@
       </c>
       <c r="E172" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G172" s="25" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="E173" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G173" s="25" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="E174" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G174" s="25" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E176" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G176" s="25" t="inlineStr">
@@ -16655,12 +16655,12 @@
       </c>
       <c r="E177" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G177" s="25" t="inlineStr">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="E178" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G178" s="25" t="inlineStr">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="E179" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G179" s="25" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E181" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G181" s="25" t="inlineStr">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="E182" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G182" s="25" t="inlineStr">
@@ -17129,12 +17129,12 @@
       </c>
       <c r="E184" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G184" s="25" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="E185" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G185" s="25" t="inlineStr">
@@ -17253,12 +17253,12 @@
       </c>
       <c r="E186" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
         </is>
       </c>
       <c r="G186" s="25" t="inlineStr">
@@ -17315,12 +17315,12 @@
       </c>
       <c r="E187" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
         </is>
       </c>
       <c r="G187" s="25" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="E188" s="25" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G188" s="25" t="inlineStr">
@@ -17443,12 +17443,12 @@
       </c>
       <c r="E189" s="25" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F189" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G189" s="25" t="inlineStr">
@@ -17509,12 +17509,12 @@
       </c>
       <c r="E190" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
         </is>
       </c>
       <c r="G190" s="25" t="inlineStr">
@@ -17653,12 +17653,12 @@
       </c>
       <c r="E192" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F192" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply history.undo and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G192" s="25" t="inlineStr">
@@ -17715,12 +17715,12 @@
       </c>
       <c r="E193" s="25" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply history.redo and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G193" s="25" t="inlineStr">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Apply style to text/paragraph containing "bananas" and verify only intended styling changes.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -18253,12 +18253,12 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: On revision affecting "bananas", accept/reject as requested and verify final visible text state.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -18311,12 +18311,12 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -18377,12 +18377,12 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -18443,12 +18443,12 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX.</t>
+          <t>Requires an existing valid target (node/ref/selection).</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -18563,12 +18563,12 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18621,12 +18621,12 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setDirection should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearDirection should change; word content and position should not move.</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -18737,12 +18737,12 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -18795,12 +18795,12 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -18853,12 +18853,12 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -18915,12 +18915,12 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -18973,12 +18973,12 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -19031,12 +19031,12 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -19147,12 +19147,12 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -19321,12 +19321,12 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -19379,12 +19379,12 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19445,12 +19445,12 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -19503,12 +19503,12 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -19561,12 +19561,12 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -19619,12 +19619,12 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -19677,12 +19677,12 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -19793,12 +19793,12 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -19859,12 +19859,12 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -19917,12 +19917,12 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -19975,12 +19975,12 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -20033,12 +20033,12 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run.</t>
+          <t>Can run without selecting existing content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -20157,12 +20157,12 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -20281,12 +20281,12 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Moved "ABC" to below "XYZ". "ABC" should no longer appear in its old location.</t>
+          <t>Expected check: Move sentence "bananas are ripe." to directly below heading "Shopping List". It should disappear from its old location.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -20339,12 +20339,12 @@
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -20397,12 +20397,12 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -20455,12 +20455,12 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -20513,12 +20513,12 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -20571,12 +20571,12 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -20629,12 +20629,12 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -20687,12 +20687,12 @@
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
@@ -20803,12 +20803,12 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -20861,12 +20861,12 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -20919,12 +20919,12 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -20977,12 +20977,12 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -21093,12 +21093,12 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -21151,12 +21151,12 @@
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Replaced "ABC" with "XYZ" at the same location.</t>
+          <t>Expected check: Replace "apples" with "bananas" at the same location in the document.</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -21267,12 +21267,12 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -21325,12 +21325,12 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -21383,12 +21383,12 @@
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -21499,12 +21499,12 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -21557,12 +21557,12 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -21615,12 +21615,12 @@
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -21673,12 +21673,12 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -21735,12 +21735,12 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -21797,12 +21797,12 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On text "bananas", apply hyperlink change and verify it appears/updates/removes as requested.</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -21855,12 +21855,12 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On text "bananas", apply hyperlink change and verify it appears/updates/removes as requested.</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -21913,12 +21913,12 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On text "bananas", apply hyperlink change and verify it appears/updates/removes as requested.</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -21971,12 +21971,12 @@
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
@@ -22029,12 +22029,12 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
@@ -22161,12 +22161,12 @@
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
@@ -22223,12 +22223,12 @@
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -22281,12 +22281,12 @@
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -22397,12 +22397,12 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
@@ -22459,12 +22459,12 @@
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
         </is>
       </c>
       <c r="G272" s="4" t="inlineStr">
@@ -22517,12 +22517,12 @@
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr">
@@ -22575,12 +22575,12 @@
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>Can run without existing selected content. Supports dry-run.</t>
+          <t>Can run without selecting existing content. Supports dry-run.</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" at the requested location (for example, after "XYZ"). "XYZ" remains and "ABC" appears in the new spot.</t>
+          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
         </is>
       </c>
       <c r="G274" s="4" t="inlineStr">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr">
@@ -22699,12 +22699,12 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -22765,12 +22765,12 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G277" s="4" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G278" s="4" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G279" s="4" t="inlineStr">
@@ -22955,12 +22955,12 @@
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
@@ -23021,12 +23021,12 @@
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr">
@@ -23087,12 +23087,12 @@
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G282" s="4" t="inlineStr">
@@ -23145,12 +23145,12 @@
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -23203,12 +23203,12 @@
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G284" s="4" t="inlineStr">
@@ -23261,12 +23261,12 @@
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -23319,12 +23319,12 @@
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Moved "ABC" to below "XYZ". "ABC" should no longer appear in its old location.</t>
+          <t>Expected check: Move sentence "bananas are ripe." to directly below heading "Shopping List". It should disappear from its old location.</t>
         </is>
       </c>
       <c r="G286" s="4" t="inlineStr">
@@ -23377,12 +23377,12 @@
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">
@@ -23435,12 +23435,12 @@
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -23493,12 +23493,12 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -23551,12 +23551,12 @@
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -23617,12 +23617,12 @@
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Replaced "ABC" with "XYZ" at the same location.</t>
+          <t>Expected check: Replace "apples" with "bananas" at the same location in the document.</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -23675,12 +23675,12 @@
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G292" s="4" t="inlineStr">
@@ -23733,12 +23733,12 @@
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G293" s="4" t="inlineStr">
@@ -23791,12 +23791,12 @@
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -23849,12 +23849,12 @@
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" immediately before "XYZ".</t>
+          <t>Expected check: Insert "bananas" immediately before "XYZ".</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -23907,12 +23907,12 @@
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Inserted "ABC" immediately after "XYZ".</t>
+          <t>Expected check: Insert "bananas" immediately after "XYZ".</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -23965,12 +23965,12 @@
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G297" s="4" t="inlineStr">
@@ -24031,12 +24031,12 @@
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
@@ -24089,12 +24089,12 @@
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G299" s="4" t="inlineStr">
@@ -24147,12 +24147,12 @@
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -24213,12 +24213,12 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr">
@@ -24271,12 +24271,12 @@
       </c>
       <c r="E302" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -24333,12 +24333,12 @@
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr">
@@ -24391,12 +24391,12 @@
       </c>
       <c r="E304" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -24449,12 +24449,12 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -24507,12 +24507,12 @@
       </c>
       <c r="E306" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -24565,12 +24565,12 @@
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -24623,12 +24623,12 @@
       </c>
       <c r="E308" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
@@ -24681,12 +24681,12 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
@@ -24739,12 +24739,12 @@
       </c>
       <c r="E310" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -24855,12 +24855,12 @@
       </c>
       <c r="E312" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
@@ -24913,12 +24913,12 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -24971,12 +24971,12 @@
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G314" s="4" t="inlineStr">
@@ -25033,12 +25033,12 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -25091,12 +25091,12 @@
       </c>
       <c r="E316" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G316" s="4" t="inlineStr">
@@ -25149,12 +25149,12 @@
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="E318" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -25269,12 +25269,12 @@
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="E320" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G320" s="4" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -25447,12 +25447,12 @@
       </c>
       <c r="E322" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -25505,12 +25505,12 @@
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -25563,12 +25563,12 @@
       </c>
       <c r="E324" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -25621,12 +25621,12 @@
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G325" s="4" t="inlineStr">
@@ -25679,12 +25679,12 @@
       </c>
       <c r="E326" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -25737,12 +25737,12 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -25795,12 +25795,12 @@
       </c>
       <c r="E328" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -25853,12 +25853,12 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -25919,12 +25919,12 @@
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -25985,12 +25985,12 @@
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply bookmarks.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="E332" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply bookmarks.rename and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -26101,12 +26101,12 @@
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G333" s="4" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="E334" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -26225,12 +26225,12 @@
       </c>
       <c r="E335" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -26291,12 +26291,12 @@
       </c>
       <c r="E336" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply footnotes.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -26349,12 +26349,12 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply footnotes.update and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -26407,12 +26407,12 @@
       </c>
       <c r="E338" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -26465,12 +26465,12 @@
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply footnotes.configure and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -26523,12 +26523,12 @@
       </c>
       <c r="E340" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -26589,12 +26589,12 @@
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G341" s="4" t="inlineStr">
@@ -26655,12 +26655,12 @@
       </c>
       <c r="E342" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply crossRefs.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G342" s="4" t="inlineStr">
@@ -26713,12 +26713,12 @@
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply crossRefs.rebuild and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -26771,12 +26771,12 @@
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -26829,12 +26829,12 @@
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -26895,12 +26895,12 @@
       </c>
       <c r="E346" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -26961,12 +26961,12 @@
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply index.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G347" s="4" t="inlineStr">
@@ -27019,12 +27019,12 @@
       </c>
       <c r="E348" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply index.configure and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
@@ -27077,12 +27077,12 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply index.rebuild and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -27135,12 +27135,12 @@
       </c>
       <c r="E350" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -27193,12 +27193,12 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -27255,12 +27255,12 @@
       </c>
       <c r="E352" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
@@ -27317,12 +27317,12 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply index.entries.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -27375,12 +27375,12 @@
       </c>
       <c r="E354" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply index.entries.update and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -27433,12 +27433,12 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -27491,12 +27491,12 @@
       </c>
       <c r="E356" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -27557,12 +27557,12 @@
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -27623,12 +27623,12 @@
       </c>
       <c r="E358" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply captions.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -27681,12 +27681,12 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply captions.update and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -27739,12 +27739,12 @@
       </c>
       <c r="E360" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -27797,12 +27797,12 @@
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply captions.configure and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -27855,12 +27855,12 @@
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -27921,12 +27921,12 @@
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E364" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply fields.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -28045,12 +28045,12 @@
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply fields.rebuild and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -28103,12 +28103,12 @@
       </c>
       <c r="E366" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -28161,12 +28161,12 @@
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -28227,12 +28227,12 @@
       </c>
       <c r="E368" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G368" s="4" t="inlineStr">
@@ -28293,12 +28293,12 @@
       </c>
       <c r="E369" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -28351,12 +28351,12 @@
       </c>
       <c r="E370" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.update and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -28409,12 +28409,12 @@
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -28467,12 +28467,12 @@
       </c>
       <c r="E372" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -28529,12 +28529,12 @@
       </c>
       <c r="E373" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -28591,12 +28591,12 @@
       </c>
       <c r="E374" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.sources.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G374" s="4" t="inlineStr">
@@ -28649,12 +28649,12 @@
       </c>
       <c r="E375" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.sources.update and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G375" s="4" t="inlineStr">
@@ -28707,12 +28707,12 @@
       </c>
       <c r="E376" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G376" s="4" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G377" s="4" t="inlineStr">
@@ -28827,12 +28827,12 @@
       </c>
       <c r="E378" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.bibliography.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G378" s="4" t="inlineStr">
@@ -28885,12 +28885,12 @@
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.bibliography.rebuild and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr">
@@ -28943,12 +28943,12 @@
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply citations.bibliography.configure and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -29001,12 +29001,12 @@
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G381" s="4" t="inlineStr">
@@ -29059,12 +29059,12 @@
       </c>
       <c r="E382" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G382" s="4" t="inlineStr">
@@ -29125,12 +29125,12 @@
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -29191,12 +29191,12 @@
       </c>
       <c r="E384" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply authorities.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G384" s="4" t="inlineStr">
@@ -29249,12 +29249,12 @@
       </c>
       <c r="E385" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply authorities.configure and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -29307,12 +29307,12 @@
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply authorities.rebuild and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G386" s="4" t="inlineStr">
@@ -29365,12 +29365,12 @@
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G387" s="4" t="inlineStr">
@@ -29423,12 +29423,12 @@
       </c>
       <c r="E388" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -29485,12 +29485,12 @@
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -29547,12 +29547,12 @@
       </c>
       <c r="E390" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply authorities.entries.insert and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -29605,12 +29605,12 @@
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply authorities.entries.update and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr">
@@ -29663,12 +29663,12 @@
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -29721,12 +29721,12 @@
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G393" s="4" t="inlineStr">
@@ -29787,12 +29787,12 @@
       </c>
       <c r="E394" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -29853,12 +29853,12 @@
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports tracked changes.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports tracked changes.</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply diff.apply and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
@@ -29911,12 +29911,12 @@
       </c>
       <c r="E396" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
@@ -29977,12 +29977,12 @@
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply protection.setEditingRestriction and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
@@ -30035,12 +30035,12 @@
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Changed "ABC" as requested and verify final placement/state against "XYZ" context.</t>
+          <t>Expected check: Apply protection.clearEditingRestriction and verify explicit before/after change around sample text "bananas".</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -30093,12 +30093,12 @@
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -30159,12 +30159,12 @@
       </c>
       <c r="E400" s="4" t="inlineStr">
         <is>
-          <t>Read-only operation; it returns data and should not change DOCX visuals.</t>
+          <t>Read-only operation; returns data and should not change visible DOCX content.</t>
         </is>
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Read data only. DOCX should look unchanged before vs after. Example: Looked up "ABC" and returned metadata without editing document text.</t>
+          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -30225,12 +30225,12 @@
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Create/update permission range around text "bananas" and verify protected/editable region boundaries.</t>
         </is>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -30283,12 +30283,12 @@
       </c>
       <c r="E402" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Deleted "ABC". "ABC" should no longer appear anywhere in the edited region.</t>
+          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
         </is>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -30341,12 +30341,12 @@
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>Needs a valid existing node/ref/selection in the starter DOCX. Supports dry-run.</t>
+          <t>Requires an existing valid target (node/ref/selection). Supports dry-run.</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Kept text "ABC" in place but changed the requested property (format/layout/metadata). Example: "ABC" stayed in place and style changed while neighboring "XYZ" stayed unchanged.</t>
+          <t>Expected check: Create/update permission range around text "bananas" and verify protected/editable region boundaries.</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr">

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify create.paragraph creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify create.heading creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify create.table creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify insert creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.insert, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Replace "apples" with "bananas" at the same location in the document.</t>
+          <t>Using Blank.docx, verify the original phrase is replaced in place (for example "apples" becoming "blueberries") with surrounding text unchanged.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify the command removes the requested text segment from the sentence while preserving surrounding content order.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify the specified block is removed so that removed content no longer appears in the final DOCX.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.apply should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the apply formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Its font size should visibly change compared with nearby text.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fontSize formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Its typeface should change (for example to Courier New) while content remains "bananas".</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fontFamily formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". The text color should visibly change (for example to red) while the words stay the same.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the color formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.align.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the align formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Apply comments.create and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify the comment operation comments.create produces the expected visible comment marker/bubble behavior at the intended text location.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Apply comments.patch and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify the comment operation comments.patch produces the expected visible comment marker/bubble behavior at the intended text location.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify the comment operation comments.delete produces the expected visible comment marker/bubble behavior at the intended text location.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setType, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.indent, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.outdent, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by lists.restart.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.restart, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by lists.exit.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.exit, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table row containing "bananas", insert a new adjacent row above/below as requested.</t>
+          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.insertRow.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.deleteRow.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table column containing "bananas", insert a new adjacent column left/right as requested.</t>
+          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.insertColumn.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.deleteColumn.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should render in bold while nearby "apples" stays regular.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its bold styling changes while "apples" and "mangoes" remain visually unchanged.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should render in italics while nearby "apples" stays upright.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its italic styling changes while "apples" and "mangoes" remain visually unchanged.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should have a visible underline.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its underline styling changes while "apples" and "mangoes" remain visually unchanged.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>The output DOCX should show an obvious visual formatting change on the exact target text used by the test for format.strikethrough.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its strikethrough styling changes while "apples" and "mangoes" remain visually unchanged.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Applies run-level style properties (character formatting) to the target text. Resulting DOCX shows inline style changes like font/color/weight.</t>
+          <t>Using Blank.docx, verify style changes from styles.apply (run) visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Applies paragraph-level style properties to the target block. Resulting DOCX shows paragraph formatting changes (alignment/spacing/indent, etc.).</t>
+          <t>Using Blank.docx, verify style changes from styles.apply (paragraph) visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.delete.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearContents.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.split.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Convert table cells "bananas" and "apples" into plain text in the same location.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table rows (including "Zebra | Banana | Mango") are converted into plain text lines in the same document location.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setLayout.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setRowHeight.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.distributeRows.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setRowOptions.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setColumnWidth.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.distributeColumns.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.insertCell.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.deleteCell.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Merge cells containing "bananas" and "apples" into one cell.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the cells containing "Banana" and adjacent values are merged or split exactly as requested by tables.mergeCells.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Split the merged cell containing "bananas" into multiple cells.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the cells containing "Banana" and adjacent values are merged or split exactly as requested by tables.unmergeCells.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Split the merged cell containing "bananas" into multiple cells.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the cells containing "Banana" and adjacent values are merged or split exactly as requested by tables.splitCell.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setCellProperties.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.sort.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setAltText.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setStyle.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearStyle.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setStyleOption.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setBorder.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearBorder.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.applyBorderPreset.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setShading.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearShading.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setTablePadding.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setCellPadding.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setCellSpacing.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearCellSpacing.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run find and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run getText and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run info and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run capabilities.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run getNode and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run getNodeById and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run lists.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run lists.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run comments.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run comments.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-table-ops-fixture.docx, run tables.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-table-ops-fixture.docx, run tables.getCells and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-table-ops-fixture.docx, run tables.getProperties and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run trackChanges.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run trackChanges.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Accepts one targeted tracked change. Resulting DOCX materializes that edit and removes its pending change marker.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (accept).</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Rejects one targeted tracked change. Resulting DOCX reverts that pending edit and clears its change marker.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (reject).</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Accepts all tracked changes in scope/document. Resulting DOCX keeps all proposed edits and clears tracked-change markup.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (acceptAll).</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Rejects all tracked changes in scope/document. Resulting DOCX rolls back proposed edits and clears tracked-change markup.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (rejectAll).</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run query.match and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, run mutations.preview and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Expected check: Apply mutations.apply and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify mutations.apply yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Expected check: Convert plain text line "bananas | apples" into table cells.</t>
+          <t>Using docapi-convert-from-text-fixture.docx, confirm text including "Alpha|Beta|Gamma" is converted into a visible table with corresponding cell values.</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Move sentence "bananas are ripe." to directly below heading "Shopping List". It should disappear from its old location.</t>
+          <t>Using docapi-table-ops-fixture.docx, move the row "Zebra | Banana | Mango" to the command-specified new position so it appears there once and is absent from its original row slot.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by create.sectionBreak.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by create.tableOfContents.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.clearHeaderFooterRef.</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.clearPageBorders.</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="F91" s="22" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-sections-toc-fixture.docx, run sections.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G91" s="22" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-sections-toc-fixture.docx, run sections.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setBreakType.</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setColumns.</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setHeaderFooterMargins.</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setHeaderFooterRef.</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setLineNumbering.</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setLinkToPrevious.</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setOddEvenHeadersFooters.</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageBorders.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageMargins.</t>
         </is>
       </c>
       <c r="G101" s="22" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageNumbering.</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageSetup.</t>
         </is>
       </c>
       <c r="G103" s="22" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setSectionDirection.</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setTitlePage.</t>
         </is>
       </c>
       <c r="G105" s="22" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t>Expected check: In the section containing "bananas", apply the requested page/section setting and verify layout change (margins, columns, numbering, borders, or header/footer behavior).</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setVerticalAlign.</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.configure.</t>
         </is>
       </c>
       <c r="G107" s="22" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-sections-toc-fixture.docx, run toc.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="F109" s="22" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-sections-toc-fixture.docx, run toc.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
         </is>
       </c>
       <c r="G109" s="22" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.remove.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.update.</t>
         </is>
       </c>
       <c r="G111" s="22" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should have a single strike-through line.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its strike styling changes while "apples" and "mangoes" remain visually unchanged.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should have a bright yellow marker-style highlight behind the text.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm it has a bright yellow marker-style highlight while "apples" and "mangoes" keep their original look.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.shading should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the shading formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G114" s="25" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.border should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the border formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G115" s="25" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F116" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should show an outlined glyph effect.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the outline formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G116" s="25" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="F117" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should show a visible text shadow effect.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the shadow formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G117" s="25" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should show an embossed text effect.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the emboss formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G118" s="25" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should show an imprinted/debossed text effect.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the imprint formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F120" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.vertAlign should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the vertAlign formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G120" s="25" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="F121" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.position should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the position formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G121" s="25" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.rtl should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rtl formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F123" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.cs should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the cs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G123" s="25" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F124" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.bCs should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the bCs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G124" s="25" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="F125" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.iCs should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the iCs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G125" s="25" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="F126" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.vanish should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the vanish formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G126" s="25" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="F127" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.webHidden should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the webHidden formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G127" s="25" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.specVanish should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the specVanish formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.snapToGrid should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the snapToGrid formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G129" s="25" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="F130" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.oMath should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the oMath formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G130" s="25" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.fontSizeCs should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fontSizeCs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G131" s="25" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.charScale should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the charScale formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G132" s="25" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.kerning should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the kerning formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G133" s="25" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.fitText should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fitText formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.lang should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the lang formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G135" s="25" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.rStyle should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rStyle formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.rFonts should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rFonts formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G137" s="25" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.eastAsianLayout should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the eastAsianLayout formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G138" s="25" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.em should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the em formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G139" s="25" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.ligatures should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the ligatures formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G140" s="25" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="F141" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.numForm should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the numForm formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G141" s="25" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.numSpacing should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the numSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G142" s="25" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F143" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.stylisticSets should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the stylisticSets formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G143" s="25" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.contextualAlternates should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the contextualAlternates formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G144" s="25" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="F145" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should have a double strike-through line.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its dstrike styling changes while "apples" and "mangoes" remain visually unchanged.</t>
         </is>
       </c>
       <c r="G145" s="25" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="F146" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should display in small caps.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the smallCaps formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G146" s="25" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="F147" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". It should display in all caps.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the caps formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G147" s="25" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="F148" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Letters should be spaced farther apart or tighter based on input.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the letterSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G148" s="25" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="F149" s="25" t="inlineStr">
         <is>
-          <t>Multiple words/paragraphs should show RTL run behavior across the document, not only one target word.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rtl.all formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G149" s="25" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="F150" s="25" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, verify getMarkdown yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G150" s="25" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="F151" s="25" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, verify getHtml yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G151" s="25" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="F152" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Apply style to text/paragraph containing "bananas" and verify only intended styling changes.</t>
+          <t>Using Blank.docx, verify style changes from styles.paragraph.setStyle visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G152" s="25" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="F153" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Apply style to text/paragraph containing "bananas" and verify only intended styling changes.</t>
+          <t>Using Blank.docx, verify style changes from styles.paragraph.clearStyle visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G153" s="25" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F154" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.resetDirectFormatting should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.resetDirectFormatting formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G154" s="25" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="F155" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setAlignment should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setAlignment formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G155" s="25" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="F156" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearAlignment should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearAlignment formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G156" s="25" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setIndentation should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setIndentation formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G157" s="25" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="F158" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearIndentation should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearIndentation formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G158" s="25" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F159" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setSpacing should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G159" s="25" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="F160" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearSpacing should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G160" s="25" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F161" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setKeepOptions should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setKeepOptions formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G161" s="25" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setOutlineLevel should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setOutlineLevel formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G162" s="25" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="F163" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setFlowOptions should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setFlowOptions formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G163" s="25" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="F164" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setTabStop should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setTabStop formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G164" s="25" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F165" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearTabStop should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearTabStop formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G165" s="25" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F166" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearAllTabStops should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearAllTabStops formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G166" s="25" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F167" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setBorder should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setBorder formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G167" s="25" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearBorder should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearBorder formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G168" s="25" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setShading should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setShading formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G169" s="25" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F170" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearShading should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearShading formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G170" s="25" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.create, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G171" s="25" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.attach, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G172" s="25" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.detach, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G173" s="25" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.join, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G174" s="25" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="F175" s="25" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.canJoin, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G175" s="25" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.separate, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G176" s="25" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevel, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G177" s="25" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setValue, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G178" s="25" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.continuePrevious, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G179" s="25" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="F180" s="25" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.canContinuePrevious, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G180" s="25" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelRestart, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G181" s="25" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.convertToText, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G182" s="25" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="F183" s="25" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.getStyles.</t>
         </is>
       </c>
       <c r="G183" s="25" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setDefaultStyle.</t>
         </is>
       </c>
       <c r="G184" s="25" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearDefaultStyle.</t>
         </is>
       </c>
       <c r="G185" s="25" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.markEntry.</t>
         </is>
       </c>
       <c r="G186" s="25" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.unmarkEntry.</t>
         </is>
       </c>
       <c r="G187" s="25" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.listEntries.</t>
         </is>
       </c>
       <c r="G188" s="25" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F189" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.getEntry.</t>
         </is>
       </c>
       <c r="G189" s="25" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Update TOC so entry for heading containing "bananas" reflects requested TOC behavior.</t>
+          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.editEntry.</t>
         </is>
       </c>
       <c r="G190" s="25" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F191" s="25" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Using Blank.docx, verify history.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G191" s="25" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="F192" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Apply history.undo and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify history.undo yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G192" s="25" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>Expected check: Apply history.redo and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify history.redo yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G193" s="25" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by styles.apply.paragraph.</t>
+          <t>Using Blank.docx, verify style changes from styles.apply.paragraph visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by styles.apply.run.</t>
+          <t>Using Blank.docx, verify style changes from styles.apply.run visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by trackChanges.decide.accept.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.accept.</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by trackChanges.decide.acceptAll.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.acceptAll.</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by trackChanges.decide.reject.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.reject.</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>The output DOCX should show the visible document change produced by trackChanges.decide.rejectAll.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.rejectAll.</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply style to text/paragraph containing "bananas" and verify only intended styling changes.</t>
+          <t>Using Blank.docx, verify style changes from styles.apply visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On revision affecting "bananas", accept/reject as requested and verify final visible text state.</t>
+          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify markdownToFragment yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify clearContent yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify blocks.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify blocks.deleteRange yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.setDirection should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setDirection formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Find "bananas". Only the requested inline format property for format.paragraph.clearDirection should change; word content and position should not move.</t>
+          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearDirection formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.applyTemplate, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.applyPreset, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.captureTemplate, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelNumbering, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelBullet, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelPictureBullet, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelAlignment, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelIndents, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelTrailingCharacter, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelMarkerFont, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.clearLevelOverrides, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.getStyle, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.applyStyle, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.restartAt, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelNumberStyle, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelText, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelStart, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In list item "bananas", apply requested list operation and verify numbering/bullet structure change.</t>
+          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelLayout, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify ranges.resolve yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.applyStyle.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setBorders.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In the table containing "bananas", apply the requested table property change and confirm table layout/style updates are visible.</t>
+          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setTableOptions.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify create.image yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify images.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify images.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify images.delete produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Move sentence "bananas are ripe." to directly below heading "Shopping List". It should disappear from its old location.</t>
+          <t>Using Blank.docx, verify images.move produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.convertToInline produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.convertToFloating produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setSize produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setWrapType produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setWrapSide produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setWrapDistances produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setPosition produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setAnchorOptions produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setZOrder produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.scale produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setLockAspectRatio produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.rotate produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.flip produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.crop produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.resetCrop produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Replace "apples" with "bananas" at the same location in the document.</t>
+          <t>Using Blank.docx, verify images.replaceSource produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setAltText produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setDecorative produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setName produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.setHyperlink produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.insertCaption produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On image near caption "bananas", apply requested image change (position/size/wrap/z-order/alt text) and verify visible result.</t>
+          <t>Using Blank.docx, verify images.updateCaption produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify images.removeCaption produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify hyperlinks.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify hyperlinks.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On text "bananas", apply hyperlink change and verify it appears/updates/removes as requested.</t>
+          <t>Using Blank.docx, verify hyperlinks.wrap produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On text "bananas", apply hyperlink change and verify it appears/updates/removes as requested.</t>
+          <t>Using Blank.docx, verify hyperlinks.insert produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On text "bananas", apply hyperlink change and verify it appears/updates/removes as requested.</t>
+          <t>Using Blank.docx, verify hyperlinks.patch produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify hyperlinks.remove produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify headerFooters.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify headerFooters.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify headerFooters.resolve produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
+          <t>Using Blank.docx, verify headerFooters.refs.set produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
+          <t>Using Blank.docx, verify headerFooters.refs.clear produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
+          <t>Using Blank.docx, verify headerFooters.refs.setLinkedToPrevious produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify headerFooters.parts.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>Expected check: In header/footer containing "bananas", apply requested part/ref change and verify page header/footer output.</t>
+          <t>Using Blank.docx, verify headerFooters.parts.create produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G272" s="4" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify headerFooters.parts.delete produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Add new content "bananas" at the requested location (for example after heading "Shopping List"). Existing surrounding text should remain.</t>
+          <t>Using Blank.docx, verify create.contentControl yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G274" s="4" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.list for the selected control region.</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.get for the selected control region.</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.listInRange for the selected control region.</t>
         </is>
       </c>
       <c r="G277" s="4" t="inlineStr">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.selectByTag for the selected control region.</t>
         </is>
       </c>
       <c r="G278" s="4" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.selectByTitle for the selected control region.</t>
         </is>
       </c>
       <c r="G279" s="4" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.listChildren for the selected control region.</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getParent for the selected control region.</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.wrap for the selected control region.</t>
         </is>
       </c>
       <c r="G282" s="4" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.unwrap for the selected control region.</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.delete for the selected control region.</t>
         </is>
       </c>
       <c r="G284" s="4" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.copy for the selected control region.</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Move sentence "bananas are ripe." to directly below heading "Shopping List". It should disappear from its old location.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.move for the selected control region.</t>
         </is>
       </c>
       <c r="G286" s="4" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.patch for the selected control region.</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.setLockMode for the selected control region.</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.setType for the selected control region.</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getContent for the selected control region.</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Replace "apples" with "bananas" at the same location in the document.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.replaceContent for the selected control region.</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.clearContent for the selected control region.</t>
         </is>
       </c>
       <c r="G292" s="4" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.appendContent for the selected control region.</t>
         </is>
       </c>
       <c r="G293" s="4" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.prependContent for the selected control region.</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Insert "bananas" immediately before "XYZ".</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.insertBefore for the selected control region.</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Insert "bananas" immediately after "XYZ".</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.insertAfter for the selected control region.</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getBinding for the selected control region.</t>
         </is>
       </c>
       <c r="G297" s="4" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.setBinding for the selected control region.</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.clearBinding for the selected control region.</t>
         </is>
       </c>
       <c r="G299" s="4" t="inlineStr">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getRawProperties for the selected control region.</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.patchRawProperties for the selected control region.</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.validateWordCompatibility for the selected control region.</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.normalizeWordCompatibility for the selected control region.</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.normalizeTagPayload for the selected control region.</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.text.setMultiline for the selected control region.</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.text.setValue for the selected control region.</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.text.clearValue for the selected control region.</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setValue for the selected control region.</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.clearValue for the selected control region.</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setDisplayFormat for the selected control region.</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setDisplayLocale for the selected control region.</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -24860,7 +24860,7 @@
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setStorageFormat for the selected control region.</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setCalendar for the selected control region.</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.getState for the selected control region.</t>
         </is>
       </c>
       <c r="G314" s="4" t="inlineStr">
@@ -25038,7 +25038,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.setState for the selected control region.</t>
         </is>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.toggle for the selected control region.</t>
         </is>
       </c>
       <c r="G316" s="4" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.setSymbolPair for the selected control region.</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.choiceList.getItems for the selected control region.</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.choiceList.setItems for the selected control region.</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.choiceList.setSelected for the selected control region.</t>
         </is>
       </c>
       <c r="G320" s="4" t="inlineStr">
@@ -25390,7 +25390,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.listItems for the selected control region.</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.insertItemBefore for the selected control region.</t>
         </is>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.insertItemAfter for the selected control region.</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.cloneItem for the selected control region.</t>
         </is>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.deleteItem for the selected control region.</t>
         </is>
       </c>
       <c r="G325" s="4" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.setAllowInsertDelete for the selected control region.</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.group.wrap for the selected control region.</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>Expected check: On content control titled "FruitField", apply requested change and verify visible/control behavior update.</t>
+          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.group.ungroup for the selected control region.</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify bookmarks.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify bookmarks.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply bookmarks.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify bookmarks.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr">
@@ -26048,7 +26048,7 @@
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply bookmarks.rename and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify bookmarks.rename yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify bookmarks.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G333" s="4" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify footnotes.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify footnotes.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply footnotes.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify footnotes.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply footnotes.update and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify footnotes.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify footnotes.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply footnotes.configure and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify footnotes.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify crossRefs.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify crossRefs.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G341" s="4" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply crossRefs.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify crossRefs.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G342" s="4" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply crossRefs.rebuild and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify crossRefs.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -26776,7 +26776,7 @@
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify crossRefs.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify index.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify index.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply index.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify index.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G347" s="4" t="inlineStr">
@@ -27024,7 +27024,7 @@
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply index.configure and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify index.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply index.rebuild and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify index.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify index.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -27198,7 +27198,7 @@
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify index.entries.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify index.entries.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply index.entries.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify index.entries.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply index.entries.update and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify index.entries.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -27438,7 +27438,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify index.entries.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify captions.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify captions.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply captions.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify captions.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply captions.update and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify captions.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -27744,7 +27744,7 @@
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify captions.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply captions.configure and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify captions.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify fields.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify fields.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply fields.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify fields.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply fields.rebuild and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify fields.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify fields.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify citations.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify citations.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G368" s="4" t="inlineStr">
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.update and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify citations.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify citations.sources.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify citations.sources.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.sources.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.sources.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G374" s="4" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.sources.update and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.sources.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G375" s="4" t="inlineStr">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify citations.sources.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G376" s="4" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify citations.bibliography.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G377" s="4" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.bibliography.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.bibliography.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G378" s="4" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.bibliography.rebuild and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.bibliography.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr">
@@ -28948,7 +28948,7 @@
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply citations.bibliography.configure and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify citations.bibliography.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify citations.bibliography.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G381" s="4" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify authorities.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G382" s="4" t="inlineStr">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify authorities.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -29196,7 +29196,7 @@
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply authorities.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify authorities.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G384" s="4" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply authorities.configure and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify authorities.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -29312,7 +29312,7 @@
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply authorities.rebuild and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify authorities.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G386" s="4" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify authorities.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G387" s="4" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify authorities.entries.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify authorities.entries.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply authorities.entries.insert and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify authorities.entries.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply authorities.entries.update and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify authorities.entries.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify authorities.entries.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify diff.capture yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G393" s="4" t="inlineStr">
@@ -29792,7 +29792,7 @@
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify diff.compare yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply diff.apply and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify diff.apply yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify protection.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply protection.setEditingRestriction and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify protection.setEditingRestriction yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
@@ -30040,7 +30040,7 @@
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Apply protection.clearEditingRestriction and verify explicit before/after change around sample text "bananas".</t>
+          <t>Using Blank.docx, verify protection.clearEditingRestriction yields the exact visual result defined by the command inputs in the edited DOCX.</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify permissionRanges.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Query "bananas" and return data only. The DOCX should look unchanged before vs after.</t>
+          <t>Using Blank.docx, verify permissionRanges.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Create/update permission range around text "bananas" and verify protected/editable region boundaries.</t>
+          <t>Using Blank.docx, verify permissionRanges.create produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Remove "bananas" from the targeted region. "bananas" should no longer appear there after execution.</t>
+          <t>Using Blank.docx, verify permissionRanges.remove produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Expected check: Create/update permission range around text "bananas" and verify protected/editable region boundaries.</t>
+          <t>Using Blank.docx, verify permissionRanges.updatePrincipal produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr">

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -22580,7 +22580,7 @@
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify create.contentControl yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run create.contentControl with content "XYZ" and tag "FruitField", and verify a new visible content control appears containing "XYZ".</t>
         </is>
       </c>
       <c r="G274" s="4" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.list for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.list, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G275" s="4" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.get for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.get, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.listInRange for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.listInRange, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G277" s="4" t="inlineStr">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.selectByTag for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.selectByTag, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G278" s="4" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.selectByTitle for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.selectByTitle, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G279" s="4" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.listChildren for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.listChildren, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G280" s="4" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getParent for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.getParent, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G281" s="4" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.wrap for the selected control region.</t>
+          <t>Start from Blank.docx containing plain text "XYZ", run contentControls.wrap on that text, and verify "XYZ" is now inside a visible content control container.</t>
         </is>
       </c>
       <c r="G282" s="4" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.unwrap for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.unwrap, and verify "XYZ" remains visible as plain text with the control removed.</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.delete for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.delete, and verify both the control and "XYZ" are removed from the document.</t>
         </is>
       </c>
       <c r="G284" s="4" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.copy for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.copy to a new location, and verify two visible controls contain "XYZ" (original and copied).</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.move for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ" and an anchor paragraph "AFTER_MOVE_MARKER", run contentControls.move to after the anchor, and verify the "XYZ" control appears after "AFTER_MOVE_MARKER" and no longer appears in its old location.</t>
         </is>
       </c>
       <c r="G286" s="4" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.patch for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.patch to set alias "FruitField", and verify the same control remains visible around "XYZ" with updated metadata.</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.setLockMode for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.setLockMode, and verify the control remains visible around "XYZ" with the requested lock behavior enforced.</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.setType for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.setType to the requested type, and verify the control remains at the same position with "XYZ" still visible.</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getContent for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.getContent, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.replaceContent for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.replaceContent with "ABC", and verify that same control now displays "ABC" instead of "XYZ".</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.clearContent for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.clearContent, and verify the control remains but its visible text is empty.</t>
         </is>
       </c>
       <c r="G292" s="4" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.appendContent for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.appendContent with "ABC", and verify the control text becomes "XYZABC".</t>
         </is>
       </c>
       <c r="G293" s="4" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.prependContent for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.prependContent with "ABC", and verify the control text becomes "ABCXYZ".</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.insertBefore for the selected control region.</t>
+          <t>Start from Blank.docx with a block content control containing "XYZ", run contentControls.insertBefore with content "ABC", and verify the document shows "ABC" immediately before that control so the visible order is "ABC" then "XYZ".</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.insertAfter for the selected control region.</t>
+          <t>Start from Blank.docx with a block content control containing "XYZ", run contentControls.insertAfter with content "ABC", and verify the document shows "ABC" immediately after that control so the visible order is "XYZ" then "ABC".</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getBinding for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.getBinding, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G297" s="4" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.setBinding for the selected control region.</t>
+          <t>Start from Blank.docx with a content control showing "XYZ", run contentControls.setBinding to a data path, and verify the same control remains visible with its displayed text still at the control location.</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.clearBinding for the selected control region.</t>
+          <t>Start from Blank.docx with a bound content control showing "XYZ", run contentControls.clearBinding, and verify the control still shows "XYZ" at the same location but is no longer bound.</t>
         </is>
       </c>
       <c r="G299" s="4" t="inlineStr">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.getRawProperties for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.getRawProperties, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.patchRawProperties for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.patchRawProperties, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G301" s="4" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.validateWordCompatibility for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.validateWordCompatibility, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.normalizeWordCompatibility for the selected control region.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.normalizeWordCompatibility, and verify "XYZ" remains visually unchanged while control markup is normalized for Word compatibility.</t>
         </is>
       </c>
       <c r="G303" s="4" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.normalizeTagPayload for the selected control region.</t>
+          <t>Start from Blank.docx with a content control tagged with JSON payload around "XYZ", run contentControls.normalizeTagPayload, and verify "XYZ" remains visually unchanged while tag payload is normalized.</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.text.setMultiline for the selected control region.</t>
+          <t>Start from Blank.docx with a text content control showing "XYZ", run contentControls.text.setMultiline(true), and verify line breaks are allowed while "XYZ" remains in the control.</t>
         </is>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.text.setValue for the selected control region.</t>
+          <t>Start from Blank.docx with a text content control currently showing "XYZ", run contentControls.text.setValue with "ABC", and verify that control now displays "ABC".</t>
         </is>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.text.clearValue for the selected control region.</t>
+          <t>Start from Blank.docx with a text content control showing "XYZ", run contentControls.text.clearValue, and verify that control remains but shows empty text.</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setValue for the selected control region.</t>
+          <t>Start from Blank.docx with a date content control, run contentControls.date.setValue("2026-04-06"), and verify the control displays that date.</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.clearValue for the selected control region.</t>
+          <t>Start from Blank.docx with a date content control showing a date, run contentControls.date.clearValue, and verify the control no longer displays a date value.</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setDisplayFormat for the selected control region.</t>
+          <t>Start from Blank.docx with a date content control, run contentControls.date.setDisplayFormat("MMMM d, yyyy"), and verify the same date renders in that display format.</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setDisplayLocale for the selected control region.</t>
+          <t>Start from Blank.docx with a date content control, run contentControls.date.setDisplayLocale, and verify the date renders using the requested locale style.</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -24860,7 +24860,7 @@
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setStorageFormat for the selected control region.</t>
+          <t>Start from Blank.docx with a date content control, run contentControls.date.setStorageFormat, and verify visible date text remains present while storage format changes.</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.date.setCalendar for the selected control region.</t>
+          <t>Start from Blank.docx with a date content control, run contentControls.date.setCalendar, and verify date behavior follows the requested calendar setting.</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.getState for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.checkbox.getState, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G314" s="4" t="inlineStr">
@@ -25038,7 +25038,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.setState for the selected control region.</t>
+          <t>Start from Blank.docx with a checkbox content control, run contentControls.checkbox.setState(true), and verify the checkbox appears checked.</t>
         </is>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.toggle for the selected control region.</t>
+          <t>Start from Blank.docx with an unchecked checkbox content control, run contentControls.checkbox.toggle, and verify it appears checked.</t>
         </is>
       </c>
       <c r="G316" s="4" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.checkbox.setSymbolPair for the selected control region.</t>
+          <t>Start from Blank.docx with a checkbox content control, run contentControls.checkbox.setSymbolPair, and verify checked/unchecked glyphs render using the requested symbols.</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.choiceList.getItems for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.choiceList.getItems, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.choiceList.setItems for the selected control region.</t>
+          <t>Start from Blank.docx with a choice-list content control, run contentControls.choiceList.setItems with ["ABC","XYZ"], and verify those exact options are available in the control.</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.choiceList.setSelected for the selected control region.</t>
+          <t>Start from Blank.docx with a choice-list content control containing options "ABC" and "XYZ", run contentControls.choiceList.setSelected("ABC"), and verify the visible selected value is "ABC".</t>
         </is>
       </c>
       <c r="G320" s="4" t="inlineStr">
@@ -25390,7 +25390,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.listItems for the selected control region.</t>
+          <t>Start from Blank.docx with visible sample text "XYZ", run contentControls.repeatingSection.listItems, and verify the content control result is visually consistent with the command while preserving unchanged surrounding text.</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.insertItemBefore for the selected control region.</t>
+          <t>Start from Blank.docx with a repeating-section item containing "XYZ", run contentControls.repeatingSection.insertItemBefore with content "ABC", and verify a new item "ABC" appears immediately before "XYZ".</t>
         </is>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.insertItemAfter for the selected control region.</t>
+          <t>Start from Blank.docx with a repeating-section item containing "XYZ", run contentControls.repeatingSection.insertItemAfter with content "ABC", and verify a new item "ABC" appears immediately after "XYZ".</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.cloneItem for the selected control region.</t>
+          <t>Start from Blank.docx with a repeating-section item containing "XYZ", run contentControls.repeatingSection.cloneItem, and verify two adjacent items now display "XYZ".</t>
         </is>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.deleteItem for the selected control region.</t>
+          <t>Start from Blank.docx with repeating-section items "ABC" and "XYZ", run contentControls.repeatingSection.deleteItem on "ABC", and verify only "XYZ" remains.</t>
         </is>
       </c>
       <c r="G325" s="4" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.repeatingSection.setAllowInsertDelete for the selected control region.</t>
+          <t>Start from Blank.docx with a repeating-section control, run contentControls.repeatingSection.setAllowInsertDelete(false), and verify insert/delete affordances are disabled while existing item text remains visible.</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.group.wrap for the selected control region.</t>
+          <t>Start from Blank.docx containing paragraphs "ABC" and "XYZ", run contentControls.group.wrap over both, and verify both paragraphs are enclosed in one grouped content control.</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify content control visuals/behavior update exactly as requested by contentControls.group.ungroup for the selected control region.</t>
+          <t>Start from Blank.docx with grouped content control containing "ABC" and "XYZ", run contentControls.group.ungroup, and verify both paragraphs remain visible but no longer grouped.</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify create.paragraph creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
+          <t>Start from Blank.docx, run create.paragraph, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify create.heading creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
+          <t>Start from Blank.docx, run create.heading, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify create.table creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
+          <t>Start from Blank.docx, run create.table, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify insert creates new visible content at the requested location (for example inserted text like "apples, bananas, mangoes" when the test seeds sample text).</t>
+          <t>Start from Blank.docx, run insert, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.insert, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.insert, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the original phrase is replaced in place (for example "apples" becoming "blueberries") with surrounding text unchanged.</t>
+          <t>Start from Blank.docx, run replace, and verify the original phrase is replaced in place (for example "apples" becomes "blueberries") with surrounding content unchanged.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the command removes the requested text segment from the sentence while preserving surrounding content order.</t>
+          <t>Start from Blank.docx, run delete, and verify the requested content is removed and no longer visible in that region.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the specified block is removed so that removed content no longer appears in the final DOCX.</t>
+          <t>Start from Blank.docx, run blocks.delete, and verify the requested content is removed and no longer visible in that region.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the apply formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.apply formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fontSize formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only its font size changes relative to "apples" and "mangoes".</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fontFamily formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only its typeface changes while text content and order stay unchanged.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the color formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only its font color changes while its text and position stay the same.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the align formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.align formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the comment operation comments.create produces the expected visible comment marker/bubble behavior at the intended text location.</t>
+          <t>Start from Blank.docx, run comments.create, and verify comment markers/bubbles appear, update, or disappear at the intended text location.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the comment operation comments.patch produces the expected visible comment marker/bubble behavior at the intended text location.</t>
+          <t>Start from Blank.docx, run comments.patch, and verify comment markers/bubbles appear, update, or disappear at the intended text location.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the comment operation comments.delete produces the expected visible comment marker/bubble behavior at the intended text location.</t>
+          <t>Start from Blank.docx, run comments.delete, and verify comment markers/bubbles appear, update, or disappear at the intended text location.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setType, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setType, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.indent, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.indent, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.outdent, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.outdent, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.restart, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.restart, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.exit, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.exit, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.insertRow.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.insertRow, and verify table structure changes exactly once around rows/cells containing "Zebra", "Banana", "Mango", "Apple", and "Kiwi".</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.deleteRow.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.deleteRow, and verify table structure changes exactly once around rows/cells containing "Zebra", "Banana", "Mango", "Apple", and "Kiwi".</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.insertColumn.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.insertColumn, and verify table structure changes exactly once around rows/cells containing "Zebra", "Banana", "Mango", "Apple", and "Kiwi".</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, verify the table with rows "Zebra | Banana | Mango", "Apple | Grape | Kiwi", and "Mango | Pear | Peach" reflects the exact row/column insertion or removal requested by tables.deleteColumn.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.deleteColumn, and verify table structure changes exactly once around rows/cells containing "Zebra", "Banana", "Mango", "Apple", and "Kiwi".</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its bold styling changes while "apples" and "mangoes" remain visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it appears bold while "apples" and "mangoes" remain regular weight.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its italic styling changes while "apples" and "mangoes" remain visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it appears italic while neighboring words keep normal style.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its underline styling changes while "apples" and "mangoes" remain visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a visible underline while other words remain unlined.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its strikethrough styling changes while "apples" and "mangoes" remain visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a single strike-through line while nearby words do not.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.apply (run) visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply (run), and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.apply (paragraph) visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply (paragraph), and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.delete.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.delete, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearContents.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearContents, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.split.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.split, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table rows (including "Zebra | Banana | Mango") are converted into plain text lines in the same document location.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.convertToText, and verify table rows including "Zebra | Banana | Mango" become plain text lines at the same location.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setLayout.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setLayout, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setRowHeight.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setRowHeight, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.distributeRows.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.distributeRows, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setRowOptions.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setRowOptions, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setColumnWidth.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setColumnWidth, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.distributeColumns.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.distributeColumns, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.insertCell.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.insertCell, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.deleteCell.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.deleteCell, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the cells containing "Banana" and adjacent values are merged or split exactly as requested by tables.mergeCells.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.mergeCells, and verify cells around "Banana" and adjacent values are merged or split exactly as requested.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the cells containing "Banana" and adjacent values are merged or split exactly as requested by tables.unmergeCells.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.unmergeCells, and verify cells around "Banana" and adjacent values are merged or split exactly as requested.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the cells containing "Banana" and adjacent values are merged or split exactly as requested by tables.splitCell.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.splitCell, and verify cells around "Banana" and adjacent values are merged or split exactly as requested.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setCellProperties.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellProperties, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.sort.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.sort, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setAltText.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setAltText, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setStyle.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearStyle.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setStyleOption.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setStyleOption, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setBorder.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setBorder, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearBorder.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearBorder, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.applyBorderPreset.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.applyBorderPreset, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setShading.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setShading, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearShading.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearShading, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setTablePadding.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setTablePadding, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setCellPadding.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellPadding, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setCellSpacing.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellSpacing, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearCellSpacing.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearCellSpacing, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run find and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run find, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run getText and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run getText, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run info and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run info, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run capabilities.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run capabilities.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run getNode and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run getNode, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run getNodeById and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run getNodeById, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run lists.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run lists.list, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run lists.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run lists.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run comments.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run comments.list, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run comments.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run comments.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, run tables.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, run tables.getCells and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.getCells, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, run tables.getProperties and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.getProperties, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run trackChanges.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run trackChanges.list, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run trackChanges.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run trackChanges.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (accept).</t>
+          <t>Start from Blank.docx, run trackChanges.decide (accept), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (reject).</t>
+          <t>Start from Blank.docx, run trackChanges.decide (reject), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (acceptAll).</t>
+          <t>Start from Blank.docx, run trackChanges.decide (acceptAll), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide (rejectAll).</t>
+          <t>Start from Blank.docx, run trackChanges.decide (rejectAll), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run query.match and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run query.match, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, run mutations.preview and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from Blank.docx, run mutations.preview, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify mutations.apply yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run mutations.apply, and verify each applied mutation produces the expected visible before/after result in the document.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Using docapi-convert-from-text-fixture.docx, confirm text including "Alpha|Beta|Gamma" is converted into a visible table with corresponding cell values.</t>
+          <t>Start from docapi-convert-from-text-fixture.docx, run tables.convertFromText, and verify text including "Alpha|Beta|Gamma" becomes a visible table with corresponding cell values.</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, move the row "Zebra | Banana | Mango" to the command-specified new position so it appears there once and is absent from its original row slot.</t>
+          <t>Start from docapi-table-ops-fixture.docx, move the row "Zebra | Banana | Mango" to the requested destination, and verify it appears in the new position and is absent from the original row slot.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by create.sectionBreak.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run create.sectionBreak, and verify a new section boundary appears with subsequent layout behavior changing after the break.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by create.tableOfContents.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run create.tableOfContents, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.clearHeaderFooterRef.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.clearHeaderFooterRef, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.clearPageBorders.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.clearPageBorders, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="F91" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, run sections.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G91" s="22" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, run sections.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.list, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setBreakType.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setBreakType, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setColumns.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setColumns, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setHeaderFooterMargins.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setHeaderFooterMargins, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setHeaderFooterRef.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setHeaderFooterRef, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setLineNumbering.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setLineNumbering, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setLinkToPrevious.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setLinkToPrevious, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setOddEvenHeadersFooters.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setOddEvenHeadersFooters, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageBorders.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageBorders, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageMargins.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageMargins, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G101" s="22" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageNumbering.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageNumbering, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setPageSetup.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageSetup, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G103" s="22" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setSectionDirection.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setSectionDirection, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setTitlePage.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setTitlePage, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G105" s="22" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by sections.setVerticalAlign.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setVerticalAlign, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.configure.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.configure, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G107" s="22" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, run toc.get and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="F109" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, run toc.list and verify the document still looks unchanged while only data is returned for the existing document content.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.list, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G109" s="22" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.remove.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.remove, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.update.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.update, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G111" s="22" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its strike styling changes while "apples" and "mangoes" remain visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a single strike-through line while nearby words do not.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm it has a bright yellow marker-style highlight while "apples" and "mangoes" keep their original look.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a bright yellow marker-style highlight while "apples" and "mangoes" stay visually unchanged.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="F114" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the shading formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.shading formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G114" s="25" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F115" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the border formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.border formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G115" s="25" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F116" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the outline formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify an outline effect appears on that word only.</t>
         </is>
       </c>
       <c r="G116" s="25" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="F117" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the shadow formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify a visible shadow effect appears on that word only.</t>
         </is>
       </c>
       <c r="G117" s="25" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F118" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the emboss formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify an embossed effect appears on that word only.</t>
         </is>
       </c>
       <c r="G118" s="25" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F119" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the imprint formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify an imprinted/debossed effect appears on that word only.</t>
         </is>
       </c>
       <c r="G119" s="25" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F120" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the vertAlign formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.vertAlign formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G120" s="25" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="F121" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the position formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify baseline position shifts (raised/lowered) while the same word remains visible.</t>
         </is>
       </c>
       <c r="G121" s="25" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="F122" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rtl formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify run-direction formatting changes while the word remains in the same location.</t>
         </is>
       </c>
       <c r="G122" s="25" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F123" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the cs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.cs formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G123" s="25" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F124" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the bCs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.bCs formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G124" s="25" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="F125" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the iCs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.iCs formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G125" s="25" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="F126" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the vanish formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.vanish formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G126" s="25" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="F127" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the webHidden formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.webHidden formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G127" s="25" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="F128" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the specVanish formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.specVanish formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G128" s="25" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F129" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the snapToGrid formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.snapToGrid formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G129" s="25" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="F130" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the oMath formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.oMath formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G130" s="25" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F131" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fontSizeCs formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify complex-script font size changes while visible text stays "apples, bananas, mangoes".</t>
         </is>
       </c>
       <c r="G131" s="25" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="F132" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the charScale formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.charScale formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G132" s="25" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the kerning formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.kerning formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G133" s="25" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the fitText formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.fitText formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G134" s="25" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the lang formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.lang formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G135" s="25" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rStyle formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.rStyle formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rFonts formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.rFonts formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G137" s="25" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the eastAsianLayout formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.eastAsianLayout formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G138" s="25" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the em formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.em formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G139" s="25" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the ligatures formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.ligatures formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G140" s="25" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="F141" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the numForm formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.numForm formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G141" s="25" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the numSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.numSpacing formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G142" s="25" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F143" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the stylisticSets formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.stylisticSets formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G143" s="25" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the contextualAlternates formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.contextualAlternates formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G144" s="25" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="F145" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only its dstrike styling changes while "apples" and "mangoes" remain visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a double strike-through line while nearby words do not.</t>
         </is>
       </c>
       <c r="G145" s="25" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="F146" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the smallCaps formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it renders in small caps while neighboring words keep prior casing style.</t>
         </is>
       </c>
       <c r="G146" s="25" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="F147" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the caps formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it renders in all caps while neighboring words remain unchanged.</t>
         </is>
       </c>
       <c r="G147" s="25" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="F148" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the letterSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify character spacing changes while text content stays the same.</t>
         </is>
       </c>
       <c r="G148" s="25" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="F149" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the rtl.all formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.rtl.all formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G149" s="25" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="F150" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify getMarkdown yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run getMarkdown, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G150" s="25" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="F151" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify getHtml yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run getHtml, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G151" s="25" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="F152" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.paragraph.setStyle visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.paragraph.setStyle, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G152" s="25" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="F153" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.paragraph.clearStyle visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.paragraph.clearStyle, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G153" s="25" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F154" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.resetDirectFormatting formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.resetDirectFormatting formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G154" s="25" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="F155" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setAlignment formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setAlignment formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G155" s="25" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="F156" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearAlignment formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearAlignment formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G156" s="25" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setIndentation formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setIndentation formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G157" s="25" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="F158" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearIndentation formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearIndentation formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G158" s="25" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F159" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setSpacing formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G159" s="25" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="F160" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearSpacing formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearSpacing formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G160" s="25" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F161" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setKeepOptions formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setKeepOptions formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G161" s="25" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setOutlineLevel formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setOutlineLevel formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G162" s="25" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="F163" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setFlowOptions formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setFlowOptions formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G163" s="25" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="F164" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setTabStop formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setTabStop formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G164" s="25" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F165" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearTabStop formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearTabStop formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G165" s="25" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F166" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearAllTabStops formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearAllTabStops formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G166" s="25" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F167" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setBorder formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setBorder formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G167" s="25" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearBorder formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearBorder formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G168" s="25" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setShading formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setShading formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G169" s="25" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F170" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearShading formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearShading formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G170" s="25" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.create, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.create, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G171" s="25" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.attach, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.attach, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G172" s="25" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.detach, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.detach, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G173" s="25" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.join, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.join, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G174" s="25" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="F175" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.canJoin, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.canJoin, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G175" s="25" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.separate, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.separate, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G176" s="25" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevel, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevel, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G177" s="25" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setValue, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setValue, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G178" s="25" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.continuePrevious, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.continuePrevious, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G179" s="25" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="F180" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.canContinuePrevious, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.canContinuePrevious, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G180" s="25" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelRestart, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelRestart, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G181" s="25" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.convertToText, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.convertToText, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G182" s="25" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="F183" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.getStyles.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.getStyles, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G183" s="25" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setDefaultStyle.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setDefaultStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G184" s="25" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.clearDefaultStyle.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearDefaultStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G185" s="25" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.markEntry.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.markEntry, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G186" s="25" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.unmarkEntry.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.unmarkEntry, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G187" s="25" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.listEntries.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.listEntries, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G188" s="25" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F189" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.getEntry.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.getEntry, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G189" s="25" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>Using docapi-sections-toc-fixture.docx, verify the document with header "SuperDoc Example Header" and footer "Custom footer" shows the section/TOC change specified by toc.editEntry.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run toc.editEntry, and verify table-of-contents entries/format update visibly for headings in the document.</t>
         </is>
       </c>
       <c r="G190" s="25" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F191" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify history.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run history.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G191" s="25" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="F192" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify history.undo yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run history.undo, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G192" s="25" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify history.redo yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run history.redo, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G193" s="25" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.apply.paragraph visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply.paragraph, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.apply.run visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply.run, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.accept.</t>
+          <t>Start from Blank.docx, run trackChanges.decide.accept, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.acceptAll.</t>
+          <t>Start from Blank.docx, run trackChanges.decide.acceptAll, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.reject.</t>
+          <t>Start from Blank.docx, run trackChanges.decide.reject, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.rejectAll.</t>
+          <t>Start from Blank.docx, run trackChanges.decide.rejectAll, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify style changes from styles.apply visibly update the intended text or paragraph while neighboring content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify tracked changes for the edited phrase are accepted/rejected or listed exactly as specified by trackChanges.decide.</t>
+          <t>Start from Blank.docx, run trackChanges.decide, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify markdownToFragment yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run markdownToFragment, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify clearContent yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run clearContent, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify blocks.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run blocks.list, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify blocks.deleteRange yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run blocks.deleteRange, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.setDirection formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.setDirection formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>Using docapi-create-paragraph-output.docx, find "bananas" and confirm only the paragraph.clearDirection formatting changes while the words "apples, bananas, mangoes" stay in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.paragraph.clearDirection formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.applyTemplate, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.applyTemplate, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.applyPreset, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.applyPreset, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.captureTemplate, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.captureTemplate, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelNumbering, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelNumbering, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelBullet, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelBullet, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelPictureBullet, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelPictureBullet, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelAlignment, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelAlignment, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelIndents, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelIndents, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelTrailingCharacter, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelTrailingCharacter, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelMarkerFont, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelMarkerFont, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.clearLevelOverrides, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.clearLevelOverrides, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.getStyle, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.getStyle, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.applyStyle, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.applyStyle, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.restartAt, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.restartAt, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelNumberStyle, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelNumberStyle, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelText, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelText, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelStart, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelStart, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify list content renders as expected after lists.setLevelLayout, with ordered list structure reflecting the command (for example items like "Yabba" and "Dabba" in output tests).</t>
+          <t>Start from Blank.docx, run lists.setLevelLayout, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify ranges.resolve yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run ranges.resolve, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.applyStyle.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.applyStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setBorders.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setBorders, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Using docapi-table-ops-fixture.docx, confirm the table that contains "Zebra", "Banana", and "Mango" shows the exact visual change expected from tables.setTableOptions.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setTableOptions, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify create.image yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run create.image, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.list, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.get, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.delete produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.delete, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.move produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.move, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.convertToInline produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.convertToInline, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.convertToFloating produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.convertToFloating, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setSize produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setSize, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setWrapType produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setWrapType, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setWrapSide produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setWrapSide, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setWrapDistances produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setWrapDistances, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setPosition produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setPosition, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setAnchorOptions produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setAnchorOptions, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setZOrder produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setZOrder, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.scale produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.scale, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setLockAspectRatio produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setLockAspectRatio, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.rotate produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.rotate, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.flip produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.flip, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.crop produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.crop, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.resetCrop produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.resetCrop, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.replaceSource produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.replaceSource, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setAltText produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setAltText, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setDecorative produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setDecorative, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setName produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setName, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.setHyperlink produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.setHyperlink, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.insertCaption produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.insertCaption, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.updateCaption produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.updateCaption, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify images.removeCaption produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run images.removeCaption, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify hyperlinks.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run hyperlinks.list, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify hyperlinks.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run hyperlinks.get, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify hyperlinks.wrap produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run hyperlinks.wrap, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify hyperlinks.insert produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run hyperlinks.insert, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify hyperlinks.patch produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run hyperlinks.patch, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify hyperlinks.remove produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run hyperlinks.remove, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.list, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.get, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.resolve produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.resolve, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.refs.set produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.refs.set, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.refs.clear produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.refs.clear, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.refs.setLinkedToPrevious produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.refs.setLinkedToPrevious, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.parts.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.parts.list, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.parts.create produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.parts.create, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G272" s="4" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify headerFooters.parts.delete produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run headerFooters.parts.delete, and verify header/footer content or linkage changes visibly on affected pages.</t>
         </is>
       </c>
       <c r="G273" s="4" t="inlineStr">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify bookmarks.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run bookmarks.list, and verify bookmark anchor behavior matches the command while visible text remains in place.</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify bookmarks.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run bookmarks.get, and verify bookmark anchor behavior matches the command while visible text remains in place.</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify bookmarks.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run bookmarks.insert, and verify bookmark anchor behavior matches the command while visible text remains in place.</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr">
@@ -26048,7 +26048,7 @@
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify bookmarks.rename yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run bookmarks.rename, and verify bookmark anchor behavior matches the command while visible text remains in place.</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify bookmarks.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run bookmarks.remove, and verify bookmark anchor behavior matches the command while visible text remains in place.</t>
         </is>
       </c>
       <c r="G333" s="4" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify footnotes.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run footnotes.list, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
         </is>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify footnotes.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run footnotes.get, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify footnotes.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run footnotes.insert, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify footnotes.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run footnotes.update, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify footnotes.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run footnotes.remove, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify footnotes.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run footnotes.configure, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify crossRefs.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run crossRefs.list, and verify cross-reference text updates to match the referenced target.</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify crossRefs.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run crossRefs.get, and verify cross-reference text updates to match the referenced target.</t>
         </is>
       </c>
       <c r="G341" s="4" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify crossRefs.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run crossRefs.insert, and verify cross-reference text updates to match the referenced target.</t>
         </is>
       </c>
       <c r="G342" s="4" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify crossRefs.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run crossRefs.rebuild, and verify cross-reference text updates to match the referenced target.</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -26776,7 +26776,7 @@
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify crossRefs.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run crossRefs.remove, and verify cross-reference text updates to match the referenced target.</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.list, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.get, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.insert, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G347" s="4" t="inlineStr">
@@ -27024,7 +27024,7 @@
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.configure, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.rebuild, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.remove, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -27198,7 +27198,7 @@
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.entries.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.entries.list, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.entries.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.entries.get, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.entries.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.entries.insert, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.entries.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.entries.update, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -27438,7 +27438,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify index.entries.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run index.entries.remove, and verify index entries/content update visibly where index field content is rendered.</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify captions.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run captions.list, and verify caption text/numbering appears or updates on the intended object.</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify captions.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run captions.get, and verify caption text/numbering appears or updates on the intended object.</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify captions.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run captions.insert, and verify caption text/numbering appears or updates on the intended object.</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify captions.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run captions.update, and verify caption text/numbering appears or updates on the intended object.</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -27744,7 +27744,7 @@
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify captions.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run captions.remove, and verify caption text/numbering appears or updates on the intended object.</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify captions.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run captions.configure, and verify caption text/numbering appears or updates on the intended object.</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify fields.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run fields.list, and verify field results appear/update/remove at the intended location.</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify fields.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run fields.get, and verify field results appear/update/remove at the intended location.</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify fields.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run fields.insert, and verify field results appear/update/remove at the intended location.</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify fields.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run fields.rebuild, and verify field results appear/update/remove at the intended location.</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify fields.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run fields.remove, and verify field results appear/update/remove at the intended location.</t>
         </is>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.list, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.get, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G368" s="4" t="inlineStr">
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.insert, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.update, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.remove, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.sources.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.sources.list, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.sources.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.sources.get, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.sources.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.sources.insert, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G374" s="4" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.sources.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.sources.update, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G375" s="4" t="inlineStr">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.sources.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.sources.remove, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G376" s="4" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.bibliography.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.bibliography.get, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G377" s="4" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.bibliography.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.bibliography.insert, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G378" s="4" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.bibliography.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.bibliography.rebuild, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G379" s="4" t="inlineStr">
@@ -28948,7 +28948,7 @@
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.bibliography.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.bibliography.configure, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify citations.bibliography.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run citations.bibliography.remove, and verify citation/source/bibliography text updates visibly in the document.</t>
         </is>
       </c>
       <c r="G381" s="4" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.list, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G382" s="4" t="inlineStr">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.get, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -29196,7 +29196,7 @@
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.insert, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G384" s="4" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.configure yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.configure, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -29312,7 +29312,7 @@
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.rebuild yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.rebuild, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G386" s="4" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.remove, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G387" s="4" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.entries.list yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.entries.list, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.entries.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.entries.get, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.entries.insert yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.entries.insert, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.entries.update yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.entries.update, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G391" s="4" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify authorities.entries.remove yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run authorities.entries.remove, and verify authorities table entries or references update visibly where rendered.</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify diff.capture yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run diff.capture, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G393" s="4" t="inlineStr">
@@ -29792,7 +29792,7 @@
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify diff.compare yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run diff.compare, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify diff.apply yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run diff.apply, and verify comparison/apply result matches expected visual document differences.</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify protection.get yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run protection.get, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
         </is>
       </c>
       <c r="G396" s="4" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify protection.setEditingRestriction yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run protection.setEditingRestriction, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
@@ -30040,7 +30040,7 @@
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify protection.clearEditingRestriction yields the exact visual result defined by the command inputs in the edited DOCX.</t>
+          <t>Start from Blank.docx, run protection.clearEditingRestriction, and verify the final document visually matches the command intent with concrete before/after changes.</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify permissionRanges.list produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run permissionRanges.list, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify permissionRanges.get produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run permissionRanges.get, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify permissionRanges.create produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run permissionRanges.create, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
         </is>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify permissionRanges.remove produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run permissionRanges.remove, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
         </is>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Using Blank.docx, verify permissionRanges.updatePrincipal produces the requested visual change on the relevant object while existing nearby content remains intact.</t>
+          <t>Start from Blank.docx, run permissionRanges.updatePrincipal, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr">

--- a/Reports/Command Support.xlsx
+++ b/Reports/Command Support.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run create.paragraph, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
+          <t>Start from Blank.docx, run create.paragraph, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run create.heading, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
+          <t>Start from Blank.docx, run create.heading, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run create.table, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
+          <t>Start from Blank.docx, run create.table, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run insert, and verify new content is inserted at the requested location while existing surrounding content remains.</t>
+          <t>Start from Blank.docx, run insert, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.insert, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx seeded with list items "Yabba" then "Dabba", run lists.insert, and verify a new list item appears exactly at the insertion index between the expected neighboring items.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run replace, and verify the original phrase is replaced in place (for example "apples" becomes "blueberries") with surrounding content unchanged.</t>
+          <t>Start from Blank.docx containing "apples, bananas, mangoes", run replace with text "blueberries", and verify the line reads "apples, blueberries, mangoes" in the same location.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run delete, and verify the requested content is removed and no longer visible in that region.</t>
+          <t>Start from Blank.docx containing "apples, bananas, mangoes", run delete on "bananas", and verify that token is removed while "apples" and "mangoes" remain in order.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run blocks.delete, and verify the requested content is removed and no longer visible in that region.</t>
+          <t>Start from Blank.docx with at least one paragraph block, run blocks.delete on that block, and verify that entire block no longer appears in the document.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.apply formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.apply with bold+underline+fontSize=48+color=FF0000+highlight=yellow, and verify "bananas" shows those exact visual properties.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only its font size changes relative to "apples" and "mangoes".</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.fontSize value=48, and verify only "bananas" is visibly larger.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only its typeface changes while text content and order stay unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.fontFamily value="Arial", and verify only "bananas" changes to Arial.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only its font color changes while its text and position stay the same.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.color value="FF0000", and verify only "bananas" turns red.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify only the format.align formatting property changes while "apples, bananas, mangoes" stays in the same order.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.align alignment="right" (or "center"), and verify that paragraph alignment changes accordingly.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run comments.create, and verify comment markers/bubbles appear, update, or disappear at the intended text location.</t>
+          <t>Start from Blank.docx, run comments.create with text "is this compliant?", and verify a new comment marker appears on the selected text with that exact comment content.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run comments.patch, and verify comment markers/bubbles appear, update, or disappear at the intended text location.</t>
+          <t>Start from Blank.docx after creating comment "initial comment", run comments.patch with "patched comment text", and verify the same comment now displays "patched comment text".</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run comments.delete, and verify comment markers/bubbles appear, update, or disappear at the intended text location.</t>
+          <t>Start from Blank.docx after creating comment "delete me", run comments.delete, and verify that comment marker/bubble is removed from the selected text.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setType, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx seeded with list items "Yabba" and "Dabba", run lists.setType kind="bullet", and verify those items render as a bulleted list.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.indent, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx seeded with list items "Yabba" and "Dabba", run lists.indent on the second item, and verify "Dabba" is visibly nested one level deeper.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.outdent, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx seeded with list items "Yabba" and "Dabba", run lists.outdent on the indented item, and verify it returns to the parent list level.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.restart, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx seeded with list items "Yabba" and "Dabba", run lists.restart on the second item, and verify numbering restarts from 1 at "Dabba".</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.exit, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx seeded with list items "Yabba" and "Dabba", run lists.exit on the selected item, and verify a normal paragraph appears after the list at that location.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it appears bold while "apples" and "mangoes" remain regular weight.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.bold, and verify only "bananas" is bold.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it appears italic while neighboring words keep normal style.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.italic, and verify only "bananas" is italic.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a visible underline while other words remain unlined.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.underline, and verify only "bananas" is underlined.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a single strike-through line while nearby words do not.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.strikethrough, and verify only "bananas" has a strike-through line.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.apply (run), and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply (run), and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.apply (paragraph), and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply (paragraph), and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.delete, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.delete, and verify the table containing rows "Zebra|Banana|Mango" and "Apple|Grape|Kiwi" is removed entirely.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.clearContents, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearContents, and verify table grid remains but cell text like "Zebra", "Banana", and "Mango" is cleared.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.split, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.split atRowIndex=1, and verify one table becomes two tables split at that row boundary.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.convertToText, and verify table rows including "Zebra | Banana | Mango" become plain text lines at the same location.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.convertToText delimiter="tab", and verify table rows such as "Zebra	Banana	Mango" become plain text lines.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setLayout, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setLayout alignment="center" autoFitMode="fixedWidth" preferredWidth=7200, and verify the table is centered with fixed width behavior.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setRowHeight, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setRowHeight rowIndex=0 heightPt=24 rule="atLeast", and verify the first row becomes visibly taller.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.distributeRows, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.distributeRows, and verify row heights are equalized across the table.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setRowOptions, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setRowOptions rowIndex=0 repeatHeader=true allowBreakAcrossPages=false, and verify first row is marked as repeating header with no row split across pages.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setColumnWidth, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setColumnWidth columnIndex=0 widthPt=120, and verify the first column width visibly changes.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.distributeColumns, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.distributeColumns, and verify columns are equalized in width.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.insertCell, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.insertCell mode="shiftRight" on the first cell, and verify a new empty cell is inserted with cells shifted right.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.deleteCell, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.deleteCell mode="shiftLeft" on the first cell, and verify that cell is removed with neighboring cells shifted left.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.mergeCells, and verify cells around "Banana" and adjacent values are merged or split exactly as requested.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.mergeCells from (0,0) to (0,1), and verify "Zebra" and "Banana" become one merged top-row cell.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.unmergeCells, and verify cells around "Banana" and adjacent values are merged or split exactly as requested.</t>
+          <t>Start from docapi-table-ops-fixture.docx after merging top-row cells, run tables.unmergeCells, and verify the merged cell splits back into separate cells.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.splitCell, and verify cells around "Banana" and adjacent values are merged or split exactly as requested.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.splitCell rows=2 columns=2 on the first cell, and verify that one cell becomes a 2x2 cell subdivision.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellProperties, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellProperties verticalAlign="center" wrapText=true fitText=false on the first cell, and verify those cell text-flow/alignment properties are visible.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.sort, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.sort by columnIndex=0 ascending text, and verify rows reorder alphabetically by the first column.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setAltText, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setAltText title="Doc API table" description="Generated by harness", and verify table alt-text metadata reflects those exact strings.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setStyle styleId="TableGrid", and verify table style changes to TableGrid.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.clearStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx after applying style TableGrid, run tables.clearStyle, and verify explicit table style formatting is removed.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setStyleOption, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setStyleOption flag="headerRow" enabled=true, and verify header-row styling is enabled on the first row.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setBorder, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setBorder edge="top" style="single" lineWeightPt=1 color="FF0000", and verify a red top border appears.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.clearBorder, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearBorder edge="insideH", and verify horizontal inside borders are cleared.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.applyBorderPreset, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.applyBorderPreset preset="grid", and verify full grid borders are applied.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setShading, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setShading color="FFFF00", and verify table cell shading turns yellow.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.clearShading, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearShading, and verify table cell shading is removed.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setTablePadding, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setTablePadding all sides 14.4pt, and verify increased inner spacing around table cell content.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellPadding, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellPadding on first cell with all sides 14.4pt, and verify that cell shows increased inner padding.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellSpacing, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setCellSpacing spacingPt=2, and verify visible spacing appears between cells.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.clearCellSpacing, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearCellSpacing, and verify cell spacing between table cells is removed.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide (accept), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx, run trackChanges.decide (accept), and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide (reject), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx, run trackChanges.decide (reject), and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide (acceptAll), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx, run trackChanges.decide (acceptAll), and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide (rejectAll), and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx, run trackChanges.decide (rejectAll), and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run query.match, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
+          <t>Start from Blank.docx containing "bananas", run query.match pattern="bananas", and verify the document visual content stays unchanged while returning matches.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run mutations.preview, and verify the document looks unchanged (for example the same visible text remains) while the command only returns data.</t>
+          <t>Start from Blank.docx with text containing "bananas", run mutations.preview for replacement text "preview text", and verify no visible document change is applied yet.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run mutations.apply, and verify each applied mutation produces the expected visible before/after result in the document.</t>
+          <t>Start from Blank.docx with text containing "bananas", run mutations.apply replacing with "applied text", and verify the matched text is visibly replaced by "applied text".</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Start from docapi-convert-from-text-fixture.docx, run tables.convertFromText, and verify text including "Alpha|Beta|Gamma" becomes a visible table with corresponding cell values.</t>
+          <t>Start from docapi-convert-from-text-fixture.docx, run tables.convertFromText on text "Alpha|Beta|Gamma" with delimiter "|" and columns=3, and verify that line becomes a 3-column table row.</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, move the row "Zebra | Banana | Mango" to the requested destination, and verify it appears in the new position and is absent from the original row slot.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.move destination=documentStart, and verify the table appears at the top of the document and not in its previous position.</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="F87" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run create.sectionBreak, and verify a new section boundary appears with subsequent layout behavior changing after the break.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run create.sectionBreak breakType="continuous" at document end, and verify a new continuous section boundary is created.</t>
         </is>
       </c>
       <c r="G87" s="22" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run create.tableOfContents, and verify table-of-contents entries/format update visibly for headings in the document.</t>
+          <t>Start from docapi-sections-toc-fixture.docx, add heading "TOC Heading Alpha" then run create.tableOfContents at document start, and verify a TOC appears with that heading entry.</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F89" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.clearHeaderFooterRef, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx after setting first-page header ref, run sections.clearHeaderFooterRef kind="header" variant="first", and verify the first-page header reference is removed.</t>
         </is>
       </c>
       <c r="G89" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.clearPageBorders, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx after applying page borders, run sections.clearPageBorders, and verify page borders are removed.</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="F93" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setBreakType, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setBreakType breakType="continuous", and verify the section break type updates to continuous.</t>
         </is>
       </c>
       <c r="G93" s="22" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setColumns, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setColumns count=2 equalWidth=true gap=720, and verify body content flows in two equal-width columns.</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="F95" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setHeaderFooterMargins, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setHeaderFooterMargins header=360 footer=480, and verify header/footer offsets update.</t>
         </is>
       </c>
       <c r="G95" s="22" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setHeaderFooterRef, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setHeaderFooterRef kind="header" variant="first", and verify first-page header uses the selected reference.</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F97" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setLineNumbering, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setLineNumbering enabled=true countBy=1 start=1 distance=360 restart="newPage", and verify line numbers appear with that configuration.</t>
         </is>
       </c>
       <c r="G97" s="22" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setLinkToPrevious, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx with at least two sections, run sections.setLinkToPrevious linked=true for header default, and verify the second section header links to previous section.</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F99" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setOddEvenHeadersFooters, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setOddEvenHeadersFooters enabled=true, and verify odd and even pages can display different headers/footers.</t>
         </is>
       </c>
       <c r="G99" s="22" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageBorders, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageBorders top border style="single" size=8 color="FF0000", and verify a red top page border appears.</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="F101" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageMargins, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageMargins top=1000 right=1100 bottom=1200 left=900, and verify page margins visibly update.</t>
         </is>
       </c>
       <c r="G101" s="22" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageNumbering, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageNumbering start=5 format="lowerRoman", and verify page numbers restart at v.</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F103" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageSetup, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setPageSetup orientation="landscape" width=15840 height=12240, and verify page orientation changes to landscape with those dimensions.</t>
         </is>
       </c>
       <c r="G103" s="22" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setSectionDirection, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setSectionDirection direction="rtl", and verify section direction becomes right-to-left.</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="F105" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setTitlePage, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setTitlePage enabled=true, and verify first-page header/footer behavior changes to title-page mode.</t>
         </is>
       </c>
       <c r="G105" s="22" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run sections.setVerticalAlign, and verify section layout visibly changes in the document that includes header "SuperDoc Example Header" and footer "Custom footer".</t>
+          <t>Start from docapi-sections-toc-fixture.docx, run sections.setVerticalAlign value="center", and verify section body text is vertically centered on the page.</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="F107" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run toc.configure, and verify table-of-contents entries/format update visibly for headings in the document.</t>
+          <t>Start from docapi-sections-toc-fixture.docx with an existing TOC, run toc.configure hyperlinks=false hideInWebView=true outlineLevels=1..2, and verify TOC updates to those settings.</t>
         </is>
       </c>
       <c r="G107" s="22" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run toc.remove, and verify table-of-contents entries/format update visibly for headings in the document.</t>
+          <t>Start from docapi-sections-toc-fixture.docx with an existing TOC, run toc.remove, and verify the TOC field is removed from the document.</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="F111" s="22" t="inlineStr">
         <is>
-          <t>Start from docapi-sections-toc-fixture.docx, run toc.update, and verify table-of-contents entries/format update visibly for headings in the document.</t>
+          <t>Start from docapi-sections-toc-fixture.docx with an existing TOC, run toc.update, and verify TOC entries refresh to current heading text and page numbers.</t>
         </is>
       </c>
       <c r="G111" s="22" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="F112" s="25" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a single strike-through line while nearby words do not.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.strike, and verify only "bananas" has a strike-through line.</t>
         </is>
       </c>
       <c r="G112" s="25" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F113" s="25" t="inlineStr">
         <is>
-          <t>Start from docapi-create-paragraph-output.docx, find "bananas", and verify it has a bright yellow marker-style highlight while "apples" and "mangoes" stay visually unchanged.</t>
+          <t>Start from docapi-create-paragraph-output.docx containing "apples, bananas, mangoes", run format.highlight value="yellow", and verify "bananas" has a bright yellow marker-style highlight.</t>
         </is>
       </c>
       <c r="G113" s="25" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="F152" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.paragraph.setStyle, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.paragraph.setStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G152" s="25" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="F153" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.paragraph.clearStyle, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.paragraph.clearStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G153" s="25" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F171" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.create, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.create, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G171" s="25" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F172" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.attach, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.attach, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G172" s="25" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.detach, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.detach, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G173" s="25" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.join, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.join, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G174" s="25" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="F175" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.canJoin, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.canJoin, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G175" s="25" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.separate, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.separate, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G176" s="25" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevel, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevel, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G177" s="25" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setValue, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setValue, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G178" s="25" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.continuePrevious, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.continuePrevious, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G179" s="25" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="F180" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.canContinuePrevious, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.canContinuePrevious, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G180" s="25" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelRestart, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelRestart, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G181" s="25" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.convertToText, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.convertToText, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G182" s="25" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F184" s="25" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setDefaultStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setDefaultStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G184" s="25" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.clearDefaultStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.clearDefaultStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G185" s="25" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="F192" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run history.undo, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run history.undo, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G192" s="25" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run history.redo, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run history.redo, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G193" s="25" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.apply.paragraph, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply.paragraph with justification="center" on doc defaults, and verify new paragraphs default to centered alignment.</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.apply.run, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply.run with patch bold=true and fontSize=28 on doc defaults, and verify newly typed run text renders bold at larger size.</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide.accept, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx after inserting tracked text "tracked change seed", run trackChanges.decide.accept, and verify that tracked insertion is accepted into final visible text.</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide.acceptAll, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx after inserting tracked text "tracked change seed", run trackChanges.decide.acceptAll, and verify all tracked insertions become normal visible text.</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide.reject, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx after inserting tracked text "tracked change seed", run trackChanges.decide.reject, and verify that tracked insertion is removed from final visible text.</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide.rejectAll, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx after inserting tracked text "tracked change seed", run trackChanges.decide.rejectAll, and verify all tracked insertions are removed.</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run styles.apply, and verify style changes are visible on the intended text/paragraph while surrounding content remains unchanged.</t>
+          <t>Start from Blank.docx, run styles.apply, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run trackChanges.decide, and verify tracked changes around the edited phrase are listed or resolved exactly as requested.</t>
+          <t>Start from Blank.docx, run trackChanges.decide, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run markdownToFragment, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run markdownToFragment, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run clearContent, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run clearContent, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run blocks.list, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run blocks.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run blocks.deleteRange, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run blocks.deleteRange, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.applyTemplate, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.applyTemplate, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.applyPreset, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.applyPreset, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.captureTemplate, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.captureTemplate, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelNumbering, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelNumbering, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelBullet, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelBullet, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelPictureBullet, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelPictureBullet, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelAlignment, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelAlignment, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelIndents, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelIndents, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelTrailingCharacter, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelTrailingCharacter, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelMarkerFont, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelMarkerFont, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.clearLevelOverrides, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.clearLevelOverrides, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.getStyle, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.getStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.applyStyle, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.applyStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.restartAt, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.restartAt, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelNumberStyle, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelNumberStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelText, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelText, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelStart, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelStart, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run lists.setLevelLayout, and verify list structure updates visibly so list items (for example "Yabba" and "Dabba") reflect the requested numbering/bullet behavior.</t>
+          <t>Start from Blank.docx, run lists.setLevelLayout, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.applyStyle, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.applyStyle, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setBorders, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setBorders, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>Start from docapi-table-ops-fixture.docx, run tables.setTableOptions, and verify the table containing "Zebra", "Banana", and "Mango" shows the exact visual change requested by the command.</t>
+          <t>Start from docapi-table-ops-fixture.docx, run tables.setTableOptions, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run create.image, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run create.image, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.list, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.get, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.get, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.delete, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.delete, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.move, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.move, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.convertToInline, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.convertToInline, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.convertToFloating, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.convertToFloating, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setSize, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setSize, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setWrapType, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setWrapType, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setWrapSide, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setWrapSide, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setWrapDistances, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setWrapDistances, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setPosition, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setPosition, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setAnchorOptions, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setAnchorOptions, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setZOrder, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setZOrder, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.scale, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.scale, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setLockAspectRatio, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setLockAspectRatio, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.rotate, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.rotate, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.flip, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.flip, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.crop, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.crop, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.resetCrop, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.resetCrop, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.replaceSource, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.replaceSource, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setAltText, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setAltText, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setDecorative, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setDecorative, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setName, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setName, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.setHyperlink, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.setHyperlink, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.insertCaption, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.insertCaption, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.updateCaption, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.updateCaption, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run images.removeCaption, and verify the image near its caption changes position/size/wrap/metadata exactly as requested without moving unrelated text.</t>
+          <t>Start from Blank.docx, run images.removeCaption, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run hyperlinks.list, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
+          <t>Start from Blank.docx, run hyperlinks.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run hyperlinks.get, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
+          <t>Start from Blank.docx, run hyperlinks.get, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run hyperlinks.wrap, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
+          <t>Start from Blank.docx, run hyperlinks.wrap, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run hyperlinks.insert, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
+          <t>Start from Blank.docx, run hyperlinks.insert, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run hyperlinks.patch, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
+          <t>Start from Blank.docx, run hyperlinks.patch, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run hyperlinks.remove, and verify hyperlink text appears/updates/removes exactly at the intended words.</t>
+          <t>Start from Blank.docx, run hyperlinks.remove, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G264" s="4" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.setLockMode, and verify the control remains visible around "XYZ" with the requested lock behavior enforced.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.setLockMode="sdtContentLocked", and verify "XYZ" remains visible while both control deletion and content editing are blocked.</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.setType to the requested type, and verify the control remains at the same position with "XYZ" still visible.</t>
+          <t>Start from Blank.docx with a content control containing "XYZ", run contentControls.setType to "richText", and verify the same control remains in place with "XYZ" still visible as rich-text content.</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx with a date content control, run contentControls.date.setDisplayLocale, and verify the date renders using the requested locale style.</t>
+          <t>Start from Blank.docx with a date content control showing 2026-04-06, run contentControls.date.setDisplayLocale("en-US"), and verify the date renders in U.S. locale style.</t>
         </is>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx with a date content control, run contentControls.date.setCalendar, and verify date behavior follows the requested calendar setting.</t>
+          <t>Start from Blank.docx with a date content control, run contentControls.date.setCalendar("gregorian"), and verify the date uses Gregorian calendar behavior.</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx with a checkbox content control, run contentControls.checkbox.setSymbolPair, and verify checked/unchecked glyphs render using the requested symbols.</t>
+          <t>Start from Blank.docx with a checkbox content control, run contentControls.checkbox.setSymbolPair using unchecked="☐" and checked="☑", and verify those exact glyphs render for unchecked/checked states.</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run footnotes.list, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
+          <t>Start from Blank.docx, run footnotes.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run footnotes.get, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
+          <t>Start from Blank.docx, run footnotes.get, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run footnotes.insert, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
+          <t>Start from Blank.docx, run footnotes.insert, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run footnotes.update, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
+          <t>Start from Blank.docx, run footnotes.update, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run footnotes.remove, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
+          <t>Start from Blank.docx, run footnotes.remove, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run footnotes.configure, and verify footnote marks/content are inserted, updated, or removed at the intended reference text.</t>
+          <t>Start from Blank.docx, run footnotes.configure, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run captions.list, and verify caption text/numbering appears or updates on the intended object.</t>
+          <t>Start from Blank.docx, run captions.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run captions.get, and verify caption text/numbering appears or updates on the intended object.</t>
+          <t>Start from Blank.docx, run captions.get, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run captions.insert, and verify caption text/numbering appears or updates on the intended object.</t>
+          <t>Start from Blank.docx, run captions.insert, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run captions.update, and verify caption text/numbering appears or updates on the intended object.</t>
+          <t>Start from Blank.docx, run captions.update, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -27744,7 +27744,7 @@
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run captions.remove, and verify caption text/numbering appears or updates on the intended object.</t>
+          <t>Start from Blank.docx, run captions.remove, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run captions.configure, and verify caption text/numbering appears or updates on the intended object.</t>
+          <t>Start from Blank.docx, run captions.configure, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run fields.list, and verify field results appear/update/remove at the intended location.</t>
+          <t>Start from Blank.docx, run fields.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run fields.get, and verify field results appear/update/remove at the intended location.</t>
+          <t>Start from Blank.docx, run fields.get, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run fields.insert, and verify field results appear/update/remove at the intended location.</t>
+          <t>Start from Blank.docx, run fields.insert, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run fields.rebuild, and verify field results appear/update/remove at the intended location.</t>
+          <t>Start from Blank.docx, run fields.rebuild, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run fields.remove, and verify field results appear/update/remove at the intended location.</t>
+          <t>Start from Blank.docx, run fields.remove, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run protection.setEditingRestriction, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run protection.setEditingRestriction, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G397" s="4" t="inlineStr">
@@ -30040,7 +30040,7 @@
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run protection.clearEditingRestriction, and verify the final document visually matches the command intent with concrete before/after changes.</t>
+          <t>Start from Blank.docx, run protection.clearEditingRestriction, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run permissionRanges.list, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
+          <t>Start from Blank.docx, run permissionRanges.list, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run permissionRanges.get, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
+          <t>Start from Blank.docx, run permissionRanges.get, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run permissionRanges.create, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
+          <t>Start from Blank.docx, run permissionRanges.create, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run permissionRanges.remove, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
+          <t>Start from Blank.docx, run permissionRanges.remove, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Start from Blank.docx, run permissionRanges.updatePrincipal, and verify permission boundaries appear around the intended text region and editing behavior changes accordingly.</t>
+          <t>Start from Blank.docx, run permissionRanges.updatePrincipal, and verify one concrete before/after visual change (with exact text tokens used by that test case) is present in the final DOCX.</t>
         </is>
       </c>
       <c r="G403" s="4" t="inlineStr">
